--- a/Results/Phase 2/Carbon dioxide/carbon dioxide land use results.xlsx
+++ b/Results/Phase 2/Carbon dioxide/carbon dioxide land use results.xlsx
@@ -2074,7 +2074,7 @@
         <v>2.171817906514845</v>
       </c>
       <c r="F2" t="n">
-        <v>4.178289807151179</v>
+        <v>4.17828980715118</v>
       </c>
       <c r="G2" t="n">
         <v>1.329438976755794</v>
@@ -2268,7 +2268,7 @@
         <v>2.194710356465353</v>
       </c>
       <c r="L4" t="n">
-        <v>2.737673960743712</v>
+        <v>2.737673960743713</v>
       </c>
       <c r="M4" t="n">
         <v>1.833742045267343</v>
@@ -2684,7 +2684,7 @@
         <v>3.101172324977011</v>
       </c>
       <c r="D9" t="n">
-        <v>2.20341824594519</v>
+        <v>2.203418245945189</v>
       </c>
       <c r="E9" t="n">
         <v>2.260657984047339</v>
@@ -2726,7 +2726,7 @@
         <v>2.800985282619354</v>
       </c>
       <c r="R9" t="n">
-        <v>7.254430732023025</v>
+        <v>7.254430732023024</v>
       </c>
       <c r="S9" t="n">
         <v>3.216244125220792</v>
@@ -5014,82 +5014,82 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8462005103219469</v>
+        <v>0.8462005103219292</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9564663015044781</v>
+        <v>0.9564663015044783</v>
       </c>
       <c r="D2" t="n">
-        <v>1.260349048039941</v>
+        <v>1.260349048039915</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5455514366598243</v>
+        <v>0.5455514366598223</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7619345393056375</v>
+        <v>0.7619345393056348</v>
       </c>
       <c r="G2" t="n">
-        <v>2.696870823202551</v>
+        <v>2.696870823203148</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4429054816331728</v>
+        <v>0.4429054816331642</v>
       </c>
       <c r="I2" t="n">
-        <v>3.252440518138965</v>
+        <v>3.252440518138945</v>
       </c>
       <c r="J2" t="n">
-        <v>1.818917156924672</v>
+        <v>1.818917156924695</v>
       </c>
       <c r="K2" t="n">
-        <v>1.523076854739529</v>
+        <v>1.523076854739509</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5683716269699937</v>
+        <v>0.5683716269699707</v>
       </c>
       <c r="M2" t="n">
-        <v>2.436353410027662</v>
+        <v>2.436353410027661</v>
       </c>
       <c r="N2" t="n">
-        <v>1.104281799475965</v>
+        <v>1.104281799475954</v>
       </c>
       <c r="O2" t="n">
-        <v>1.200281197286283</v>
+        <v>1.200281197286285</v>
       </c>
       <c r="P2" t="n">
-        <v>1.436087897431856</v>
+        <v>1.436087897431844</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.382271009773671</v>
+        <v>2.38227100977366</v>
       </c>
       <c r="R2" t="n">
-        <v>0.5940124318643213</v>
+        <v>0.5940124318643109</v>
       </c>
       <c r="S2" t="n">
-        <v>1.55291971949273</v>
+        <v>1.552919719492724</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8053644939520097</v>
+        <v>0.8053644939519944</v>
       </c>
       <c r="U2" t="n">
-        <v>1.044390165867603</v>
+        <v>1.044390165867551</v>
       </c>
       <c r="V2" t="n">
-        <v>1.198836897374544</v>
+        <v>1.198836897374546</v>
       </c>
       <c r="W2" t="n">
-        <v>1.182841045163254</v>
+        <v>1.182841045163235</v>
       </c>
       <c r="X2" t="n">
-        <v>1.194945011687066</v>
+        <v>1.194945011687051</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.908185581824119</v>
+        <v>1.908185581824117</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.369591648201469</v>
+        <v>1.369591648201461</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.009557754963387</v>
+        <v>1.009557754963368</v>
       </c>
       <c r="AB2" t="n">
         <v>2.427778462725086</v>
@@ -5102,85 +5102,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5500119019568719</v>
+        <v>0.5500119019568444</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7633854188513542</v>
+        <v>0.7633854188513681</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7532471008127481</v>
+        <v>0.7532471008127815</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6363166698225421</v>
+        <v>0.6363166698225511</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5753395001401165</v>
+        <v>0.57533950014013</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7953892432163527</v>
+        <v>0.7953892432163501</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7532471008127481</v>
+        <v>0.7532471008127815</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7532471008127481</v>
+        <v>0.7532471008127815</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7489443328356155</v>
+        <v>0.7489443328356099</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7532471008127481</v>
+        <v>0.7532471008127815</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7532471008127481</v>
+        <v>0.7532471008127815</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7593957464479305</v>
+        <v>0.7593957464479466</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5957058210605091</v>
+        <v>0.5957058210604855</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6389995323633654</v>
+        <v>0.6389995323633569</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6283871976328352</v>
+        <v>0.6283871976328423</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5100715469170873</v>
+        <v>0.5100715469170639</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7532471008127481</v>
+        <v>0.7532471008127815</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7532471008127481</v>
+        <v>0.7532471008127815</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7532471008127481</v>
+        <v>0.7532471008127815</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6525915429922644</v>
+        <v>0.6525915429922412</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6853132685277747</v>
+        <v>0.6853132685277785</v>
       </c>
       <c r="W3" t="n">
-        <v>0.753287041815341</v>
+        <v>0.7532870418153417</v>
       </c>
       <c r="X3" t="n">
-        <v>0.5286984563952699</v>
+        <v>0.5286984563952577</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.9528230184834275</v>
+        <v>0.9528230184834655</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.5462367038477045</v>
+        <v>0.5462367038477006</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.7532471008127481</v>
+        <v>0.7532471008127815</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9654734766494339</v>
+        <v>0.9654734766494233</v>
       </c>
     </row>
     <row r="4">
@@ -5190,85 +5190,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.556647491959757</v>
+        <v>1.556647491959753</v>
       </c>
       <c r="C4" t="n">
-        <v>1.603281098203192</v>
+        <v>1.60328109820319</v>
       </c>
       <c r="D4" t="n">
-        <v>1.707599770780344</v>
+        <v>1.7075997707803</v>
       </c>
       <c r="E4" t="n">
-        <v>1.441526787280569</v>
+        <v>1.441526787280579</v>
       </c>
       <c r="F4" t="n">
-        <v>1.521908158857501</v>
+        <v>1.521908158857485</v>
       </c>
       <c r="G4" t="n">
-        <v>2.231195089337083</v>
+        <v>2.231195089336968</v>
       </c>
       <c r="H4" t="n">
-        <v>1.409651189732035</v>
+        <v>1.409651189732017</v>
       </c>
       <c r="I4" t="n">
-        <v>2.433693719312356</v>
+        <v>2.433693719312336</v>
       </c>
       <c r="J4" t="n">
-        <v>1.881963795219856</v>
+        <v>1.881963795219902</v>
       </c>
       <c r="K4" t="n">
-        <v>1.803360971216646</v>
+        <v>1.803360971216641</v>
       </c>
       <c r="L4" t="n">
-        <v>1.45538212640946</v>
+        <v>1.455382126409418</v>
       </c>
       <c r="M4" t="n">
-        <v>2.140147087888223</v>
+        <v>2.140147087888224</v>
       </c>
       <c r="N4" t="n">
-        <v>1.650715091312917</v>
+        <v>1.650715091312914</v>
       </c>
       <c r="O4" t="n">
-        <v>1.685705744532939</v>
+        <v>1.685705744532904</v>
       </c>
       <c r="P4" t="n">
-        <v>1.771654517753925</v>
+        <v>1.771654517753902</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.116527151559447</v>
+        <v>2.116527151559429</v>
       </c>
       <c r="R4" t="n">
-        <v>1.464727898703888</v>
+        <v>1.464727898703869</v>
       </c>
       <c r="S4" t="n">
-        <v>1.814238344986588</v>
+        <v>1.814238344986548</v>
       </c>
       <c r="T4" t="n">
-        <v>1.541763243513657</v>
+        <v>1.541763243513607</v>
       </c>
       <c r="U4" t="n">
-        <v>1.62888529414572</v>
+        <v>1.628885294145727</v>
       </c>
       <c r="V4" t="n">
-        <v>1.501575608668375</v>
+        <v>1.501575608668369</v>
       </c>
       <c r="W4" t="n">
-        <v>1.679349013876674</v>
+        <v>1.679349013876656</v>
       </c>
       <c r="X4" t="n">
-        <v>1.683760767542658</v>
+        <v>1.683760767542677</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.943728580063984</v>
+        <v>1.943728580063975</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.747417415747813</v>
+        <v>1.747417415747806</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.61618928939397</v>
+        <v>1.616189289393935</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.133069735801335</v>
+        <v>2.133069735801308</v>
       </c>
     </row>
     <row r="5">
@@ -5278,85 +5278,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.448690222232914</v>
+        <v>1.448690222232933</v>
       </c>
       <c r="C5" t="n">
-        <v>1.532905383746338</v>
+        <v>1.53290538374632</v>
       </c>
       <c r="D5" t="n">
-        <v>1.52276706570771</v>
+        <v>1.522767065707706</v>
       </c>
       <c r="E5" t="n">
-        <v>1.474609648949226</v>
+        <v>1.474609648949208</v>
       </c>
       <c r="F5" t="n">
-        <v>1.453896458191232</v>
+        <v>1.453896458191236</v>
       </c>
       <c r="G5" t="n">
-        <v>1.538127381755794</v>
+        <v>1.538127381755809</v>
       </c>
       <c r="H5" t="n">
-        <v>1.52276706570771</v>
+        <v>1.522767065707706</v>
       </c>
       <c r="I5" t="n">
-        <v>1.52276706570771</v>
+        <v>1.522767065707706</v>
       </c>
       <c r="J5" t="n">
-        <v>1.491971265094665</v>
+        <v>1.491971265094678</v>
       </c>
       <c r="K5" t="n">
-        <v>1.52276706570771</v>
+        <v>1.522767065707706</v>
       </c>
       <c r="L5" t="n">
-        <v>1.52276706570771</v>
+        <v>1.522767065707706</v>
       </c>
       <c r="M5" t="n">
-        <v>1.528915711344526</v>
+        <v>1.52891571134449</v>
       </c>
       <c r="N5" t="n">
-        <v>1.465345119181165</v>
+        <v>1.465345119181114</v>
       </c>
       <c r="O5" t="n">
-        <v>1.481125168570586</v>
+        <v>1.481125168570604</v>
       </c>
       <c r="P5" t="n">
-        <v>1.477257097177669</v>
+        <v>1.477257097177644</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.434132431824267</v>
+        <v>1.434132431824227</v>
       </c>
       <c r="R5" t="n">
-        <v>1.52276706570771</v>
+        <v>1.522767065707706</v>
       </c>
       <c r="S5" t="n">
-        <v>1.52276706570771</v>
+        <v>1.522767065707706</v>
       </c>
       <c r="T5" t="n">
-        <v>1.52276706570771</v>
+        <v>1.522767065707706</v>
       </c>
       <c r="U5" t="n">
-        <v>1.486079296839368</v>
+        <v>1.486079296839382</v>
       </c>
       <c r="V5" t="n">
-        <v>1.314402276052632</v>
+        <v>1.314402276052657</v>
       </c>
       <c r="W5" t="n">
-        <v>1.522781623734157</v>
+        <v>1.522781623734132</v>
       </c>
       <c r="X5" t="n">
-        <v>1.440921721600866</v>
+        <v>1.440921721600844</v>
       </c>
       <c r="Y5" t="n">
         <v>1.59551014415992</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.447314206852752</v>
+        <v>1.447314206852758</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.52276706570771</v>
+        <v>1.522767065707706</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.600076739628814</v>
+        <v>1.60007673962882</v>
       </c>
     </row>
     <row r="6">
@@ -5366,85 +5366,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4657819108990078</v>
+        <v>0.4657819108990039</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5124155171424185</v>
+        <v>0.5124155171424174</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6167341897195554</v>
+        <v>0.6167341897195504</v>
       </c>
       <c r="E6" t="n">
         <v>0.3506612062198056</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4310425777967216</v>
+        <v>0.4310425777967223</v>
       </c>
       <c r="G6" t="n">
-        <v>1.129242129296706</v>
+        <v>1.129242129296708</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3187856086712748</v>
+        <v>0.3187856086712731</v>
       </c>
       <c r="I6" t="n">
-        <v>1.342828138251584</v>
+        <v>1.342828138251579</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8069018078968797</v>
+        <v>0.8069018078969229</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7124953901558879</v>
+        <v>0.7124953901558951</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3645165453486827</v>
+        <v>0.3645165453486777</v>
       </c>
       <c r="M6" t="n">
-        <v>1.049281506827466</v>
+        <v>1.049281506827464</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5598495102521444</v>
+        <v>0.5598495102521501</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5837527844926736</v>
+        <v>0.583752784492657</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6697015577136627</v>
+        <v>0.6697015577136585</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.025661570498686</v>
+        <v>1.025661570498679</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3738623176431329</v>
+        <v>0.3738623176431284</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7233727639258267</v>
+        <v>0.7233727639258202</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4508976624528799</v>
+        <v>0.4508976624528824</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5269323341054769</v>
+        <v>0.5269323341054675</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5769459689779167</v>
+        <v>0.5769459689779185</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5773960538364353</v>
+        <v>0.577396053836425</v>
       </c>
       <c r="X6" t="n">
-        <v>0.5818078075024145</v>
+        <v>0.5818078075023964</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.8528629990032341</v>
+        <v>0.8528629990032298</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.6565518346870561</v>
+        <v>0.6565518346870538</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.5253237083331986</v>
+        <v>0.5253237083331962</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.042204154740542</v>
+        <v>1.042204154740543</v>
       </c>
     </row>
     <row r="7">
@@ -5454,85 +5454,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3578246411721779</v>
+        <v>0.3578246411721693</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4420398026855416</v>
+        <v>0.442039802685551</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4319014846469423</v>
+        <v>0.4319014846469436</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3837440678884338</v>
+        <v>0.3837440678884402</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3630308771304619</v>
+        <v>0.3630308771304692</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4361744217155415</v>
+        <v>0.4361744217155695</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4319014846469423</v>
+        <v>0.4319014846469436</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4319014846469423</v>
+        <v>0.4319014846469436</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4169092777717008</v>
+        <v>0.4169092777716728</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4319014846469423</v>
+        <v>0.4319014846469437</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4319014846469423</v>
+        <v>0.4319014846469436</v>
       </c>
       <c r="M7" t="n">
-        <v>0.438050130283735</v>
+        <v>0.4380501302837413</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3744795381203668</v>
+        <v>0.3744795381203214</v>
       </c>
       <c r="O7" t="n">
         <v>0.3791722085303377</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3753041371373999</v>
+        <v>0.3753041371373877</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3432668507634884</v>
+        <v>0.3432668507635022</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4319014846469423</v>
+        <v>0.4319014846469436</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4319014846469423</v>
+        <v>0.4319014846469437</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4319014846469423</v>
+        <v>0.4319014846469437</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3841263367991153</v>
+        <v>0.3841263367991285</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3897726363621651</v>
+        <v>0.3897726363621707</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4208286636938975</v>
+        <v>0.4208286636939046</v>
       </c>
       <c r="X7" t="n">
-        <v>0.338968761560604</v>
+        <v>0.3389687615606011</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5046445630991436</v>
+        <v>0.5046445630991816</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.3564486257920058</v>
+        <v>0.3564486257919711</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.4319014846469423</v>
+        <v>0.4319014846469436</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.5092111585680359</v>
+        <v>0.509211158568052</v>
       </c>
     </row>
     <row r="8">
@@ -5542,85 +5542,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5342874701218863</v>
+        <v>0.5342874701218898</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5342874701218863</v>
+        <v>0.5342874701218898</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5342874701218863</v>
+        <v>0.5342874701218898</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5342874701218863</v>
+        <v>0.5342874701218898</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5342874701218863</v>
+        <v>0.5342874701218898</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5342874701218863</v>
+        <v>0.5342874701218898</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5342874701218863</v>
+        <v>0.5342874701218898</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5342874701218863</v>
+        <v>0.5342874701218898</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5342874701218863</v>
+        <v>0.5342874701218898</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5342874701218863</v>
+        <v>0.5342874701218898</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5342874701218863</v>
+        <v>0.5342874701218898</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5342874701218863</v>
+        <v>0.5342874701218898</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5342874701218863</v>
+        <v>0.5342874701218898</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5342874701218863</v>
+        <v>0.5342874701218898</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5342874701218863</v>
+        <v>0.5342874701218898</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.5342874701218863</v>
+        <v>0.5342874701218898</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5342874701218863</v>
+        <v>0.5342874701218898</v>
       </c>
       <c r="S8" t="n">
-        <v>0.53503975044264</v>
+        <v>0.5350397504426398</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5342874701218863</v>
+        <v>0.5342874701218898</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5342874701218863</v>
+        <v>0.5342874701218898</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5342874701218863</v>
+        <v>0.5342874701218898</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5342874701218863</v>
+        <v>0.5342874701218898</v>
       </c>
       <c r="X8" t="n">
-        <v>0.5342874701218863</v>
+        <v>0.5342874701218898</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.5342874701218863</v>
+        <v>0.5342874701218898</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.5342874701218863</v>
+        <v>0.5342874701218898</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.5342874701218863</v>
+        <v>0.5342874701218898</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.5342874701218863</v>
+        <v>0.5342874701218898</v>
       </c>
     </row>
     <row r="9">
@@ -5630,85 +5630,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8454864501717655</v>
+        <v>0.8454864501717668</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9530937449253167</v>
+        <v>0.9530937449253185</v>
       </c>
       <c r="D9" t="n">
         <v>1.290573121897758</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5317426127506899</v>
+        <v>0.5317426127506896</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7617328036599516</v>
+        <v>0.7617328036599517</v>
       </c>
       <c r="G9" t="n">
-        <v>2.834407368644576</v>
+        <v>2.834407368644954</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4120640770498073</v>
+        <v>0.4120640770498093</v>
       </c>
       <c r="I9" t="n">
-        <v>3.431479780860442</v>
+        <v>3.431479780860444</v>
       </c>
       <c r="J9" t="n">
-        <v>1.895492136158562</v>
+        <v>1.89549213615867</v>
       </c>
       <c r="K9" t="n">
-        <v>1.572927481273561</v>
+        <v>1.572927481273564</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5469029185677727</v>
+        <v>0.546902918567769</v>
       </c>
       <c r="M9" t="n">
-        <v>2.547820557947884</v>
+        <v>2.547820557947881</v>
       </c>
       <c r="N9" t="n">
-        <v>1.122847183248976</v>
+        <v>1.122847183248972</v>
       </c>
       <c r="O9" t="n">
-        <v>1.226018023099173</v>
+        <v>1.22601802309917</v>
       </c>
       <c r="P9" t="n">
-        <v>1.479440188771395</v>
+        <v>1.479440188771393</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.496306008547192</v>
+        <v>2.496306008547194</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5744591682497769</v>
+        <v>0.5744591682497761</v>
       </c>
       <c r="S9" t="n">
-        <v>1.604999697249408</v>
+        <v>1.604999697249411</v>
       </c>
       <c r="T9" t="n">
-        <v>0.8015998612855844</v>
+        <v>0.8015998612855864</v>
       </c>
       <c r="U9" t="n">
-        <v>1.058481465543288</v>
+        <v>1.058481465543299</v>
       </c>
       <c r="V9" t="n">
-        <v>1.236048082686102</v>
+        <v>1.236048082686107</v>
       </c>
       <c r="W9" t="n">
-        <v>1.207275039469168</v>
+        <v>1.20727503946916</v>
       </c>
       <c r="X9" t="n">
-        <v>1.220283208481313</v>
+        <v>1.22028320848131</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.986804981687261</v>
+        <v>1.986804981687268</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.407976470909936</v>
+        <v>1.407976470909935</v>
       </c>
       <c r="AA9" t="n">
         <v>1.021046969400971</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.545288000407275</v>
+        <v>2.545288000407273</v>
       </c>
     </row>
     <row r="10">
@@ -5718,85 +5718,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5271716672034163</v>
+        <v>0.5271716672034217</v>
       </c>
       <c r="C10" t="n">
-        <v>0.745589143055843</v>
+        <v>0.7455891430558576</v>
       </c>
       <c r="D10" t="n">
-        <v>0.745589143055843</v>
+        <v>0.7455891430558576</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6292882802047686</v>
+        <v>0.6292882802047652</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5611985571782876</v>
+        <v>0.5611985571782988</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7908794294955189</v>
+        <v>0.7908794294955347</v>
       </c>
       <c r="H10" t="n">
-        <v>0.745589143055843</v>
+        <v>0.7455891430558576</v>
       </c>
       <c r="I10" t="n">
-        <v>0.745589143055843</v>
+        <v>0.7455891430558576</v>
       </c>
       <c r="J10" t="n">
-        <v>0.745589143055843</v>
+        <v>0.7455891430558576</v>
       </c>
       <c r="K10" t="n">
-        <v>0.745589143055843</v>
+        <v>0.7455891430558576</v>
       </c>
       <c r="L10" t="n">
-        <v>0.745589143055843</v>
+        <v>0.7455891430558576</v>
       </c>
       <c r="M10" t="n">
-        <v>0.745589143053112</v>
+        <v>0.7455891430531363</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5762790586818923</v>
+        <v>0.5762790586819053</v>
       </c>
       <c r="O10" t="n">
-        <v>0.622806939660612</v>
+        <v>0.6228069396606244</v>
       </c>
       <c r="P10" t="n">
-        <v>0.611401831796476</v>
+        <v>0.6114018317964922</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4842476482266334</v>
+        <v>0.484247648226645</v>
       </c>
       <c r="R10" t="n">
-        <v>0.745589143055843</v>
+        <v>0.7455891430558576</v>
       </c>
       <c r="S10" t="n">
-        <v>0.745589143055843</v>
+        <v>0.7455891430558576</v>
       </c>
       <c r="T10" t="n">
-        <v>0.745589143055843</v>
+        <v>0.7455891430558576</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6374143141215144</v>
+        <v>0.6374143141215157</v>
       </c>
       <c r="V10" t="n">
         <v>0.6841627034077795</v>
       </c>
       <c r="W10" t="n">
-        <v>0.7456320677707474</v>
+        <v>0.7456320677707551</v>
       </c>
       <c r="X10" t="n">
-        <v>0.5042660435344489</v>
+        <v>0.5042660435344476</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.9600739784778615</v>
+        <v>0.9600739784778627</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.5231144505082493</v>
+        <v>0.5231144505082518</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.745589143055843</v>
+        <v>0.7455891430558576</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9737444598046314</v>
+        <v>0.9737444598046496</v>
       </c>
     </row>
     <row r="11">
@@ -5806,85 +5806,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.303418126123008</v>
+        <v>1.303418126122981</v>
       </c>
       <c r="C11" t="n">
-        <v>1.303418126123008</v>
+        <v>1.303418126122981</v>
       </c>
       <c r="D11" t="n">
-        <v>1.303418126123008</v>
+        <v>1.303418126122981</v>
       </c>
       <c r="E11" t="n">
-        <v>1.303418126123008</v>
+        <v>1.303418126122981</v>
       </c>
       <c r="F11" t="n">
-        <v>1.303418126123008</v>
+        <v>1.303418126122981</v>
       </c>
       <c r="G11" t="n">
-        <v>1.303418126123008</v>
+        <v>1.303418126122981</v>
       </c>
       <c r="H11" t="n">
-        <v>1.303418126123008</v>
+        <v>1.303418126122981</v>
       </c>
       <c r="I11" t="n">
-        <v>1.303418126123008</v>
+        <v>1.303418126122981</v>
       </c>
       <c r="J11" t="n">
-        <v>1.280637469094548</v>
+        <v>1.280637469094544</v>
       </c>
       <c r="K11" t="n">
-        <v>1.303418126123008</v>
+        <v>1.303418126122981</v>
       </c>
       <c r="L11" t="n">
-        <v>1.303418126123008</v>
+        <v>1.303418126122981</v>
       </c>
       <c r="M11" t="n">
-        <v>1.303418126123008</v>
+        <v>1.303418126122981</v>
       </c>
       <c r="N11" t="n">
-        <v>1.303418126123008</v>
+        <v>1.303418126122981</v>
       </c>
       <c r="O11" t="n">
-        <v>1.303418126123008</v>
+        <v>1.303418126122981</v>
       </c>
       <c r="P11" t="n">
-        <v>1.303418126123008</v>
+        <v>1.303418126122981</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.303418126123008</v>
+        <v>1.303418126122981</v>
       </c>
       <c r="R11" t="n">
-        <v>1.303418126123008</v>
+        <v>1.303418126122981</v>
       </c>
       <c r="S11" t="n">
-        <v>1.303787891033892</v>
+        <v>1.3037878910339</v>
       </c>
       <c r="T11" t="n">
-        <v>1.303418126123008</v>
+        <v>1.303418126122981</v>
       </c>
       <c r="U11" t="n">
-        <v>1.303418126123008</v>
+        <v>1.303418126122981</v>
       </c>
       <c r="V11" t="n">
-        <v>1.151431611923769</v>
+        <v>1.151431611923734</v>
       </c>
       <c r="W11" t="n">
-        <v>1.303418126123008</v>
+        <v>1.303418126122981</v>
       </c>
       <c r="X11" t="n">
-        <v>1.303418126123008</v>
+        <v>1.303418126122981</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.303418126123008</v>
+        <v>1.303418126122981</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.303418126123008</v>
+        <v>1.303418126122981</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.303418126123008</v>
+        <v>1.303418126122981</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.303418126123008</v>
+        <v>1.303418126122981</v>
       </c>
     </row>
     <row r="12">
@@ -5894,85 +5894,85 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.45638033974658</v>
+        <v>1.456380339746586</v>
       </c>
       <c r="C12" t="n">
-        <v>1.509272061965309</v>
+        <v>1.509272061965307</v>
       </c>
       <c r="D12" t="n">
-        <v>1.675151759083023</v>
+        <v>1.675151759083013</v>
       </c>
       <c r="E12" t="n">
-        <v>1.302167264000019</v>
+        <v>1.302167264000001</v>
       </c>
       <c r="F12" t="n">
-        <v>1.415213292324238</v>
+        <v>1.415213292324253</v>
       </c>
       <c r="G12" t="n">
-        <v>2.433985556714675</v>
+        <v>2.433985556714699</v>
       </c>
       <c r="H12" t="n">
-        <v>1.243342219839846</v>
+        <v>1.24334221983983</v>
       </c>
       <c r="I12" t="n">
-        <v>2.727461833055388</v>
+        <v>2.727461833055369</v>
       </c>
       <c r="J12" t="n">
-        <v>1.949704182868411</v>
+        <v>1.949704182868383</v>
       </c>
       <c r="K12" t="n">
-        <v>1.813936108021024</v>
+        <v>1.81393610802102</v>
       </c>
       <c r="L12" t="n">
-        <v>1.309618939891181</v>
+        <v>1.309618939891169</v>
       </c>
       <c r="M12" t="n">
-        <v>2.293120850305574</v>
+        <v>2.293120850305554</v>
       </c>
       <c r="N12" t="n">
-        <v>1.592710194352638</v>
+        <v>1.592710194352625</v>
       </c>
       <c r="O12" t="n">
-        <v>1.643421286151078</v>
+        <v>1.643421286151076</v>
       </c>
       <c r="P12" t="n">
-        <v>1.767984726032201</v>
+        <v>1.767984726032181</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.267800139071589</v>
+        <v>2.267800139071583</v>
       </c>
       <c r="R12" t="n">
-        <v>1.323163537466166</v>
+        <v>1.323163537466163</v>
       </c>
       <c r="S12" t="n">
-        <v>1.829700417887011</v>
+        <v>1.829700417886983</v>
       </c>
       <c r="T12" t="n">
-        <v>1.434808965112455</v>
+        <v>1.434808965112444</v>
       </c>
       <c r="U12" t="n">
-        <v>1.561072807044503</v>
+        <v>1.561072807044539</v>
       </c>
       <c r="V12" t="n">
-        <v>1.496364801339945</v>
+        <v>1.496364801339954</v>
       </c>
       <c r="W12" t="n">
-        <v>1.634208632994265</v>
+        <v>1.634208632994254</v>
       </c>
       <c r="X12" t="n">
-        <v>1.640602478909075</v>
+        <v>1.640602478909061</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.01736742589401</v>
+        <v>2.017367425894011</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.732858491119372</v>
+        <v>1.732858491119369</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.542672800094309</v>
+        <v>1.542672800094313</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.291876033862158</v>
+        <v>2.291876033862145</v>
       </c>
     </row>
     <row r="13">
@@ -5982,85 +5982,85 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.299920528007666</v>
+        <v>1.299920528007646</v>
       </c>
       <c r="C13" t="n">
-        <v>1.407278272544955</v>
+        <v>1.407278272544939</v>
       </c>
       <c r="D13" t="n">
-        <v>1.407278272544955</v>
+        <v>1.407278272544939</v>
       </c>
       <c r="E13" t="n">
-        <v>1.350113440497041</v>
+        <v>1.350113440497047</v>
       </c>
       <c r="F13" t="n">
-        <v>1.316645609858667</v>
+        <v>1.316645609858666</v>
       </c>
       <c r="G13" t="n">
         <v>1.429539600227804</v>
       </c>
       <c r="H13" t="n">
-        <v>1.407278272544955</v>
+        <v>1.407278272544939</v>
       </c>
       <c r="I13" t="n">
-        <v>1.407278272544955</v>
+        <v>1.407278272544939</v>
       </c>
       <c r="J13" t="n">
-        <v>1.38449761551654</v>
+        <v>1.384497615516521</v>
       </c>
       <c r="K13" t="n">
-        <v>1.407278272544955</v>
+        <v>1.407278272544939</v>
       </c>
       <c r="L13" t="n">
-        <v>1.407278272544955</v>
+        <v>1.407278272544939</v>
       </c>
       <c r="M13" t="n">
-        <v>1.407278272543624</v>
+        <v>1.407278272543604</v>
       </c>
       <c r="N13" t="n">
-        <v>1.324058059900035</v>
+        <v>1.32405805990002</v>
       </c>
       <c r="O13" t="n">
-        <v>1.346927696775388</v>
+        <v>1.346927696775374</v>
       </c>
       <c r="P13" t="n">
-        <v>1.341321796186518</v>
+        <v>1.341321796186522</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.278822280965677</v>
+        <v>1.278822280965669</v>
       </c>
       <c r="R13" t="n">
-        <v>1.407278272544955</v>
+        <v>1.407278272544939</v>
       </c>
       <c r="S13" t="n">
-        <v>1.407278272544955</v>
+        <v>1.407278272544939</v>
       </c>
       <c r="T13" t="n">
-        <v>1.407278272544955</v>
+        <v>1.407278272544939</v>
       </c>
       <c r="U13" t="n">
-        <v>1.354107592841892</v>
+        <v>1.354107592841904</v>
       </c>
       <c r="V13" t="n">
-        <v>1.225099100959509</v>
+        <v>1.225099100959485</v>
       </c>
       <c r="W13" t="n">
-        <v>1.407299371134074</v>
+        <v>1.407299371134054</v>
       </c>
       <c r="X13" t="n">
-        <v>1.288661831400511</v>
+        <v>1.288661831400497</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.512703024289264</v>
+        <v>1.512703024289282</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.297926302812108</v>
+        <v>1.297926302812101</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.407278272544955</v>
+        <v>1.407278272544939</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.51942241355176</v>
+        <v>1.519422413551768</v>
       </c>
     </row>
     <row r="14">
@@ -6070,85 +6070,85 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3654127049510483</v>
+        <v>0.3654127049510555</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3654127049510483</v>
+        <v>0.3654127049510555</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3654127049510483</v>
+        <v>0.3654127049510555</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3654127049510483</v>
+        <v>0.3654127049510555</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3654127049510483</v>
+        <v>0.3654127049510555</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3558789715838002</v>
+        <v>0.3558789715838009</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3654127049510483</v>
+        <v>0.3654127049510555</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3654127049510483</v>
+        <v>0.3654127049510555</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3562211493551672</v>
+        <v>0.3562211493551701</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3654127049510483</v>
+        <v>0.3654127049510555</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3654127049510483</v>
+        <v>0.3654127049510555</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3654127049510483</v>
+        <v>0.3654127049510555</v>
       </c>
       <c r="N14" t="n">
-        <v>0.3654127049510483</v>
+        <v>0.3654127049510555</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3558789715838002</v>
+        <v>0.3558789715838009</v>
       </c>
       <c r="P14" t="n">
-        <v>0.3558789715838002</v>
+        <v>0.3558789715838009</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.3654127049510483</v>
+        <v>0.3654127049510555</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3654127049510483</v>
+        <v>0.3654127049510555</v>
       </c>
       <c r="S14" t="n">
-        <v>0.365782469861944</v>
+        <v>0.3657824698619451</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3654127049510483</v>
+        <v>0.3654127049510555</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3558789715838</v>
+        <v>0.3558789715838011</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3563679215279053</v>
+        <v>0.3563679215279017</v>
       </c>
       <c r="W14" t="n">
-        <v>0.3558789715838002</v>
+        <v>0.3558789715838009</v>
       </c>
       <c r="X14" t="n">
-        <v>0.3558789715838002</v>
+        <v>0.3558789715838009</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.3654127049510483</v>
+        <v>0.3654127049510555</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.3654127049510483</v>
+        <v>0.3654127049510555</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.3654127049510483</v>
+        <v>0.3654127049510555</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.3654127049510483</v>
+        <v>0.3654127049510555</v>
       </c>
     </row>
     <row r="15">
@@ -6158,82 +6158,82 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5183749185746415</v>
+        <v>0.5183749185746421</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5712666407933659</v>
+        <v>0.5712666407933675</v>
       </c>
       <c r="D15" t="n">
-        <v>0.737146337911074</v>
+        <v>0.7371463379110714</v>
       </c>
       <c r="E15" t="n">
-        <v>0.3641618428280721</v>
+        <v>0.3641618428280723</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4772078711523114</v>
+        <v>0.4772078711523091</v>
       </c>
       <c r="G15" t="n">
-        <v>1.486446402175577</v>
+        <v>1.4864464021755</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3053367986678934</v>
+        <v>0.305336798667896</v>
       </c>
       <c r="I15" t="n">
-        <v>1.789456411883432</v>
+        <v>1.789456411883434</v>
       </c>
       <c r="J15" t="n">
-        <v>1.025287863128988</v>
+        <v>1.025287863129006</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8759306868490762</v>
+        <v>0.875930686849077</v>
       </c>
       <c r="L15" t="n">
-        <v>0.3716135187192319</v>
+        <v>0.3716135187192302</v>
       </c>
       <c r="M15" t="n">
-        <v>1.355115429133623</v>
+        <v>1.355115429133621</v>
       </c>
       <c r="N15" t="n">
-        <v>0.6547047731806913</v>
+        <v>0.6547047731806885</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6958821316118785</v>
+        <v>0.6958821316118784</v>
       </c>
       <c r="P15" t="n">
-        <v>0.8204455714929911</v>
+        <v>0.8204455714929907</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.329794717899646</v>
+        <v>1.329794717899645</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3851581162942249</v>
+        <v>0.3851581162942246</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8916949967150479</v>
+        <v>0.8916949967150448</v>
       </c>
       <c r="T15" t="n">
-        <v>0.4968035439405006</v>
+        <v>0.4968035439405</v>
       </c>
       <c r="U15" t="n">
-        <v>0.6135336525053063</v>
+        <v>0.6135336525052933</v>
       </c>
       <c r="V15" t="n">
-        <v>0.70130111094408</v>
+        <v>0.7013011109440777</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6866694784550555</v>
+        <v>0.6866694784550553</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6930633243698742</v>
+        <v>0.6930633243698753</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.079362004722068</v>
+        <v>1.079362004722069</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.7948530699474317</v>
+        <v>0.7948530699474303</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.6046673789223652</v>
+        <v>0.6046673789223624</v>
       </c>
       <c r="AB15" t="n">
         <v>1.353870612690204</v>
@@ -6246,85 +6246,85 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3619151068357091</v>
+        <v>0.361915106835715</v>
       </c>
       <c r="C16" t="n">
-        <v>0.4692728513730202</v>
+        <v>0.4692728513730209</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4692728513730202</v>
+        <v>0.4692728513730209</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4121080193250934</v>
+        <v>0.4121080193250976</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3786401886867137</v>
+        <v>0.3786401886867195</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4820004456886158</v>
+        <v>0.4820004456886186</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4692728513730202</v>
+        <v>0.4692728513730209</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4692728513730202</v>
+        <v>0.4692728513730209</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4600812957771291</v>
+        <v>0.4600812957771369</v>
       </c>
       <c r="K16" t="n">
-        <v>0.4692728513730202</v>
+        <v>0.4692728513730209</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4692728513730202</v>
+        <v>0.4692728513730209</v>
       </c>
       <c r="M16" t="n">
-        <v>0.469272851371682</v>
+        <v>0.4692728513716841</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3860526387280928</v>
+        <v>0.3860526387280905</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3993885422361907</v>
+        <v>0.3993885422361869</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3937826416473218</v>
+        <v>0.3937826416473288</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.3408168597937193</v>
+        <v>0.3408168597937229</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4692728513730202</v>
+        <v>0.4692728513730209</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4692728513730202</v>
+        <v>0.4692728513730209</v>
       </c>
       <c r="T16" t="n">
-        <v>0.4692728513730202</v>
+        <v>0.4692728513730209</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4065684383027068</v>
+        <v>0.4065684383027114</v>
       </c>
       <c r="V16" t="n">
-        <v>0.4300354105636527</v>
+        <v>0.430035410563652</v>
       </c>
       <c r="W16" t="n">
-        <v>0.4597602165948592</v>
+        <v>0.4597602165948714</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3411226768613076</v>
+        <v>0.3411226768613139</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.5746976031173047</v>
+        <v>0.5746976031173303</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.3599208816401676</v>
+        <v>0.3599208816401679</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.4692728513730202</v>
+        <v>0.4692728513730209</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.5814169923798064</v>
+        <v>0.581416992379821</v>
       </c>
     </row>
   </sheetData>
@@ -6490,85 +6490,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.937780675385496</v>
+        <v>0.9377806753854807</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6025667624275916</v>
+        <v>0.6025667624275797</v>
       </c>
       <c r="D2" t="n">
-        <v>1.150491186830835</v>
+        <v>1.150491186830338</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2176138411876628</v>
+        <v>0.217613841187654</v>
       </c>
       <c r="F2" t="n">
-        <v>1.24458296444948</v>
+        <v>1.244582964449369</v>
       </c>
       <c r="G2" t="n">
-        <v>2.631035950427076</v>
+        <v>2.631035950426341</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5435020159194598</v>
+        <v>0.5435020159194476</v>
       </c>
       <c r="I2" t="n">
-        <v>2.377285901110068</v>
+        <v>2.377285901110043</v>
       </c>
       <c r="J2" t="n">
-        <v>1.833141522639072</v>
+        <v>1.833141522638863</v>
       </c>
       <c r="K2" t="n">
-        <v>1.660758509663417</v>
+        <v>1.660758509663316</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8515296264493508</v>
+        <v>0.8515296264493293</v>
       </c>
       <c r="M2" t="n">
-        <v>2.304514663899825</v>
+        <v>2.30451466389976</v>
       </c>
       <c r="N2" t="n">
-        <v>1.108831063712171</v>
+        <v>1.108831063712155</v>
       </c>
       <c r="O2" t="n">
-        <v>1.162525675398547</v>
+        <v>1.162525675398573</v>
       </c>
       <c r="P2" t="n">
-        <v>1.517808593755076</v>
+        <v>1.517808593755529</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.729564450293848</v>
+        <v>1.729564450293821</v>
       </c>
       <c r="R2" t="n">
-        <v>1.726169877853717</v>
+        <v>1.72616987785369</v>
       </c>
       <c r="S2" t="n">
-        <v>1.713414586524871</v>
+        <v>1.713414586525066</v>
       </c>
       <c r="T2" t="n">
-        <v>1.342384772194927</v>
+        <v>1.342384772194909</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9519149827461272</v>
+        <v>0.9519149827460371</v>
       </c>
       <c r="V2" t="n">
-        <v>1.386673859876687</v>
+        <v>1.38667385987649</v>
       </c>
       <c r="W2" t="n">
-        <v>1.317321763023267</v>
+        <v>1.317321763023251</v>
       </c>
       <c r="X2" t="n">
-        <v>1.510699955561424</v>
+        <v>1.510699955561457</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.910725093362953</v>
+        <v>2.910725093362669</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.479355676674974</v>
+        <v>1.479355676674954</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.186533448533138</v>
+        <v>1.186533448533128</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.458699894500576</v>
+        <v>2.458699894500541</v>
       </c>
     </row>
     <row r="3">
@@ -6578,85 +6578,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6001640262567449</v>
+        <v>0.6001640262567088</v>
       </c>
       <c r="C3" t="n">
-        <v>0.828682529512241</v>
+        <v>0.8286825295122204</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8191357654275898</v>
+        <v>0.8191357654275568</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6919850911930594</v>
+        <v>0.6919850911930397</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6288166289178296</v>
+        <v>0.628816628917824</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8645409819666722</v>
+        <v>0.8645409819666673</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8191357654275898</v>
+        <v>0.8191357654275568</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8191357654275898</v>
+        <v>0.8191357654275568</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8144672154481382</v>
+        <v>0.814467215448122</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8191357654275898</v>
+        <v>0.8191357654275568</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8191357654275898</v>
+        <v>0.8191357654275568</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8240413354090371</v>
+        <v>0.8240413354090192</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6493960342245443</v>
+        <v>0.6493960342245023</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6960419858196966</v>
+        <v>0.6960419858196741</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6846079360017017</v>
+        <v>0.6846079360016847</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.55713108192273</v>
+        <v>0.5571310819227184</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8191357654275898</v>
+        <v>0.8191357654275568</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8191357654275898</v>
+        <v>0.8191357654275568</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8191357654275898</v>
+        <v>0.8191357654275568</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7127427773417998</v>
+        <v>0.7127427773417789</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7483594279251569</v>
+        <v>0.7483594279251353</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8191787989498205</v>
+        <v>0.8191787989498029</v>
       </c>
       <c r="X3" t="n">
-        <v>0.5772002764899258</v>
+        <v>0.5772002764899047</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.037682699209582</v>
+        <v>1.037682699209559</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.5960965138485348</v>
+        <v>0.5960965138485342</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.8191357654275898</v>
+        <v>0.8191357654275568</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.04720873659808</v>
+        <v>1.047208736598049</v>
       </c>
     </row>
     <row r="4">
@@ -6666,85 +6666,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.662449810082086</v>
+        <v>1.662449810082159</v>
       </c>
       <c r="C4" t="n">
-        <v>1.546335355769</v>
+        <v>1.546335355768907</v>
       </c>
       <c r="D4" t="n">
-        <v>1.739980293730983</v>
+        <v>1.739980293730808</v>
       </c>
       <c r="E4" t="n">
-        <v>1.393249830949239</v>
+        <v>1.393249830949227</v>
       </c>
       <c r="F4" t="n">
-        <v>1.770805344096456</v>
+        <v>1.770805344096311</v>
       </c>
       <c r="G4" t="n">
-        <v>2.27962147462734</v>
+        <v>2.279621474627095</v>
       </c>
       <c r="H4" t="n">
-        <v>1.518739868560509</v>
+        <v>1.518739868560393</v>
       </c>
       <c r="I4" t="n">
-        <v>2.187132561334939</v>
+        <v>2.187132561334878</v>
       </c>
       <c r="J4" t="n">
-        <v>1.955521256259846</v>
+        <v>1.955521256259769</v>
       </c>
       <c r="K4" t="n">
-        <v>1.925966741042027</v>
+        <v>1.925966741041897</v>
       </c>
       <c r="L4" t="n">
-        <v>1.631012315555843</v>
+        <v>1.631012315555744</v>
       </c>
       <c r="M4" t="n">
-        <v>2.163725847223801</v>
+        <v>2.163725847223755</v>
       </c>
       <c r="N4" t="n">
-        <v>1.724795668052103</v>
+        <v>1.724795668052038</v>
       </c>
       <c r="O4" t="n">
-        <v>1.744366723497822</v>
+        <v>1.744366723497827</v>
       </c>
       <c r="P4" t="n">
-        <v>1.873863175296082</v>
+        <v>1.873863175295873</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.951045698441691</v>
+        <v>1.951045698441623</v>
       </c>
       <c r="R4" t="n">
-        <v>1.949808416648366</v>
+        <v>1.949808416648277</v>
       </c>
       <c r="S4" t="n">
-        <v>1.94515926273919</v>
+        <v>1.945159262739167</v>
       </c>
       <c r="T4" t="n">
-        <v>1.809923252267921</v>
+        <v>1.80992325226788</v>
       </c>
       <c r="U4" t="n">
-        <v>1.667601599141629</v>
+        <v>1.667601599141547</v>
       </c>
       <c r="V4" t="n">
-        <v>1.616560267921864</v>
+        <v>1.616560267921705</v>
       </c>
       <c r="W4" t="n">
-        <v>1.800788079729605</v>
+        <v>1.800788079729588</v>
       </c>
       <c r="X4" t="n">
-        <v>1.871272160148381</v>
+        <v>1.8712721601483</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.381564882951851</v>
+        <v>2.381564882951726</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.859847538557361</v>
+        <v>1.859847538557337</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.75311727489186</v>
+        <v>1.753117274891804</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.216386729388056</v>
+        <v>2.216386729388078</v>
       </c>
     </row>
     <row r="5">
@@ -6754,85 +6754,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.539392505969525</v>
+        <v>1.539392505969427</v>
       </c>
       <c r="C5" t="n">
-        <v>1.628751897685998</v>
+        <v>1.6287518976859</v>
       </c>
       <c r="D5" t="n">
-        <v>1.619205133601325</v>
+        <v>1.619205133601356</v>
       </c>
       <c r="E5" t="n">
-        <v>1.566152581227783</v>
+        <v>1.56615258122768</v>
       </c>
       <c r="F5" t="n">
-        <v>1.546365745488532</v>
+        <v>1.546365745488508</v>
       </c>
       <c r="G5" t="n">
-        <v>1.635754801854826</v>
+        <v>1.635754801854691</v>
       </c>
       <c r="H5" t="n">
-        <v>1.619205133601325</v>
+        <v>1.619205133601356</v>
       </c>
       <c r="I5" t="n">
-        <v>1.619205133601325</v>
+        <v>1.619205133601356</v>
       </c>
       <c r="J5" t="n">
-        <v>1.584226433166414</v>
+        <v>1.584226433166434</v>
       </c>
       <c r="K5" t="n">
-        <v>1.619205133601325</v>
+        <v>1.619205133601356</v>
       </c>
       <c r="L5" t="n">
-        <v>1.619205133601325</v>
+        <v>1.619205133601356</v>
       </c>
       <c r="M5" t="n">
-        <v>1.624110703584434</v>
+        <v>1.624110703584296</v>
       </c>
       <c r="N5" t="n">
-        <v>1.557336994762346</v>
+        <v>1.557336994762328</v>
       </c>
       <c r="O5" t="n">
-        <v>1.574338896374401</v>
+        <v>1.57433889637433</v>
       </c>
       <c r="P5" t="n">
-        <v>1.57017131948111</v>
+        <v>1.570171319481104</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.523707503078123</v>
+        <v>1.523707503078054</v>
       </c>
       <c r="R5" t="n">
-        <v>1.619205133601325</v>
+        <v>1.619205133601356</v>
       </c>
       <c r="S5" t="n">
-        <v>1.619205133601325</v>
+        <v>1.619205133601356</v>
       </c>
       <c r="T5" t="n">
-        <v>1.619205133601325</v>
+        <v>1.619205133601356</v>
       </c>
       <c r="U5" t="n">
-        <v>1.580426138773583</v>
+        <v>1.580426138773503</v>
       </c>
       <c r="V5" t="n">
-        <v>1.383902152942013</v>
+        <v>1.383902152941944</v>
       </c>
       <c r="W5" t="n">
-        <v>1.619220818814832</v>
+        <v>1.619220818814736</v>
       </c>
       <c r="X5" t="n">
-        <v>1.531022488833462</v>
+        <v>1.531022488833314</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.698862924657158</v>
+        <v>1.698862924657023</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.537909945459869</v>
+        <v>1.537909945459866</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.619205133601325</v>
+        <v>1.619205133601356</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.701914776898575</v>
+        <v>1.701914776898497</v>
       </c>
     </row>
     <row r="6">
@@ -6842,85 +6842,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5167402180388925</v>
+        <v>0.516740218038882</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4006257637257945</v>
+        <v>0.4006257637257886</v>
       </c>
       <c r="D6" t="n">
-        <v>0.594270701687785</v>
+        <v>0.5942707016878358</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2475402389060549</v>
+        <v>0.247540238906045</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6250957520532303</v>
+        <v>0.6250957520531586</v>
       </c>
       <c r="G6" t="n">
-        <v>1.121378760948449</v>
+        <v>1.121378760948262</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3730302765172941</v>
+        <v>0.3730302765172813</v>
       </c>
       <c r="I6" t="n">
-        <v>1.041422969291717</v>
+        <v>1.041422969291692</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8280581303952157</v>
+        <v>0.82805813039515</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7802571489988347</v>
+        <v>0.7802571489987937</v>
       </c>
       <c r="L6" t="n">
-        <v>0.485302723512617</v>
+        <v>0.4853027235125961</v>
       </c>
       <c r="M6" t="n">
-        <v>1.018016255180598</v>
+        <v>1.018016255180503</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5790860760088982</v>
+        <v>0.5790860760088795</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5861240098189258</v>
+        <v>0.5861240098189424</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7156204616172196</v>
+        <v>0.7156204616170688</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.8053361063984861</v>
+        <v>0.8053361063984663</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8040988246051413</v>
+        <v>0.8040988246051233</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7994496706959684</v>
+        <v>0.7994496706959993</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6642136602247501</v>
+        <v>0.6642136602247303</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5093588854627344</v>
+        <v>0.5093588854626812</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6612310180463239</v>
+        <v>0.6612310180463086</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6425453660507027</v>
+        <v>0.6425453660507138</v>
       </c>
       <c r="X6" t="n">
-        <v>0.7130294464694794</v>
+        <v>0.7130294464692647</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.235855290908641</v>
+        <v>1.235855290908453</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.7141379465141651</v>
+        <v>0.7141379465141465</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.607407682848671</v>
+        <v>0.6074076828486699</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.07067713734484</v>
+        <v>1.070677137344824</v>
       </c>
     </row>
     <row r="7">
@@ -6930,85 +6930,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.393682913926315</v>
+        <v>0.3936829139263083</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4830423056427572</v>
+        <v>0.483042305642752</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4734955415581076</v>
+        <v>0.4734955415580999</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4204429891845697</v>
+        <v>0.4204429891845601</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4006561534453192</v>
+        <v>0.4006561534453122</v>
       </c>
       <c r="G7" t="n">
-        <v>0.477512088175942</v>
+        <v>0.4775120881759237</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4734955415581076</v>
+        <v>0.4734955415580999</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4734955415581076</v>
+        <v>0.4734955415580999</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4567633073017726</v>
+        <v>0.4567633073017653</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4734955415581076</v>
+        <v>0.4734955415580999</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4734955415581076</v>
+        <v>0.4734955415580999</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4784011115412423</v>
+        <v>0.4784011115412335</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4116274027191512</v>
+        <v>0.4116274027191189</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4160961826954762</v>
+        <v>0.4160961826954557</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4119286058022072</v>
+        <v>0.4119286058021894</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3779979110349127</v>
+        <v>0.3779979110348999</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4734955415581076</v>
+        <v>0.4734955415580999</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4734955415581076</v>
+        <v>0.4734955415580999</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4734955415581076</v>
+        <v>0.4734955415580999</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4221834250946835</v>
+        <v>0.4221834250946724</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4285729030664808</v>
+        <v>0.4285729030664682</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4609781051359444</v>
+        <v>0.4609781051359437</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3727797751545801</v>
+        <v>0.37277977515455</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5531533326139767</v>
+        <v>0.5531533326139664</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.3922003534166642</v>
+        <v>0.3922003534166351</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.4734955415581076</v>
+        <v>0.4734955415580999</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.556205184855374</v>
+        <v>0.5562051848553582</v>
       </c>
     </row>
     <row r="8">
@@ -7018,85 +7018,85 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.5662228108408534</v>
+        <v>0.566222810840829</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5662228108408534</v>
+        <v>0.566222810840829</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5662228108408534</v>
+        <v>0.566222810840829</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5662228108408534</v>
+        <v>0.566222810840829</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5662228108408534</v>
+        <v>0.566222810840829</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5662228108408534</v>
+        <v>0.566222810840829</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5662228108408534</v>
+        <v>0.566222810840829</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5662228108408534</v>
+        <v>0.566222810840829</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5662228108408534</v>
+        <v>0.566222810840829</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5662228108408534</v>
+        <v>0.566222810840829</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5662228108408534</v>
+        <v>0.5662228108408406</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5662228108408534</v>
+        <v>0.566222810840829</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5662228108408534</v>
+        <v>0.566222810840829</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5662228108408534</v>
+        <v>0.566222810840829</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5662228108408534</v>
+        <v>0.566222810840829</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.5662228108408534</v>
+        <v>0.566222810840829</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5662228108408534</v>
+        <v>0.566222810840829</v>
       </c>
       <c r="S8" t="n">
-        <v>0.578216762937192</v>
+        <v>0.5782167629371818</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5662228108408534</v>
+        <v>0.566222810840829</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5662228108408534</v>
+        <v>0.566222810840829</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5662228108408534</v>
+        <v>0.566222810840829</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5662228108408534</v>
+        <v>0.566222810840829</v>
       </c>
       <c r="X8" t="n">
-        <v>0.5662228108408534</v>
+        <v>0.566222810840829</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.5662228108408534</v>
+        <v>0.566222810840829</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.5662228108408534</v>
+        <v>0.566222810840829</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.5662228108408534</v>
+        <v>0.566222810840829</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.5662228108408534</v>
+        <v>0.566222810840829</v>
       </c>
     </row>
     <row r="9">
@@ -7106,85 +7106,85 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.9329753142604342</v>
+        <v>0.9329753142604266</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5624599838613745</v>
+        <v>0.5624599838613634</v>
       </c>
       <c r="D9" t="n">
-        <v>1.161575936882475</v>
+        <v>1.161575936882347</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1703530132427537</v>
+        <v>0.1703530132427414</v>
       </c>
       <c r="F9" t="n">
-        <v>1.268565212421886</v>
+        <v>1.268565212421642</v>
       </c>
       <c r="G9" t="n">
-        <v>2.752721820920334</v>
+        <v>2.752721820919778</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5092428600997033</v>
+        <v>0.5092428600996992</v>
       </c>
       <c r="I9" t="n">
-        <v>2.480015884245967</v>
+        <v>2.480015884245942</v>
       </c>
       <c r="J9" t="n">
-        <v>1.900239598416259</v>
+        <v>1.900239598416101</v>
       </c>
       <c r="K9" t="n">
-        <v>1.709961754351502</v>
+        <v>1.709961754351423</v>
       </c>
       <c r="L9" t="n">
-        <v>0.8402810540913771</v>
+        <v>0.8402810540913735</v>
       </c>
       <c r="M9" t="n">
-        <v>2.396536387312493</v>
+        <v>2.396536387312354</v>
       </c>
       <c r="N9" t="n">
-        <v>1.116803678009484</v>
+        <v>1.116803678009474</v>
       </c>
       <c r="O9" t="n">
-        <v>1.174509437727468</v>
+        <v>1.174509437727438</v>
       </c>
       <c r="P9" t="n">
-        <v>1.556333052326528</v>
+        <v>1.556333052326963</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.783907704466208</v>
+        <v>1.783907704466195</v>
       </c>
       <c r="R9" t="n">
-        <v>1.780259547315547</v>
+        <v>1.780259547315535</v>
       </c>
       <c r="S9" t="n">
-        <v>1.766551397588078</v>
+        <v>1.766551397587959</v>
       </c>
       <c r="T9" t="n">
-        <v>1.367804546805577</v>
+        <v>1.367804546805586</v>
       </c>
       <c r="U9" t="n">
-        <v>0.9481654966403111</v>
+        <v>0.9481654966401787</v>
       </c>
       <c r="V9" t="n">
-        <v>1.427720528539467</v>
+        <v>1.427720528539261</v>
       </c>
       <c r="W9" t="n">
-        <v>1.340869255914253</v>
+        <v>1.340869255914249</v>
       </c>
       <c r="X9" t="n">
-        <v>1.548693377606078</v>
+        <v>1.548693377606016</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.053304579061329</v>
+        <v>3.053304579060729</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.515007587372235</v>
+        <v>1.515007587372234</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.200310663294758</v>
+        <v>1.20031066329473</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.568222468771435</v>
+        <v>2.568222468771395</v>
       </c>
     </row>
     <row r="10">
@@ -7194,85 +7194,85 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.5701376920198847</v>
+        <v>0.5701376920198679</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8054672747986278</v>
+        <v>0.80546727479861</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8054672747986278</v>
+        <v>0.80546727479861</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6801612139206655</v>
+        <v>0.6801612139206572</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6067992905793377</v>
+        <v>0.6067992905793292</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8542643967677979</v>
+        <v>0.8542643967677818</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8054672747986278</v>
+        <v>0.80546727479861</v>
       </c>
       <c r="I10" t="n">
-        <v>0.8054672747986278</v>
+        <v>0.80546727479861</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8054672747986278</v>
+        <v>0.80546727479861</v>
       </c>
       <c r="K10" t="n">
-        <v>0.8054672747986278</v>
+        <v>0.80546727479861</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8054672747986278</v>
+        <v>0.80546727479861</v>
       </c>
       <c r="M10" t="n">
-        <v>0.8054672747957718</v>
+        <v>0.8054672747957676</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6230474781790113</v>
+        <v>0.6230474781789855</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6731780218225487</v>
+        <v>0.6731780218225319</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6608898142970938</v>
+        <v>0.6608898142970719</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.5238900580822302</v>
+        <v>0.5238900580822227</v>
       </c>
       <c r="R10" t="n">
-        <v>0.8054672747986278</v>
+        <v>0.80546727479861</v>
       </c>
       <c r="S10" t="n">
-        <v>0.8054672747986278</v>
+        <v>0.80546727479861</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8054672747986278</v>
+        <v>0.80546727479861</v>
       </c>
       <c r="U10" t="n">
-        <v>0.6911264124041552</v>
+        <v>0.6911264124041354</v>
       </c>
       <c r="V10" t="n">
-        <v>0.7417221000591354</v>
+        <v>0.741722100059113</v>
       </c>
       <c r="W10" t="n">
-        <v>0.8055135230536348</v>
+        <v>0.8055135230536135</v>
       </c>
       <c r="X10" t="n">
-        <v>0.5454584814874037</v>
+        <v>0.5454584814873857</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.040340317955873</v>
+        <v>1.040340317955835</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.5657663242735436</v>
+        <v>0.5657663242735249</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.8054672747986278</v>
+        <v>0.80546727479861</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.051288701232044</v>
+        <v>1.051288701232015</v>
       </c>
     </row>
     <row r="11">
@@ -7282,85 +7282,85 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1.37583026000696</v>
+        <v>1.375830260006785</v>
       </c>
       <c r="C11" t="n">
-        <v>1.37583026000696</v>
+        <v>1.375830260006785</v>
       </c>
       <c r="D11" t="n">
-        <v>1.37583026000696</v>
+        <v>1.375830260006785</v>
       </c>
       <c r="E11" t="n">
-        <v>1.37583026000696</v>
+        <v>1.375830260006785</v>
       </c>
       <c r="F11" t="n">
-        <v>1.37583026000696</v>
+        <v>1.375830260006785</v>
       </c>
       <c r="G11" t="n">
-        <v>1.37583026000696</v>
+        <v>1.375830260006785</v>
       </c>
       <c r="H11" t="n">
-        <v>1.37583026000696</v>
+        <v>1.375830260006785</v>
       </c>
       <c r="I11" t="n">
-        <v>1.37583026000696</v>
+        <v>1.375830260006785</v>
       </c>
       <c r="J11" t="n">
-        <v>1.349767366689444</v>
+        <v>1.349767366689325</v>
       </c>
       <c r="K11" t="n">
-        <v>1.37583026000696</v>
+        <v>1.375830260006785</v>
       </c>
       <c r="L11" t="n">
-        <v>1.37583026000696</v>
+        <v>1.375830260006758</v>
       </c>
       <c r="M11" t="n">
-        <v>1.37583026000696</v>
+        <v>1.375830260006785</v>
       </c>
       <c r="N11" t="n">
-        <v>1.37583026000696</v>
+        <v>1.375830260006785</v>
       </c>
       <c r="O11" t="n">
-        <v>1.37583026000696</v>
+        <v>1.375830260006785</v>
       </c>
       <c r="P11" t="n">
-        <v>1.37583026000696</v>
+        <v>1.375830260006785</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.37583026000696</v>
+        <v>1.375830260006785</v>
       </c>
       <c r="R11" t="n">
-        <v>1.37583026000696</v>
+        <v>1.375830260006785</v>
       </c>
       <c r="S11" t="n">
-        <v>1.381725592512396</v>
+        <v>1.381725592512328</v>
       </c>
       <c r="T11" t="n">
-        <v>1.37583026000696</v>
+        <v>1.375830260006785</v>
       </c>
       <c r="U11" t="n">
-        <v>1.37583026000696</v>
+        <v>1.375830260006785</v>
       </c>
       <c r="V11" t="n">
-        <v>1.201945508059159</v>
+        <v>1.201945508059101</v>
       </c>
       <c r="W11" t="n">
-        <v>1.37583026000696</v>
+        <v>1.375830260006785</v>
       </c>
       <c r="X11" t="n">
-        <v>1.37583026000696</v>
+        <v>1.375830260006785</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.37583026000696</v>
+        <v>1.375830260006785</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.37583026000696</v>
+        <v>1.375830260006785</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.37583026000696</v>
+        <v>1.375830260006785</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.37583026000696</v>
+        <v>1.375830260006785</v>
       </c>
     </row>
     <row r="12">
@@ -7370,85 +7370,85 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.556098443296216</v>
+        <v>1.556098443296117</v>
       </c>
       <c r="C12" t="n">
-        <v>1.373980734844109</v>
+        <v>1.373980734844016</v>
       </c>
       <c r="D12" t="n">
-        <v>1.668461463465459</v>
+        <v>1.668461463465487</v>
       </c>
       <c r="E12" t="n">
-        <v>1.181250186069627</v>
+        <v>1.181250186069539</v>
       </c>
       <c r="F12" t="n">
-        <v>1.721049413521926</v>
+        <v>1.721049413521637</v>
       </c>
       <c r="G12" t="n">
-        <v>2.45055013413363</v>
+        <v>2.450550134133122</v>
       </c>
       <c r="H12" t="n">
-        <v>1.347823165009004</v>
+        <v>1.347823165008997</v>
       </c>
       <c r="I12" t="n">
-        <v>2.316508230348024</v>
+        <v>2.316508230347937</v>
       </c>
       <c r="J12" t="n">
-        <v>2.005470546712249</v>
+        <v>2.005470546712103</v>
       </c>
       <c r="K12" t="n">
-        <v>1.938007040209911</v>
+        <v>1.938007040209871</v>
       </c>
       <c r="L12" t="n">
-        <v>1.510536856868763</v>
+        <v>1.510536856868703</v>
       </c>
       <c r="M12" t="n">
-        <v>2.275475934416062</v>
+        <v>2.275475934415848</v>
       </c>
       <c r="N12" t="n">
-        <v>1.646454759506954</v>
+        <v>1.646454759506767</v>
       </c>
       <c r="O12" t="n">
-        <v>1.674818608077046</v>
+        <v>1.674818608076854</v>
       </c>
       <c r="P12" t="n">
-        <v>1.862494625824456</v>
+        <v>1.862494625824545</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.974353355407473</v>
+        <v>1.97435335540733</v>
       </c>
       <c r="R12" t="n">
-        <v>1.972560193381916</v>
+        <v>1.972560193381956</v>
       </c>
       <c r="S12" t="n">
-        <v>1.965822289142464</v>
+        <v>1.965822289142354</v>
       </c>
       <c r="T12" t="n">
-        <v>1.769828070390985</v>
+        <v>1.769828070390866</v>
       </c>
       <c r="U12" t="n">
-        <v>1.563564804277815</v>
+        <v>1.563564804277606</v>
       </c>
       <c r="V12" t="n">
-        <v>1.625393547348186</v>
+        <v>1.625393547348221</v>
       </c>
       <c r="W12" t="n">
-        <v>1.756588689854886</v>
+        <v>1.756588689854836</v>
       </c>
       <c r="X12" t="n">
-        <v>1.858739531394488</v>
+        <v>1.858739531394073</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.598294204679584</v>
+        <v>2.598294204679197</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.842182108741615</v>
+        <v>1.842182108741418</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.68750056666296</v>
+        <v>1.687500566663029</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.3598640100586</v>
+        <v>2.359864010058387</v>
       </c>
     </row>
     <row r="13">
@@ -7458,85 +7458,85 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.377754523676216</v>
+        <v>1.377754523676202</v>
       </c>
       <c r="C13" t="n">
-        <v>1.493424998904578</v>
+        <v>1.493424998904703</v>
       </c>
       <c r="D13" t="n">
-        <v>1.493424998904578</v>
+        <v>1.493424998904703</v>
       </c>
       <c r="E13" t="n">
-        <v>1.431833882991278</v>
+        <v>1.43183388299126</v>
       </c>
       <c r="F13" t="n">
-        <v>1.395774631806822</v>
+        <v>1.395774631806702</v>
       </c>
       <c r="G13" t="n">
-        <v>1.51741002544185</v>
+        <v>1.517410025441805</v>
       </c>
       <c r="H13" t="n">
-        <v>1.493424998904578</v>
+        <v>1.493424998904703</v>
       </c>
       <c r="I13" t="n">
-        <v>1.493424998904578</v>
+        <v>1.493424998904703</v>
       </c>
       <c r="J13" t="n">
-        <v>1.467362105587068</v>
+        <v>1.467362105586987</v>
       </c>
       <c r="K13" t="n">
-        <v>1.493424998904578</v>
+        <v>1.493424998904703</v>
       </c>
       <c r="L13" t="n">
-        <v>1.493424998904578</v>
+        <v>1.493424998904703</v>
       </c>
       <c r="M13" t="n">
-        <v>1.493424998903184</v>
+        <v>1.493424998903309</v>
       </c>
       <c r="N13" t="n">
-        <v>1.403761029262928</v>
+        <v>1.403761029262729</v>
       </c>
       <c r="O13" t="n">
-        <v>1.428401466466929</v>
+        <v>1.428401466467055</v>
       </c>
       <c r="P13" t="n">
-        <v>1.422361499934087</v>
+        <v>1.422361499934008</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.355022635349252</v>
+        <v>1.355022635349076</v>
       </c>
       <c r="R13" t="n">
-        <v>1.493424998904578</v>
+        <v>1.493424998904703</v>
       </c>
       <c r="S13" t="n">
-        <v>1.493424998904578</v>
+        <v>1.493424998904703</v>
       </c>
       <c r="T13" t="n">
-        <v>1.493424998904578</v>
+        <v>1.493424998904703</v>
       </c>
       <c r="U13" t="n">
-        <v>1.437223556931055</v>
+        <v>1.437223556930911</v>
       </c>
       <c r="V13" t="n">
-        <v>1.288207872299233</v>
+        <v>1.288207872299252</v>
       </c>
       <c r="W13" t="n">
-        <v>1.49344773109817</v>
+        <v>1.493447731098092</v>
       </c>
       <c r="X13" t="n">
-        <v>1.365624064016819</v>
+        <v>1.365624064016733</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.608871073297495</v>
+        <v>1.608871073297448</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.375605885248981</v>
+        <v>1.3756058852489</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.493424998904578</v>
+        <v>1.493424998904703</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.61425248213519</v>
+        <v>1.614252482135042</v>
       </c>
     </row>
     <row r="14">
@@ -7546,85 +7546,85 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.3906659766309973</v>
+        <v>0.3906659766309852</v>
       </c>
       <c r="C14" t="n">
-        <v>0.3906659766309973</v>
+        <v>0.3906659766309852</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3906659766309973</v>
+        <v>0.3906659766309852</v>
       </c>
       <c r="E14" t="n">
-        <v>0.3906659766309973</v>
+        <v>0.3906659766309852</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3906659766309973</v>
+        <v>0.3906659766309852</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3798890887700293</v>
+        <v>0.3798890887700108</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3906659766309973</v>
+        <v>0.3906659766309852</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3906659766309973</v>
+        <v>0.3906659766309852</v>
       </c>
       <c r="J14" t="n">
-        <v>0.3802927450907742</v>
+        <v>0.3802927450907687</v>
       </c>
       <c r="K14" t="n">
-        <v>0.3906659766309973</v>
+        <v>0.3906659766309852</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3906659766309973</v>
+        <v>0.3906659766309859</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3906659766309973</v>
+        <v>0.3906659766309852</v>
       </c>
       <c r="N14" t="n">
-        <v>0.3906659766309973</v>
+        <v>0.3906659766309852</v>
       </c>
       <c r="O14" t="n">
-        <v>0.3798890887700293</v>
+        <v>0.3798890887700108</v>
       </c>
       <c r="P14" t="n">
-        <v>0.3798890887700293</v>
+        <v>0.3798890887700108</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.3906659766309973</v>
+        <v>0.3906659766309852</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3906659766309973</v>
+        <v>0.3906659766309852</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3965613091364493</v>
+        <v>0.3965613091364408</v>
       </c>
       <c r="T14" t="n">
-        <v>0.3906659766309973</v>
+        <v>0.3906659766309852</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3798890887700265</v>
+        <v>0.379889088770011</v>
       </c>
       <c r="V14" t="n">
-        <v>0.3804840640986382</v>
+        <v>0.3804840640986247</v>
       </c>
       <c r="W14" t="n">
-        <v>0.3798890887700293</v>
+        <v>0.3798890887700108</v>
       </c>
       <c r="X14" t="n">
-        <v>0.3798890887700293</v>
+        <v>0.3798890887700108</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.3906659766309973</v>
+        <v>0.3906659766309852</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.3906659766309973</v>
+        <v>0.3906659766309852</v>
       </c>
       <c r="AA14" t="n">
-        <v>0.3906659766309973</v>
+        <v>0.3906659766309852</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.3906659766309973</v>
+        <v>0.3906659766309852</v>
       </c>
     </row>
     <row r="15">
@@ -7634,85 +7634,85 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.5709341599202237</v>
+        <v>0.5709341599202196</v>
       </c>
       <c r="C15" t="n">
         <v>0.3888164514681236</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6832971800894836</v>
+        <v>0.6832971800894589</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1960859026936697</v>
+        <v>0.1960859026936573</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7358851301459695</v>
+        <v>0.7358851301459186</v>
       </c>
       <c r="G15" t="n">
-        <v>1.454608962896593</v>
+        <v>1.454608962896363</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3626588816330236</v>
+        <v>0.3626588816330235</v>
       </c>
       <c r="I15" t="n">
-        <v>1.331343946972079</v>
+        <v>1.331343946972084</v>
       </c>
       <c r="J15" t="n">
-        <v>1.035995925113583</v>
+        <v>1.035995925113529</v>
       </c>
       <c r="K15" t="n">
-        <v>0.9528427568339745</v>
+        <v>0.9528427568339346</v>
       </c>
       <c r="L15" t="n">
-        <v>0.52537257349283</v>
+        <v>0.5253725734928207</v>
       </c>
       <c r="M15" t="n">
-        <v>1.290311651040133</v>
+        <v>1.290311651040052</v>
       </c>
       <c r="N15" t="n">
-        <v>0.661290476130998</v>
+        <v>0.6612904761309889</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6788774368400874</v>
+        <v>0.6788774368400187</v>
       </c>
       <c r="P15" t="n">
-        <v>0.8665534545875454</v>
+        <v>0.8665534545874021</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.9891890720315104</v>
+        <v>0.9891890720315146</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9873959100059725</v>
+        <v>0.9873959100059703</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9806580057665035</v>
+        <v>0.9806580057665029</v>
       </c>
       <c r="T15" t="n">
-        <v>0.78466378701505</v>
+        <v>0.784663787015048</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5676236330408928</v>
+        <v>0.5676236330408451</v>
       </c>
       <c r="V15" t="n">
-        <v>0.8039321033876112</v>
+        <v>0.8039321033875761</v>
       </c>
       <c r="W15" t="n">
-        <v>0.7606475186179591</v>
+        <v>0.7606475186179436</v>
       </c>
       <c r="X15" t="n">
-        <v>0.8627983601575558</v>
+        <v>0.8627983601574213</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.613129921303615</v>
+        <v>1.61312992130337</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.8570178253656565</v>
+        <v>0.857017825365655</v>
       </c>
       <c r="AA15" t="n">
-        <v>0.7023362832869844</v>
+        <v>0.7023362832869787</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.374699726682633</v>
+        <v>1.374699726682622</v>
       </c>
     </row>
     <row r="16">
@@ -7722,85 +7722,85 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.3925902403002488</v>
+        <v>0.3925902403002489</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5082607155286131</v>
+        <v>0.5082607155286036</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5082607155286131</v>
+        <v>0.5082607155286036</v>
       </c>
       <c r="E16" t="n">
-        <v>0.4466695996153391</v>
+        <v>0.4466695996153274</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4106103484308546</v>
+        <v>0.4106103484308507</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5214688542048976</v>
+        <v>0.5214688542048869</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5082607155286131</v>
+        <v>0.5082607155286036</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5082607155286131</v>
+        <v>0.5082607155286036</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4978874839883968</v>
+        <v>0.4978874839883863</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5082607155286131</v>
+        <v>0.5082607155286036</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5082607155286131</v>
+        <v>0.5082607155286036</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5082607155272129</v>
+        <v>0.508260715527208</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4185967458869758</v>
+        <v>0.4185967458869727</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4324602952300056</v>
+        <v>0.4324602952299956</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4264203286971546</v>
+        <v>0.426420328697146</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.3698583519732913</v>
+        <v>0.3698583519732866</v>
       </c>
       <c r="R16" t="n">
-        <v>0.5082607155286131</v>
+        <v>0.5082607155286036</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5082607155286131</v>
+        <v>0.5082607155286036</v>
       </c>
       <c r="T16" t="n">
-        <v>0.5082607155286131</v>
+        <v>0.5082607155286036</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4412823856941312</v>
+        <v>0.4412823856941187</v>
       </c>
       <c r="V16" t="n">
-        <v>0.4667464283386888</v>
+        <v>0.4667464283386745</v>
       </c>
       <c r="W16" t="n">
-        <v>0.4975065598612397</v>
+        <v>0.4975065598612305</v>
       </c>
       <c r="X16" t="n">
-        <v>0.3696828927799096</v>
+        <v>0.3696828927799036</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.6237067899215438</v>
+        <v>0.6237067899215321</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.3904416018730457</v>
+        <v>0.3904416018730288</v>
       </c>
       <c r="AA16" t="n">
-        <v>0.5082607155286131</v>
+        <v>0.5082607155286036</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.6290881987592346</v>
+        <v>0.629088198759212</v>
       </c>
     </row>
   </sheetData>
@@ -9451,7 +9451,7 @@
         <v>0.7076101109542199</v>
       </c>
       <c r="E2" t="n">
-        <v>8.081231726671362</v>
+        <v>8.081231726671364</v>
       </c>
       <c r="F2" t="n">
         <v>5.395941926710318</v>
@@ -9493,7 +9493,7 @@
         <v>5.767003789035777</v>
       </c>
       <c r="S2" t="n">
-        <v>3.159132687601301</v>
+        <v>3.159132687601302</v>
       </c>
       <c r="T2" t="n">
         <v>1.826774673969821</v>
@@ -9514,7 +9514,7 @@
         <v>1.314075069606409</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.498583747701543</v>
+        <v>3.498583747701544</v>
       </c>
       <c r="AA2" t="n">
         <v>1.001546677124086</v>
@@ -9630,7 +9630,7 @@
         <v>4.387036561664005</v>
       </c>
       <c r="F4" t="n">
-        <v>3.411407494466715</v>
+        <v>3.411407494466716</v>
       </c>
       <c r="G4" t="n">
         <v>1.90453973416511</v>
@@ -9648,7 +9648,7 @@
         <v>2.310085363621579</v>
       </c>
       <c r="L4" t="n">
-        <v>2.874620828463028</v>
+        <v>2.874620828463027</v>
       </c>
       <c r="M4" t="n">
         <v>1.892462443572797</v>
@@ -9666,7 +9666,7 @@
         <v>2.402013074817786</v>
       </c>
       <c r="R4" t="n">
-        <v>3.545821695497168</v>
+        <v>3.545821695497167</v>
       </c>
       <c r="S4" t="n">
         <v>2.595283302192905</v>
@@ -9848,7 +9848,7 @@
         <v>1.353444270329452</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8678154196984715</v>
+        <v>0.8678154196984716</v>
       </c>
       <c r="U6" t="n">
         <v>0.5384525330892532</v>
@@ -9891,13 +9891,13 @@
         <v>0.5334699963737377</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4833956595325644</v>
+        <v>0.4833956595325645</v>
       </c>
       <c r="F7" t="n">
         <v>0.4611137001156522</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5359632161970896</v>
+        <v>0.5359632161970898</v>
       </c>
       <c r="H7" t="n">
         <v>0.5334699963737377</v>
@@ -10079,7 +10079,7 @@
         <v>1.474276073289943</v>
       </c>
       <c r="I9" t="n">
-        <v>4.144895292962384</v>
+        <v>4.144895292962382</v>
       </c>
       <c r="J9" t="n">
         <v>2.414744012762994</v>
@@ -10088,7 +10088,7 @@
         <v>2.464150424562596</v>
       </c>
       <c r="L9" t="n">
-        <v>4.128697744290464</v>
+        <v>4.128697744290465</v>
       </c>
       <c r="M9" t="n">
         <v>1.249002122291554</v>
@@ -10179,7 +10179,7 @@
         <v>0.8873486624837819</v>
       </c>
       <c r="M10" t="n">
-        <v>0.8873486624839217</v>
+        <v>0.8873486624839219</v>
       </c>
       <c r="N10" t="n">
         <v>0.6879019726317135</v>
@@ -10206,7 +10206,7 @@
         <v>0.7599682322369837</v>
       </c>
       <c r="V10" t="n">
-        <v>0.8150427321779026</v>
+        <v>0.8150427321779025</v>
       </c>
       <c r="W10" t="n">
         <v>0.8873992274238881</v>
@@ -10322,7 +10322,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.570441139623197</v>
+        <v>3.570441139623196</v>
       </c>
       <c r="C12" t="n">
         <v>2.517783924534434</v>
@@ -10734,7 +10734,7 @@
         <v>0.4880076072309931</v>
       </c>
       <c r="V16" t="n">
-        <v>0.5157080768417052</v>
+        <v>0.5157080768417051</v>
       </c>
       <c r="W16" t="n">
         <v>0.5506431824019693</v>
@@ -10752,7 +10752,7 @@
         <v>0.5640333547521406</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.6961387622270307</v>
+        <v>0.6961387622270306</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Phase 2/Carbon dioxide/carbon dioxide land use results.xlsx
+++ b/Results/Phase 2/Carbon dioxide/carbon dioxide land use results.xlsx
@@ -586,85 +586,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.5804648703114779</v>
+        <v>0.580464870311635</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5438603931107866</v>
+        <v>0.543860393110786</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3761450059539121</v>
+        <v>0.3761450059539579</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.5932134322754132</v>
+        <v>-0.5932134322754521</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1598643891816718</v>
+        <v>0.1598643891816728</v>
       </c>
       <c r="G2" t="n">
-        <v>2.014664296629675</v>
+        <v>2.014664296629709</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5655190986434879</v>
+        <v>0.565519098643428</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7229713788892791</v>
+        <v>0.7229713788893488</v>
       </c>
       <c r="J2" t="n">
-        <v>1.278806835868453</v>
+        <v>1.278806835868491</v>
       </c>
       <c r="K2" t="n">
-        <v>1.612978377532623</v>
+        <v>1.612978377532647</v>
       </c>
       <c r="L2" t="n">
-        <v>0.402581124966104</v>
+        <v>0.402581124966327</v>
       </c>
       <c r="M2" t="n">
-        <v>2.574910656018032</v>
+        <v>2.574910656018022</v>
       </c>
       <c r="N2" t="n">
-        <v>0.8745933153982899</v>
+        <v>0.8745933153983045</v>
       </c>
       <c r="O2" t="n">
-        <v>1.180875874187529</v>
+        <v>1.180875874187558</v>
       </c>
       <c r="P2" t="n">
-        <v>1.093766151040719</v>
+        <v>1.09376615104076</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4826760163644479</v>
+        <v>0.4826760163645896</v>
       </c>
       <c r="R2" t="n">
-        <v>0.8816018426256398</v>
+        <v>0.8816018426256731</v>
       </c>
       <c r="S2" t="n">
-        <v>1.326459399947219</v>
+        <v>1.326459399947246</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7519429346759949</v>
+        <v>0.75194293467602</v>
       </c>
       <c r="U2" t="n">
-        <v>1.202634631300011</v>
+        <v>1.202634631300039</v>
       </c>
       <c r="V2" t="n">
-        <v>1.086944632660244</v>
+        <v>1.086944632660238</v>
       </c>
       <c r="W2" t="n">
-        <v>0.7340680494176848</v>
+        <v>0.7340680494176957</v>
       </c>
       <c r="X2" t="n">
-        <v>0.5389168426436257</v>
+        <v>0.5389168426435691</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.7838987390412046</v>
+        <v>0.7838987390412198</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.6849617231621608</v>
+        <v>0.684961723162355</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.299225252259897</v>
+        <v>1.299225252259915</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.448386774579931</v>
+        <v>2.448386774579927</v>
       </c>
     </row>
     <row r="3">
@@ -674,85 +674,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.3942362628812741</v>
+        <v>0.3942362628813598</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5593529109376897</v>
+        <v>0.559352910937688</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5486558099173388</v>
+        <v>0.5486558099173507</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4591645861816003</v>
+        <v>0.4591645861815947</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4145142292707796</v>
+        <v>0.4145142292707704</v>
       </c>
       <c r="G3" t="n">
-        <v>0.580675708940575</v>
+        <v>0.5806757089405732</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5486558099173388</v>
+        <v>0.5486558099173507</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5486558099173388</v>
+        <v>0.5486558099173507</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5469753914029718</v>
+        <v>0.546975391403006</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5486558099173388</v>
+        <v>0.5486558099173507</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5486558099173388</v>
+        <v>0.5486558099173507</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5602356991170709</v>
+        <v>0.5602356991170736</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4289548271191409</v>
+        <v>0.4289548271191599</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4618496965066851</v>
+        <v>0.4618496965066523</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4537863691716566</v>
+        <v>0.4537863691716337</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3638892974480159</v>
+        <v>0.3638892974479903</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5486558099173388</v>
+        <v>0.5486558099173507</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5486558099173388</v>
+        <v>0.5486558099173507</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5486558099173388</v>
+        <v>0.5486558099173507</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4726648338122322</v>
+        <v>0.4726648338122973</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5009217628185521</v>
+        <v>0.5009217628185483</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5486861577197186</v>
+        <v>0.5486861577197185</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3780421557329622</v>
+        <v>0.3780421557329995</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.7011295464267824</v>
+        <v>0.7011295464267957</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.3913678405185397</v>
+        <v>0.391367840518565</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.5486558099173388</v>
+        <v>0.5486558099173507</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.7143566997568711</v>
+        <v>0.7143566997568616</v>
       </c>
     </row>
     <row r="4">
@@ -762,85 +762,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.113721895709074</v>
+        <v>1.113721895709011</v>
       </c>
       <c r="C4" t="n">
-        <v>1.107178126911031</v>
+        <v>1.107178126911033</v>
       </c>
       <c r="D4" t="n">
-        <v>1.039249704395721</v>
+        <v>1.039249704395751</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6813114374435867</v>
+        <v>0.6813114374435694</v>
       </c>
       <c r="F4" t="n">
-        <v>0.958016491133403</v>
+        <v>0.9580164911333926</v>
       </c>
       <c r="G4" t="n">
-        <v>1.636470745382113</v>
+        <v>1.636470745382119</v>
       </c>
       <c r="H4" t="n">
-        <v>1.108274337438203</v>
+        <v>1.108274337438233</v>
       </c>
       <c r="I4" t="n">
-        <v>1.165663844689774</v>
+        <v>1.165663844689756</v>
       </c>
       <c r="J4" t="n">
-        <v>1.348876979423926</v>
+        <v>1.348876979423925</v>
       </c>
       <c r="K4" t="n">
-        <v>1.490060944705445</v>
+        <v>1.490060944705481</v>
       </c>
       <c r="L4" t="n">
-        <v>1.048885359347078</v>
+        <v>1.048885359347117</v>
       </c>
       <c r="M4" t="n">
-        <v>1.848033120198731</v>
+        <v>1.84803312019873</v>
       </c>
       <c r="N4" t="n">
-        <v>1.220928260112635</v>
+        <v>1.220928260112661</v>
       </c>
       <c r="O4" t="n">
-        <v>1.332564656239922</v>
+        <v>1.332564656239945</v>
       </c>
       <c r="P4" t="n">
-        <v>1.30081418504693</v>
+        <v>1.300814185046926</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.07807900674008</v>
+        <v>1.0780790067401</v>
       </c>
       <c r="R4" t="n">
-        <v>1.223482785988725</v>
+        <v>1.22348278598875</v>
       </c>
       <c r="S4" t="n">
-        <v>1.385628141851262</v>
+        <v>1.385628141851341</v>
       </c>
       <c r="T4" t="n">
-        <v>1.176223636572848</v>
+        <v>1.176223636572863</v>
       </c>
       <c r="U4" t="n">
-        <v>1.340495467703203</v>
+        <v>1.340495467703224</v>
       </c>
       <c r="V4" t="n">
-        <v>1.173060159609062</v>
+        <v>1.17306015960906</v>
       </c>
       <c r="W4" t="n">
-        <v>1.169708450793688</v>
+        <v>1.169708450793735</v>
       </c>
       <c r="X4" t="n">
-        <v>1.098578127505712</v>
+        <v>1.098578127505694</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.187871152019962</v>
+        <v>1.187871152019924</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.151809771509146</v>
+        <v>1.151809771509174</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.375701614818743</v>
+        <v>1.375701614818766</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.797351688598901</v>
+        <v>1.797351688598902</v>
       </c>
     </row>
     <row r="5">
@@ -850,85 +850,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.045843755107482</v>
+        <v>1.045843755107526</v>
       </c>
       <c r="C5" t="n">
-        <v>1.112824967736606</v>
+        <v>1.112824967736604</v>
       </c>
       <c r="D5" t="n">
-        <v>1.10212786671625</v>
+        <v>1.102127866716224</v>
       </c>
       <c r="E5" t="n">
-        <v>1.06489086752456</v>
+        <v>1.064890867524559</v>
       </c>
       <c r="F5" t="n">
-        <v>1.050833367596486</v>
+        <v>1.050833367596476</v>
       </c>
       <c r="G5" t="n">
-        <v>1.113798743913588</v>
+        <v>1.113798743913646</v>
       </c>
       <c r="H5" t="n">
-        <v>1.10212786671625</v>
+        <v>1.102127866716224</v>
       </c>
       <c r="I5" t="n">
-        <v>1.10212786671625</v>
+        <v>1.102127866716224</v>
       </c>
       <c r="J5" t="n">
-        <v>1.082133011514947</v>
+        <v>1.082133011514946</v>
       </c>
       <c r="K5" t="n">
-        <v>1.10212786671625</v>
+        <v>1.102127866716224</v>
       </c>
       <c r="L5" t="n">
-        <v>1.10212786671625</v>
+        <v>1.102127866716224</v>
       </c>
       <c r="M5" t="n">
-        <v>1.113707755916096</v>
+        <v>1.113707755916087</v>
       </c>
       <c r="N5" t="n">
-        <v>1.058498264086214</v>
+        <v>1.05849826408626</v>
       </c>
       <c r="O5" t="n">
-        <v>1.07048805770692</v>
+        <v>1.070488057706968</v>
       </c>
       <c r="P5" t="n">
-        <v>1.06754906957767</v>
+        <v>1.067549069577688</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.034782642559114</v>
+        <v>1.034782642559198</v>
       </c>
       <c r="R5" t="n">
-        <v>1.10212786671625</v>
+        <v>1.102127866716224</v>
       </c>
       <c r="S5" t="n">
-        <v>1.10212786671625</v>
+        <v>1.102127866716224</v>
       </c>
       <c r="T5" t="n">
-        <v>1.10212786671625</v>
+        <v>1.102127866716224</v>
       </c>
       <c r="U5" t="n">
-        <v>1.074430048257034</v>
+        <v>1.074430048257036</v>
       </c>
       <c r="V5" t="n">
-        <v>0.9594617049797334</v>
+        <v>0.9594617049797257</v>
       </c>
       <c r="W5" t="n">
-        <v>1.10213892813386</v>
+        <v>1.102138928133877</v>
       </c>
       <c r="X5" t="n">
-        <v>1.039941193212723</v>
+        <v>1.039941193212763</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.157702753236934</v>
+        <v>1.157702753236907</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.044798248838978</v>
+        <v>1.04479824883901</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.10212786671625</v>
+        <v>1.102127866716224</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.165318088335072</v>
+        <v>1.165318088335059</v>
       </c>
     </row>
     <row r="6">
@@ -938,85 +938,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3149439240484774</v>
+        <v>0.3149439240484653</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3084001552504314</v>
+        <v>0.3084001552504297</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2404717327351236</v>
+        <v>0.2404717327351806</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1174665342170137</v>
+        <v>-0.1174665342170257</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1592385194728093</v>
+        <v>0.1592385194728064</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8304137385494585</v>
+        <v>0.8304137385494901</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3094963657776065</v>
+        <v>0.3094963657776548</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3668858730291726</v>
+        <v>0.3668858730291663</v>
       </c>
       <c r="J6" t="n">
-        <v>0.561388433538577</v>
+        <v>0.5613884335385571</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6912829730448492</v>
+        <v>0.6912829730448665</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2501073876864892</v>
+        <v>0.2501073876866195</v>
       </c>
       <c r="M6" t="n">
-        <v>1.049255148538137</v>
+        <v>1.049255148538138</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4221502884520384</v>
+        <v>0.4221502884521209</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5265076494072738</v>
+        <v>0.5265076494072977</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4947571782142714</v>
+        <v>0.4947571782143089</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2793010350794857</v>
+        <v>0.2793010350795003</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4247048143281288</v>
+        <v>0.4247048143281762</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5868501701906697</v>
+        <v>0.5868501701907145</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3774456649122557</v>
+        <v>0.377445664912289</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5344384608705453</v>
+        <v>0.5344384608705722</v>
       </c>
       <c r="V6" t="n">
-        <v>0.4895475415967799</v>
+        <v>0.4895475415967806</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3636514439610395</v>
+        <v>0.3636514439610392</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2925211206730577</v>
+        <v>0.2925211206730514</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.3890931803593724</v>
+        <v>0.3890931803593577</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.3530317998485558</v>
+        <v>0.3530317998486018</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.5769236431581483</v>
+        <v>0.5769236431581746</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9985737169383095</v>
+        <v>0.9985737169383078</v>
       </c>
     </row>
     <row r="7">
@@ -1026,85 +1026,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.247065783446886</v>
+        <v>0.2470657834469218</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3140469960760103</v>
+        <v>0.3140469960760136</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3033498950556588</v>
+        <v>0.3033498950556465</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2661128958639673</v>
+        <v>0.2661128958639615</v>
       </c>
       <c r="F7" t="n">
-        <v>0.252055395935891</v>
+        <v>0.2520553959358848</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3077417370809344</v>
+        <v>0.3077417370809622</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3033498950556588</v>
+        <v>0.3033498950556465</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3033498950556588</v>
+        <v>0.3033498950556465</v>
       </c>
       <c r="J7" t="n">
-        <v>0.294644465629597</v>
+        <v>0.2946444656296077</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3033498950556588</v>
+        <v>0.3033498950556465</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3033498950556588</v>
+        <v>0.3033498950556465</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3149297842555011</v>
+        <v>0.3149297842554921</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2597202924256229</v>
+        <v>0.2597202924256751</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2644310508742643</v>
+        <v>0.2644310508743292</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2614920627450179</v>
+        <v>0.2614920627450388</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2360046708985181</v>
+        <v>0.2360046708986233</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3033498950556588</v>
+        <v>0.3033498950556465</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3033498950556588</v>
+        <v>0.3033498950556465</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3033498950556588</v>
+        <v>0.3033498950556465</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2683730414243792</v>
+        <v>0.2683730414243491</v>
       </c>
       <c r="V7" t="n">
-        <v>0.2759490869674499</v>
+        <v>0.2759490869674515</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2960819213012059</v>
+        <v>0.2960819213012155</v>
       </c>
       <c r="X7" t="n">
-        <v>0.2338841863800692</v>
+        <v>0.233884186380112</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3589247815763402</v>
+        <v>0.3589247815762969</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.2460202771783827</v>
+        <v>0.2460202771784396</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.3033498950556588</v>
+        <v>0.3033498950556465</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.3665401166744753</v>
+        <v>0.3665401166744721</v>
       </c>
     </row>
   </sheetData>
@@ -1270,85 +1270,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.34922093668016</v>
+        <v>2.349220936680062</v>
       </c>
       <c r="C2" t="n">
-        <v>2.977103984708091</v>
+        <v>2.977103984708093</v>
       </c>
       <c r="D2" t="n">
-        <v>2.127973975155941</v>
+        <v>2.127973975155837</v>
       </c>
       <c r="E2" t="n">
         <v>2.171817906514844</v>
       </c>
       <c r="F2" t="n">
-        <v>4.178289807151177</v>
+        <v>4.17828980715117</v>
       </c>
       <c r="G2" t="n">
-        <v>1.329438976755859</v>
+        <v>1.329438976755785</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8573785614983375</v>
+        <v>0.8573785614982503</v>
       </c>
       <c r="I2" t="n">
-        <v>2.395533413001343</v>
+        <v>2.395533413001243</v>
       </c>
       <c r="J2" t="n">
-        <v>1.862085383634615</v>
+        <v>1.862085383634577</v>
       </c>
       <c r="K2" t="n">
-        <v>2.28841777031952</v>
+        <v>2.28841777031942</v>
       </c>
       <c r="L2" t="n">
-        <v>3.778077843708034</v>
+        <v>3.778077843707891</v>
       </c>
       <c r="M2" t="n">
-        <v>1.298724497839173</v>
+        <v>1.298724497839177</v>
       </c>
       <c r="N2" t="n">
-        <v>1.538313612833859</v>
+        <v>1.538313612833889</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9673700342593078</v>
+        <v>0.9673700342591843</v>
       </c>
       <c r="P2" t="n">
-        <v>1.245586618964184</v>
+        <v>1.24558661896416</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.684003913027093</v>
+        <v>2.684003913026995</v>
       </c>
       <c r="R2" t="n">
-        <v>6.827888773755632</v>
+        <v>6.827888773755546</v>
       </c>
       <c r="S2" t="n">
-        <v>3.070397964709065</v>
+        <v>3.070397964708978</v>
       </c>
       <c r="T2" t="n">
-        <v>1.570784846531991</v>
+        <v>1.570784846531941</v>
       </c>
       <c r="U2" t="n">
-        <v>1.109961561360851</v>
+        <v>1.109961561360741</v>
       </c>
       <c r="V2" t="n">
-        <v>1.672499382496353</v>
+        <v>1.672499382496357</v>
       </c>
       <c r="W2" t="n">
-        <v>2.056302160345559</v>
+        <v>2.056302160345512</v>
       </c>
       <c r="X2" t="n">
-        <v>2.074856046557723</v>
+        <v>2.074856046557624</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.701480870501971</v>
+        <v>1.701480870501869</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.814487028325466</v>
+        <v>1.814487028325414</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.524241743431264</v>
+        <v>1.524241743431153</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.788134168793237</v>
+        <v>1.788134168793236</v>
       </c>
     </row>
     <row r="3">
@@ -1358,85 +1358,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6336722363495636</v>
+        <v>0.6336722363494607</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8777956700333284</v>
+        <v>0.8777956700333306</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8640165318509038</v>
+        <v>0.8640165318508973</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7319479373634064</v>
+        <v>0.7319479373634101</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6720440422711352</v>
+        <v>0.6720440422711299</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9117799220211641</v>
+        <v>0.9117799220211396</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8640165318509038</v>
+        <v>0.8640165318508973</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8640165318509038</v>
+        <v>0.8640165318508973</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8581995365953189</v>
+        <v>0.8581995365952654</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8640165318509038</v>
+        <v>0.8640165318508973</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8640165318509038</v>
+        <v>0.8640165318508973</v>
       </c>
       <c r="M3" t="n">
-        <v>0.863644021117533</v>
+        <v>0.8636440211175301</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6854611668754114</v>
+        <v>0.6854611668753422</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7345297311150337</v>
+        <v>0.7345297311149647</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7225018404048049</v>
+        <v>0.7225018404047051</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.588404325162098</v>
+        <v>0.5884043251620681</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8640165318509038</v>
+        <v>0.8640165318508973</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8640165318509038</v>
+        <v>0.8640165318508973</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8640165318509038</v>
+        <v>0.8640165318508973</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7504792021883289</v>
+        <v>0.7504792021882702</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7859296773831588</v>
+        <v>0.7859296773831562</v>
       </c>
       <c r="W3" t="n">
-        <v>0.864061800289189</v>
+        <v>0.8640618002891438</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6095158370431966</v>
+        <v>0.6095158370430968</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.091144841573616</v>
+        <v>1.091144841573586</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.6293934728803625</v>
+        <v>0.6293934728802917</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.8640165318509038</v>
+        <v>0.8640165318508973</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.099185681385425</v>
+        <v>1.099185681385422</v>
       </c>
     </row>
     <row r="4">
@@ -1446,85 +1446,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.216872396617026</v>
+        <v>2.216872396616913</v>
       </c>
       <c r="C4" t="n">
-        <v>2.454485198765854</v>
+        <v>2.454485198765874</v>
       </c>
       <c r="D4" t="n">
-        <v>2.136230477154436</v>
+        <v>2.136230477154299</v>
       </c>
       <c r="E4" t="n">
-        <v>2.146226428140547</v>
+        <v>2.146226428140568</v>
       </c>
       <c r="F4" t="n">
         <v>2.885126948631058</v>
       </c>
       <c r="G4" t="n">
-        <v>1.845173847108972</v>
+        <v>1.845173847108823</v>
       </c>
       <c r="H4" t="n">
-        <v>1.67311336896087</v>
+        <v>1.673113368960756</v>
       </c>
       <c r="I4" t="n">
-        <v>2.23375275040754</v>
+        <v>2.233752750407432</v>
       </c>
       <c r="J4" t="n">
-        <v>2.012941047081273</v>
+        <v>2.012941047081283</v>
       </c>
       <c r="K4" t="n">
-        <v>2.194710356465396</v>
+        <v>2.194710356465289</v>
       </c>
       <c r="L4" t="n">
-        <v>2.737673960743709</v>
+        <v>2.737673960743631</v>
       </c>
       <c r="M4" t="n">
-        <v>1.833742045267335</v>
+        <v>1.833742045267339</v>
       </c>
       <c r="N4" t="n">
-        <v>1.921306199229566</v>
+        <v>1.921306199229532</v>
       </c>
       <c r="O4" t="n">
-        <v>1.713203969197157</v>
+        <v>1.713203969197062</v>
       </c>
       <c r="P4" t="n">
-        <v>1.814610647337946</v>
+        <v>1.814610647337922</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.338896860275293</v>
+        <v>2.338896860275183</v>
       </c>
       <c r="R4" t="n">
-        <v>3.849294232058072</v>
+        <v>3.849294232057967</v>
       </c>
       <c r="S4" t="n">
-        <v>2.479732954845325</v>
+        <v>2.479732954845235</v>
       </c>
       <c r="T4" t="n">
-        <v>1.933141582616034</v>
+        <v>1.933141582615996</v>
       </c>
       <c r="U4" t="n">
-        <v>1.765176906431434</v>
+        <v>1.765176906431312</v>
       </c>
       <c r="V4" t="n">
-        <v>1.810066434830707</v>
+        <v>1.810066434830718</v>
       </c>
       <c r="W4" t="n">
-        <v>2.110106942268989</v>
+        <v>2.110106942268898</v>
       </c>
       <c r="X4" t="n">
-        <v>2.116869615922597</v>
+        <v>2.116869615922491</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.980778748642941</v>
+        <v>1.980778748642849</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.021968166184279</v>
+        <v>2.021968166184214</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.916177168072532</v>
+        <v>1.916177168072484</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.008902670129084</v>
+        <v>2.008902670129091</v>
       </c>
     </row>
     <row r="5">
@@ -1534,85 +1534,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.591575040336354</v>
+        <v>1.591575040336334</v>
       </c>
       <c r="C5" t="n">
         <v>1.689311969389751</v>
       </c>
       <c r="D5" t="n">
-        <v>1.675532831207334</v>
+        <v>1.675532831207316</v>
       </c>
       <c r="E5" t="n">
-        <v>1.621410732191697</v>
+        <v>1.621410732191688</v>
       </c>
       <c r="F5" t="n">
-        <v>1.607141539748745</v>
+        <v>1.607141539748768</v>
       </c>
       <c r="G5" t="n">
-        <v>1.692942026058366</v>
+        <v>1.692942026058333</v>
       </c>
       <c r="H5" t="n">
-        <v>1.675532831207334</v>
+        <v>1.675532831207316</v>
       </c>
       <c r="I5" t="n">
-        <v>1.675532831207334</v>
+        <v>1.675532831207316</v>
       </c>
       <c r="J5" t="n">
-        <v>1.647036444058237</v>
+        <v>1.647036444058215</v>
       </c>
       <c r="K5" t="n">
-        <v>1.675532831207334</v>
+        <v>1.675532831207316</v>
       </c>
       <c r="L5" t="n">
-        <v>1.675532831207334</v>
+        <v>1.675532831207316</v>
       </c>
       <c r="M5" t="n">
-        <v>1.675160320475205</v>
+        <v>1.675160320475196</v>
       </c>
       <c r="N5" t="n">
-        <v>1.61045149737671</v>
+        <v>1.610451497376685</v>
       </c>
       <c r="O5" t="n">
-        <v>1.628336412849893</v>
+        <v>1.628336412849855</v>
       </c>
       <c r="P5" t="n">
-        <v>1.62395238792468</v>
+        <v>1.623952387924583</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.575075418271205</v>
+        <v>1.575075418271168</v>
       </c>
       <c r="R5" t="n">
-        <v>1.675532831207334</v>
+        <v>1.675532831207316</v>
       </c>
       <c r="S5" t="n">
-        <v>1.675532831207334</v>
+        <v>1.675532831207316</v>
       </c>
       <c r="T5" t="n">
-        <v>1.675532831207334</v>
+        <v>1.675532831207316</v>
       </c>
       <c r="U5" t="n">
-        <v>1.634149807767962</v>
+        <v>1.634149807767923</v>
       </c>
       <c r="V5" t="n">
-        <v>1.486922187944039</v>
+        <v>1.486922187944043</v>
       </c>
       <c r="W5" t="n">
-        <v>1.675549331021547</v>
+        <v>1.67554933102149</v>
       </c>
       <c r="X5" t="n">
-        <v>1.582770316447981</v>
+        <v>1.582770316447909</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.758318433026025</v>
+        <v>1.758318433025978</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.59001548129563</v>
+        <v>1.59001548129559</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.675532831207334</v>
+        <v>1.675532831207316</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.75778903651051</v>
+        <v>1.757789036510531</v>
       </c>
     </row>
     <row r="6">
@@ -1622,85 +1622,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.042814941693397</v>
+        <v>1.042814941693276</v>
       </c>
       <c r="C6" t="n">
-        <v>1.280427743842262</v>
+        <v>1.280427743842263</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9621730222308089</v>
+        <v>0.9621730222307103</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9721689732169475</v>
+        <v>0.9721689732169533</v>
       </c>
       <c r="F6" t="n">
         <v>1.711069493707451</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6568820458255934</v>
+        <v>0.6568820458254598</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4990559140372424</v>
+        <v>0.4990559140371288</v>
       </c>
       <c r="I6" t="n">
-        <v>1.059695295483908</v>
+        <v>1.059695295483791</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8478291950672905</v>
+        <v>0.847829195067264</v>
       </c>
       <c r="K6" t="n">
-        <v>1.020652901541768</v>
+        <v>1.020652901541652</v>
       </c>
       <c r="L6" t="n">
-        <v>1.563616505820104</v>
+        <v>1.563616505820072</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6596845903437241</v>
+        <v>0.6596845903437222</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7472487443059698</v>
+        <v>0.7472487443058961</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5249121679137775</v>
+        <v>0.5249121679136889</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6263188460545585</v>
+        <v>0.6263188460545548</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.164839405351662</v>
+        <v>1.16483940535155</v>
       </c>
       <c r="R6" t="n">
-        <v>2.675236777134445</v>
+        <v>2.675236777134301</v>
       </c>
       <c r="S6" t="n">
-        <v>1.305675499921714</v>
+        <v>1.305675499921597</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7590841276924103</v>
+        <v>0.75908412769236</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5768851051480326</v>
+        <v>0.5768851051479384</v>
       </c>
       <c r="V6" t="n">
-        <v>0.773789789680005</v>
+        <v>0.7737897896800067</v>
       </c>
       <c r="W6" t="n">
-        <v>0.921815140985605</v>
+        <v>0.9218151409855289</v>
       </c>
       <c r="X6" t="n">
-        <v>0.9285778146392115</v>
+        <v>0.928577814639113</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.8067212937193193</v>
+        <v>0.8067212937192083</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.847910711260648</v>
+        <v>0.847910711260583</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.7421197131489056</v>
+        <v>0.7421197131488827</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8348452152054802</v>
+        <v>0.8348452152054784</v>
       </c>
     </row>
     <row r="7">
@@ -1710,85 +1710,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.417517585412739</v>
+        <v>0.4175175854126781</v>
       </c>
       <c r="C7" t="n">
-        <v>0.515254514466134</v>
+        <v>0.5152545144661369</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5014753762837231</v>
+        <v>0.5014753762836842</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4473532772680712</v>
+        <v>0.4473532772680719</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4330840848251557</v>
+        <v>0.4330840848251521</v>
       </c>
       <c r="G7" t="n">
-        <v>0.504650224774998</v>
+        <v>0.5046502247749592</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5014753762837231</v>
+        <v>0.5014753762836842</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5014753762837231</v>
+        <v>0.5014753762836842</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4819245920442682</v>
+        <v>0.4819245920442148</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5014753762837231</v>
+        <v>0.5014753762836842</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5014753762837231</v>
+        <v>0.5014753762836842</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5011028655515858</v>
+        <v>0.5011028655515809</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4363940424531159</v>
+        <v>0.4363940424530455</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4400446115665224</v>
+        <v>0.4400446115664782</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4356605866413134</v>
+        <v>0.4356605866412164</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4010179633475932</v>
+        <v>0.4010179633475347</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5014753762837231</v>
+        <v>0.5014753762836842</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5014753762837231</v>
+        <v>0.5014753762836842</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5014753762837231</v>
+        <v>0.5014753762836842</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4458580064845889</v>
+        <v>0.445858006484558</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4506455427933345</v>
+        <v>0.4506455427933322</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4872575297381742</v>
+        <v>0.4872575297381223</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3944785151646202</v>
+        <v>0.3944785151645466</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5842609781024062</v>
+        <v>0.5842609781023279</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.415958026372011</v>
+        <v>0.4159580263719557</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.5014753762837231</v>
+        <v>0.5014753762836842</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.5837315815869167</v>
+        <v>0.5837315815869183</v>
       </c>
     </row>
   </sheetData>
@@ -1954,85 +1954,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6183474168114906</v>
+        <v>0.6183474168116859</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6797025466907256</v>
+        <v>0.6797025466909052</v>
       </c>
       <c r="D2" t="n">
-        <v>0.8175835731056951</v>
+        <v>0.8175835731056901</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.03030067708562283</v>
+        <v>-0.03030067708554156</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1294707522621194</v>
+        <v>0.1294707522621274</v>
       </c>
       <c r="G2" t="n">
-        <v>2.567969754594221</v>
+        <v>2.567969754594215</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4077149473064237</v>
+        <v>0.4077149473064298</v>
       </c>
       <c r="I2" t="n">
         <v>1.022388149827249</v>
       </c>
       <c r="J2" t="n">
-        <v>1.610417876766247</v>
+        <v>1.610417876766233</v>
       </c>
       <c r="K2" t="n">
-        <v>1.460343232001333</v>
+        <v>1.460343232001344</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4644000620871928</v>
+        <v>0.4644000620875091</v>
       </c>
       <c r="M2" t="n">
-        <v>2.415475300055977</v>
+        <v>2.41547530005598</v>
       </c>
       <c r="N2" t="n">
-        <v>0.922116388293688</v>
+        <v>0.9221163882936888</v>
       </c>
       <c r="O2" t="n">
-        <v>1.16622845384143</v>
+        <v>1.166228453841429</v>
       </c>
       <c r="P2" t="n">
-        <v>1.346460202769861</v>
+        <v>1.346460202769869</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6826620226058396</v>
+        <v>0.6826620226058552</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6617022357840874</v>
+        <v>0.6617022357840845</v>
       </c>
       <c r="S2" t="n">
-        <v>1.472879814140913</v>
+        <v>1.472879814140929</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8692531691257726</v>
+        <v>0.8692531691257799</v>
       </c>
       <c r="U2" t="n">
         <v>1.31447030694609</v>
       </c>
       <c r="V2" t="n">
-        <v>1.162883463105568</v>
+        <v>1.162883463105555</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9871820567413115</v>
+        <v>0.9871820567413206</v>
       </c>
       <c r="X2" t="n">
-        <v>0.9323755839627726</v>
+        <v>0.9323755839627373</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.153303600865322</v>
+        <v>1.153303600865319</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.9500027440103533</v>
+        <v>0.9500027440103571</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.001735908729994</v>
+        <v>1.001735908730032</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.476598582409344</v>
+        <v>2.47659858240936</v>
       </c>
     </row>
     <row r="3">
@@ -2042,85 +2042,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.46649086175535</v>
+        <v>0.4664908617553222</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6545489126270758</v>
+        <v>0.6545489126268863</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6441100665027188</v>
+        <v>0.6441100665027231</v>
       </c>
       <c r="E3" t="n">
-        <v>0.542258633817451</v>
+        <v>0.542258633817459</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4883099413865468</v>
+        <v>0.4883099413865533</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6809405656800797</v>
+        <v>0.6809405656800742</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6441100665027188</v>
+        <v>0.6441100665027231</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6441100665027188</v>
+        <v>0.6441100665027231</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6412775490567032</v>
+        <v>0.6412775490567091</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6441100665027188</v>
+        <v>0.6441100665027231</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6441100665027188</v>
+        <v>0.6441100665027231</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6531952451928764</v>
+        <v>0.6531952451928843</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5064254677193406</v>
+        <v>0.5064254677193315</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5442623908303409</v>
+        <v>0.5442623908303014</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5349876467225334</v>
+        <v>0.5349876467225199</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4315846341286047</v>
+        <v>0.4315846341285806</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6441100665027188</v>
+        <v>0.6441100665027231</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6441100665027188</v>
+        <v>0.6441100665027231</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6441100665027188</v>
+        <v>0.6441100665027231</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5553500412640987</v>
+        <v>0.5553500412640728</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5858114736821735</v>
+        <v>0.5858114736822043</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6441449735185305</v>
+        <v>0.6441449735185304</v>
       </c>
       <c r="X3" t="n">
-        <v>0.4478637870286453</v>
+        <v>0.4478637870286394</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.8171776837329746</v>
+        <v>0.8171776837329499</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.4631914938586184</v>
+        <v>0.4631914938585961</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.6441100665027188</v>
+        <v>0.6441100665027231</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.832297376005273</v>
+        <v>0.8322973760052778</v>
       </c>
     </row>
     <row r="4">
@@ -2130,85 +2130,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.325094762120997</v>
+        <v>1.325094762120999</v>
       </c>
       <c r="C4" t="n">
-        <v>1.35409199578482</v>
+        <v>1.354091995784761</v>
       </c>
       <c r="D4" t="n">
-        <v>1.397714001541169</v>
+        <v>1.397714001541173</v>
       </c>
       <c r="E4" t="n">
-        <v>1.084047153072735</v>
+        <v>1.084047153072756</v>
       </c>
       <c r="F4" t="n">
-        <v>1.143185996881801</v>
+        <v>1.143185996881806</v>
       </c>
       <c r="G4" t="n">
-        <v>2.035709210621462</v>
+        <v>2.035709210621466</v>
       </c>
       <c r="H4" t="n">
         <v>1.248321700357733</v>
       </c>
       <c r="I4" t="n">
-        <v>1.472362864819417</v>
+        <v>1.47236286481942</v>
       </c>
       <c r="J4" t="n">
-        <v>1.662916707190229</v>
+        <v>1.662916707190214</v>
       </c>
       <c r="K4" t="n">
-        <v>1.631992349543648</v>
+        <v>1.631992349543653</v>
       </c>
       <c r="L4" t="n">
-        <v>1.268982759065099</v>
+        <v>1.268982759065109</v>
       </c>
       <c r="M4" t="n">
-        <v>1.985900510364485</v>
+        <v>1.985900510364486</v>
       </c>
       <c r="N4" t="n">
-        <v>1.435814985190903</v>
+        <v>1.435814985190909</v>
       </c>
       <c r="O4" t="n">
-        <v>1.524790966574459</v>
+        <v>1.524790966574461</v>
       </c>
       <c r="P4" t="n">
-        <v>1.590483322670823</v>
+        <v>1.590483322670826</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.348536680712806</v>
+        <v>1.348536680712833</v>
       </c>
       <c r="R4" t="n">
-        <v>1.340897084538522</v>
+        <v>1.340897084538519</v>
       </c>
       <c r="S4" t="n">
-        <v>1.636561786521546</v>
+        <v>1.63656178652155</v>
       </c>
       <c r="T4" t="n">
-        <v>1.416546962555458</v>
+        <v>1.416546962555461</v>
       </c>
       <c r="U4" t="n">
-        <v>1.57882338128738</v>
+        <v>1.578823381287384</v>
       </c>
       <c r="V4" t="n">
-        <v>1.372204225863888</v>
+        <v>1.372204225863925</v>
       </c>
       <c r="W4" t="n">
-        <v>1.459530657300409</v>
+        <v>1.459530657300416</v>
       </c>
       <c r="X4" t="n">
-        <v>1.439554341542727</v>
+        <v>1.439554341542766</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.520080009435952</v>
+        <v>1.520080009435957</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.445979234391506</v>
+        <v>1.445979234391503</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.464835365450325</v>
+        <v>1.464835365450343</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.004089087796044</v>
+        <v>2.004089087796054</v>
       </c>
     </row>
     <row r="5">
@@ -2218,85 +2218,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.269744830992735</v>
+        <v>1.269744830992733</v>
       </c>
       <c r="C5" t="n">
-        <v>1.344923791537504</v>
+        <v>1.3449237915372</v>
       </c>
       <c r="D5" t="n">
-        <v>1.334484945413148</v>
+        <v>1.334484945413121</v>
       </c>
       <c r="E5" t="n">
-        <v>1.29273829856603</v>
+        <v>1.292738298566039</v>
       </c>
       <c r="F5" t="n">
-        <v>1.273978667615157</v>
+        <v>1.273978667615163</v>
       </c>
       <c r="G5" t="n">
-        <v>1.347909229877736</v>
+        <v>1.347909229877722</v>
       </c>
       <c r="H5" t="n">
-        <v>1.334484945413148</v>
+        <v>1.334484945413118</v>
       </c>
       <c r="I5" t="n">
-        <v>1.334484945413148</v>
+        <v>1.334484945413118</v>
       </c>
       <c r="J5" t="n">
-        <v>1.309676437960392</v>
+        <v>1.309676437960386</v>
       </c>
       <c r="K5" t="n">
-        <v>1.334484945413148</v>
+        <v>1.334484945413121</v>
       </c>
       <c r="L5" t="n">
-        <v>1.334484945413148</v>
+        <v>1.334484945413118</v>
       </c>
       <c r="M5" t="n">
-        <v>1.343570124104072</v>
+        <v>1.343570124104078</v>
       </c>
       <c r="N5" t="n">
-        <v>1.284300525930788</v>
+        <v>1.284300525930786</v>
       </c>
       <c r="O5" t="n">
-        <v>1.298091640101166</v>
+        <v>1.298091640101146</v>
       </c>
       <c r="P5" t="n">
-        <v>1.294711104783418</v>
+        <v>1.294711104783394</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.257021920912403</v>
+        <v>1.257021920912404</v>
       </c>
       <c r="R5" t="n">
-        <v>1.334484945413148</v>
+        <v>1.334484945413118</v>
       </c>
       <c r="S5" t="n">
-        <v>1.334484945413148</v>
+        <v>1.334484945413121</v>
       </c>
       <c r="T5" t="n">
-        <v>1.334484945413148</v>
+        <v>1.334484945413118</v>
       </c>
       <c r="U5" t="n">
-        <v>1.302132958486504</v>
+        <v>1.302132958486498</v>
       </c>
       <c r="V5" t="n">
-        <v>1.161868262040484</v>
+        <v>1.161868262040477</v>
       </c>
       <c r="W5" t="n">
-        <v>1.334497668610507</v>
+        <v>1.334497668610505</v>
       </c>
       <c r="X5" t="n">
-        <v>1.262955480985009</v>
+        <v>1.262955480985005</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.397566059631006</v>
+        <v>1.397566059630979</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.268542250137513</v>
+        <v>1.268542250137501</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.334484945413148</v>
+        <v>1.334484945413121</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.404760606421362</v>
+        <v>1.40476060642137</v>
       </c>
     </row>
     <row r="6">
@@ -2306,85 +2306,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3530677189889382</v>
+        <v>0.3530677189889512</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3820649526527609</v>
+        <v>0.3820649526527921</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4256869584091095</v>
+        <v>0.4256869584090926</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1120201099406763</v>
+        <v>0.1120201099407025</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1711589537497429</v>
+        <v>0.1711589537497493</v>
       </c>
       <c r="G6" t="n">
-        <v>1.054801566848992</v>
+        <v>1.054801566848986</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2762946572256733</v>
+        <v>0.2762946572256519</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5003358216873576</v>
+        <v>0.5003358216873373</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7042903267219141</v>
+        <v>0.704290326721893</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6599653064115888</v>
+        <v>0.6599653064115755</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2969557159330392</v>
+        <v>0.2969557159330342</v>
       </c>
       <c r="M6" t="n">
-        <v>1.013873467232427</v>
+        <v>1.013873467232431</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4637879420588444</v>
+        <v>0.4637879420588287</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5438833228019869</v>
+        <v>0.5438833228019861</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6095756788983512</v>
+        <v>0.6095756788983467</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3765096375807477</v>
+        <v>0.3765096375807326</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3688700414064622</v>
+        <v>0.3688700414064437</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6645347433894866</v>
+        <v>0.6645347433894735</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4445199194233994</v>
+        <v>0.4445199194233843</v>
       </c>
       <c r="U6" t="n">
-        <v>0.59791573751491</v>
+        <v>0.5979157375149075</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5383364203984107</v>
+        <v>0.5383364203983865</v>
       </c>
       <c r="W6" t="n">
-        <v>0.4786230135279378</v>
+        <v>0.4786230135279441</v>
       </c>
       <c r="X6" t="n">
-        <v>0.4586466977702557</v>
+        <v>0.4586466977702724</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5480529663038931</v>
+        <v>0.5480529663038766</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.4739521912594468</v>
+        <v>0.4739521912594647</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.4928083223182652</v>
+        <v>0.492808322318257</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.032062044663985</v>
+        <v>1.032062044663991</v>
       </c>
     </row>
     <row r="7">
@@ -2394,85 +2394,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2977177878606755</v>
+        <v>0.2977177878606428</v>
       </c>
       <c r="C7" t="n">
-        <v>0.3728967484054433</v>
+        <v>0.3728967484048736</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3624579022810883</v>
+        <v>0.3624579022810793</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3207112554339714</v>
+        <v>0.3207112554339744</v>
       </c>
       <c r="F7" t="n">
-        <v>0.301951624483097</v>
+        <v>0.3019516244831024</v>
       </c>
       <c r="G7" t="n">
-        <v>0.367001586105265</v>
+        <v>0.3670015861052538</v>
       </c>
       <c r="H7" t="n">
-        <v>0.3624579022810883</v>
+        <v>0.3624579022810793</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3624579022810883</v>
+        <v>0.3624579022810793</v>
       </c>
       <c r="J7" t="n">
-        <v>0.3510500574920776</v>
+        <v>0.351050057492072</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3624579022810883</v>
+        <v>0.3624579022810793</v>
       </c>
       <c r="L7" t="n">
-        <v>0.3624579022810883</v>
+        <v>0.3624579022810793</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3715430809720113</v>
+        <v>0.3715430809720198</v>
       </c>
       <c r="N7" t="n">
-        <v>0.31227348279873</v>
+        <v>0.3122734827987052</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3171839963286969</v>
+        <v>0.3171839963286703</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3138034610109465</v>
+        <v>0.3138034610109192</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2849948777803451</v>
+        <v>0.2849948777803105</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3624579022810883</v>
+        <v>0.3624579022810793</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3624579022810883</v>
+        <v>0.3624579022810793</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3624579022810883</v>
+        <v>0.3624579022810793</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3212253147140338</v>
+        <v>0.3212253147140265</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3280004565750049</v>
+        <v>0.3280004565750277</v>
       </c>
       <c r="W7" t="n">
-        <v>0.353590024838035</v>
+        <v>0.35359002483804</v>
       </c>
       <c r="X7" t="n">
-        <v>0.2820478372125369</v>
+        <v>0.2820478372125387</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4255390164989474</v>
+        <v>0.4255390164989258</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.296515207005454</v>
+        <v>0.2965152070054305</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.3624579022810883</v>
+        <v>0.3624579022810793</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.4327335632893035</v>
+        <v>0.4327335632893101</v>
       </c>
     </row>
   </sheetData>
@@ -2638,85 +2638,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.846200510321925</v>
+        <v>0.8462005103219219</v>
       </c>
       <c r="C2" t="n">
         <v>0.9564663015044796</v>
       </c>
       <c r="D2" t="n">
-        <v>1.260349048039918</v>
+        <v>1.260349048039914</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5455514366598238</v>
+        <v>0.5455514366598267</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7619345393056359</v>
+        <v>0.7619345393056353</v>
       </c>
       <c r="G2" t="n">
-        <v>2.69687082320314</v>
+        <v>2.696870823203144</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4429054816331559</v>
+        <v>0.4429054816331489</v>
       </c>
       <c r="I2" t="n">
-        <v>3.25244051813895</v>
+        <v>3.252440518138941</v>
       </c>
       <c r="J2" t="n">
-        <v>1.818917156924727</v>
+        <v>1.81891715692473</v>
       </c>
       <c r="K2" t="n">
-        <v>1.523076854739511</v>
+        <v>1.523076854739503</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5683716269699663</v>
+        <v>0.5683716269699662</v>
       </c>
       <c r="M2" t="n">
-        <v>2.436353410027664</v>
+        <v>2.436353410027667</v>
       </c>
       <c r="N2" t="n">
-        <v>1.10428179947595</v>
+        <v>1.104281799475942</v>
       </c>
       <c r="O2" t="n">
-        <v>1.200281197286268</v>
+        <v>1.200281197286263</v>
       </c>
       <c r="P2" t="n">
-        <v>1.436087897431836</v>
+        <v>1.436087897431834</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.382271009773646</v>
+        <v>2.382271009773643</v>
       </c>
       <c r="R2" t="n">
-        <v>0.5940124318643037</v>
+        <v>0.5940124318642982</v>
       </c>
       <c r="S2" t="n">
-        <v>1.552919719492718</v>
+        <v>1.552919719492711</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8053644939519885</v>
+        <v>0.805364493951984</v>
       </c>
       <c r="U2" t="n">
-        <v>1.044390165867582</v>
+        <v>1.044390165867575</v>
       </c>
       <c r="V2" t="n">
-        <v>1.198836897374528</v>
+        <v>1.198836897374546</v>
       </c>
       <c r="W2" t="n">
-        <v>1.182841045163233</v>
+        <v>1.18284104516322</v>
       </c>
       <c r="X2" t="n">
-        <v>1.194945011687048</v>
+        <v>1.194945011687043</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.908185581824101</v>
+        <v>1.9081855818241</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.369591648201449</v>
+        <v>1.369591648201443</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.009557754963368</v>
+        <v>1.009557754963361</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.427778462725094</v>
+        <v>2.427778462725088</v>
       </c>
     </row>
     <row r="3">
@@ -2726,85 +2726,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5500119019568436</v>
+        <v>0.5500119019568522</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7633854188513656</v>
+        <v>0.7633854188513638</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7532471008127494</v>
+        <v>0.7532471008127574</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6363166698225509</v>
+        <v>0.6363166698225519</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5753395001401304</v>
+        <v>0.5753395001401291</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7953892432163485</v>
+        <v>0.7953892432163497</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7532471008127494</v>
+        <v>0.7532471008127574</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7532471008127494</v>
+        <v>0.7532471008127574</v>
       </c>
       <c r="J3" t="n">
-        <v>0.74894433283561</v>
+        <v>0.7489443328356207</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7532471008127494</v>
+        <v>0.7532471008127574</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7532471008127494</v>
+        <v>0.7532471008127574</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7593957464479484</v>
+        <v>0.7593957464479448</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5957058210605092</v>
+        <v>0.5957058210605097</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6389995323633502</v>
+        <v>0.6389995323633767</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6283871976328377</v>
+        <v>0.6283871976328411</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5100715469170743</v>
+        <v>0.510071546917088</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7532471008127494</v>
+        <v>0.7532471008127574</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7532471008127494</v>
+        <v>0.7532471008127574</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7532471008127494</v>
+        <v>0.7532471008127574</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6525915429922398</v>
+        <v>0.6525915429922833</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6853132685277845</v>
+        <v>0.6853132685277927</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7532870418153395</v>
+        <v>0.7532870418153542</v>
       </c>
       <c r="X3" t="n">
-        <v>0.528698456395257</v>
+        <v>0.5286984563952662</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.9528230184834517</v>
+        <v>0.952823018483439</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.5462367038477035</v>
+        <v>0.5462367038477034</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.7532471008127494</v>
+        <v>0.7532471008127574</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9654734766494384</v>
+        <v>0.965473476649426</v>
       </c>
     </row>
     <row r="4">
@@ -2814,85 +2814,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.556647491959762</v>
+        <v>1.556647491959757</v>
       </c>
       <c r="C4" t="n">
-        <v>1.603281098203187</v>
+        <v>1.603281098203193</v>
       </c>
       <c r="D4" t="n">
-        <v>1.707599770780311</v>
+        <v>1.707599770780306</v>
       </c>
       <c r="E4" t="n">
-        <v>1.441526787280575</v>
+        <v>1.441526787280582</v>
       </c>
       <c r="F4" t="n">
-        <v>1.521908158857489</v>
+        <v>1.521908158857496</v>
       </c>
       <c r="G4" t="n">
-        <v>2.231195089336965</v>
+        <v>2.23119508933697</v>
       </c>
       <c r="H4" t="n">
-        <v>1.409651189732028</v>
+        <v>1.409651189732018</v>
       </c>
       <c r="I4" t="n">
-        <v>2.433693719312334</v>
+        <v>2.433693719312328</v>
       </c>
       <c r="J4" t="n">
-        <v>1.881963795219908</v>
+        <v>1.88196379521992</v>
       </c>
       <c r="K4" t="n">
-        <v>1.803360971216644</v>
+        <v>1.80336097121664</v>
       </c>
       <c r="L4" t="n">
-        <v>1.455382126409437</v>
+        <v>1.455382126409432</v>
       </c>
       <c r="M4" t="n">
-        <v>2.140147087888232</v>
+        <v>2.140147087888243</v>
       </c>
       <c r="N4" t="n">
-        <v>1.6507150913129</v>
+        <v>1.650715091312897</v>
       </c>
       <c r="O4" t="n">
-        <v>1.685705744532919</v>
+        <v>1.685705744532912</v>
       </c>
       <c r="P4" t="n">
-        <v>1.771654517753908</v>
+        <v>1.771654517753903</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.116527151559435</v>
+        <v>2.116527151559433</v>
       </c>
       <c r="R4" t="n">
-        <v>1.464727898703886</v>
+        <v>1.464727898703884</v>
       </c>
       <c r="S4" t="n">
-        <v>1.814238344986575</v>
+        <v>1.814238344986576</v>
       </c>
       <c r="T4" t="n">
-        <v>1.54176324351363</v>
+        <v>1.541763243513626</v>
       </c>
       <c r="U4" t="n">
         <v>1.628885294145715</v>
       </c>
       <c r="V4" t="n">
-        <v>1.501575608668388</v>
+        <v>1.501575608668428</v>
       </c>
       <c r="W4" t="n">
-        <v>1.67934901387668</v>
+        <v>1.679349013876674</v>
       </c>
       <c r="X4" t="n">
-        <v>1.683760767542658</v>
+        <v>1.683760767542654</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.943728580063991</v>
+        <v>1.943728580063983</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.74741741574781</v>
+        <v>1.747417415747808</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.616189289393952</v>
+        <v>1.616189289393948</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.133069735801317</v>
+        <v>2.13306973580132</v>
       </c>
     </row>
     <row r="5">
@@ -2902,46 +2902,46 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.448690222232928</v>
+        <v>1.448690222232926</v>
       </c>
       <c r="C5" t="n">
-        <v>1.532905383746318</v>
+        <v>1.532905383746327</v>
       </c>
       <c r="D5" t="n">
-        <v>1.522767065707708</v>
+        <v>1.522767065707727</v>
       </c>
       <c r="E5" t="n">
-        <v>1.474609648949209</v>
+        <v>1.474609648949218</v>
       </c>
       <c r="F5" t="n">
-        <v>1.453896458191237</v>
+        <v>1.453896458191245</v>
       </c>
       <c r="G5" t="n">
-        <v>1.538127381755798</v>
+        <v>1.538127381755825</v>
       </c>
       <c r="H5" t="n">
-        <v>1.522767065707708</v>
+        <v>1.522767065707727</v>
       </c>
       <c r="I5" t="n">
-        <v>1.522767065707708</v>
+        <v>1.522767065707727</v>
       </c>
       <c r="J5" t="n">
-        <v>1.491971265094667</v>
+        <v>1.491971265094683</v>
       </c>
       <c r="K5" t="n">
-        <v>1.522767065707708</v>
+        <v>1.522767065707727</v>
       </c>
       <c r="L5" t="n">
-        <v>1.522767065707708</v>
+        <v>1.522767065707727</v>
       </c>
       <c r="M5" t="n">
-        <v>1.528915711344506</v>
+        <v>1.528915711344517</v>
       </c>
       <c r="N5" t="n">
-        <v>1.465345119181125</v>
+        <v>1.465345119181148</v>
       </c>
       <c r="O5" t="n">
-        <v>1.481125168570592</v>
+        <v>1.481125168570608</v>
       </c>
       <c r="P5" t="n">
         <v>1.477257097177637</v>
@@ -2950,34 +2950,34 @@
         <v>1.434132431824257</v>
       </c>
       <c r="R5" t="n">
-        <v>1.522767065707708</v>
+        <v>1.522767065707727</v>
       </c>
       <c r="S5" t="n">
-        <v>1.522767065707708</v>
+        <v>1.522767065707727</v>
       </c>
       <c r="T5" t="n">
-        <v>1.522767065707708</v>
+        <v>1.522767065707727</v>
       </c>
       <c r="U5" t="n">
-        <v>1.486079296839368</v>
+        <v>1.486079296839381</v>
       </c>
       <c r="V5" t="n">
-        <v>1.314402276052644</v>
+        <v>1.314402276052634</v>
       </c>
       <c r="W5" t="n">
-        <v>1.522781623734146</v>
+        <v>1.522781623734165</v>
       </c>
       <c r="X5" t="n">
-        <v>1.440921721600845</v>
+        <v>1.440921721600872</v>
       </c>
       <c r="Y5" t="n">
         <v>1.595510144159928</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.447314206852759</v>
+        <v>1.447314206852753</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.522767065707708</v>
+        <v>1.522767065707727</v>
       </c>
       <c r="AB5" t="n">
         <v>1.600076739628823</v>
@@ -2990,85 +2990,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.4657819108989888</v>
+        <v>0.4657819108989826</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5124155171424177</v>
+        <v>0.512415517142417</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6167341897195364</v>
+        <v>0.6167341897195281</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3506612062198062</v>
+        <v>0.3506612062198067</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4310425777967219</v>
+        <v>0.4310425777967227</v>
       </c>
       <c r="G6" t="n">
-        <v>1.12924212929671</v>
+        <v>1.1292421292967</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3187856086712573</v>
+        <v>0.3187856086712468</v>
       </c>
       <c r="I6" t="n">
-        <v>1.342828138251564</v>
+        <v>1.342828138251553</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8069018078969186</v>
+        <v>0.8069018078969368</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7124953901558714</v>
+        <v>0.7124953901558624</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3645165453486633</v>
+        <v>0.364516545348655</v>
       </c>
       <c r="M6" t="n">
-        <v>1.049281506827464</v>
+        <v>1.04928150682747</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5598495102521295</v>
+        <v>0.5598495102521198</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5837527844926615</v>
+        <v>0.5837527844926507</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6697015577136518</v>
+        <v>0.6697015577136363</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.025661570498666</v>
+        <v>1.025661570498658</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3738623176431199</v>
+        <v>0.3738623176431066</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7233727639258051</v>
+        <v>0.723372763925796</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4508976624528636</v>
+        <v>0.4508976624528552</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5269323341054614</v>
+        <v>0.5269323341054505</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5769459689779142</v>
+        <v>0.5769459689779275</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5773960538364211</v>
+        <v>0.577396053836409</v>
       </c>
       <c r="X6" t="n">
-        <v>0.5818078075023997</v>
+        <v>0.5818078075023903</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.8528629990032158</v>
+        <v>0.8528629990032074</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.6565518346870418</v>
+        <v>0.6565518346870307</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.5253237083331818</v>
+        <v>0.5253237083331724</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.042204154740551</v>
+        <v>1.042204154740541</v>
       </c>
     </row>
     <row r="7">
@@ -3078,85 +3078,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3578246411721614</v>
+        <v>0.3578246411721507</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4420398026855527</v>
+        <v>0.4420398026855511</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4319014846469392</v>
+        <v>0.4319014846469558</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3837440678884396</v>
+        <v>0.3837440678884409</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3630308771304692</v>
+        <v>0.3630308771304686</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4361744217155363</v>
+        <v>0.4361744217155589</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4319014846469392</v>
+        <v>0.4319014846469558</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4319014846469392</v>
+        <v>0.4319014846469558</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4169092777716857</v>
+        <v>0.4169092777716894</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4319014846469392</v>
+        <v>0.4319014846469558</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4319014846469392</v>
+        <v>0.4319014846469558</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4380501302837382</v>
+        <v>0.438050130283741</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3744795381203537</v>
+        <v>0.3744795381203698</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3791722085303341</v>
+        <v>0.3791722085303419</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3753041371373833</v>
+        <v>0.3753041371373735</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3432668507634901</v>
+        <v>0.3432668507634838</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4319014846469392</v>
+        <v>0.4319014846469558</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4319014846469392</v>
+        <v>0.4319014846469558</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4319014846469392</v>
+        <v>0.4319014846469558</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3841263367991134</v>
+        <v>0.3841263367991158</v>
       </c>
       <c r="V7" t="n">
-        <v>0.389772636362168</v>
+        <v>0.3897726363621739</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4208286636938867</v>
+        <v>0.4208286636939007</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3389687615605884</v>
+        <v>0.3389687615606043</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5046445630991626</v>
+        <v>0.5046445630991525</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.3564486257919882</v>
+        <v>0.3564486257919836</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.4319014846469392</v>
+        <v>0.4319014846469558</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.5092111585680573</v>
+        <v>0.5092111585680534</v>
       </c>
     </row>
   </sheetData>
@@ -3322,85 +3322,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.937780675385941</v>
+        <v>0.9377806753854947</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6025667624275894</v>
+        <v>0.6025667624275881</v>
       </c>
       <c r="D2" t="n">
-        <v>1.150491186831265</v>
+        <v>1.150491186830831</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2176138411876573</v>
+        <v>0.2176138411876578</v>
       </c>
       <c r="F2" t="n">
-        <v>1.244582964449479</v>
+        <v>1.244582964449478</v>
       </c>
       <c r="G2" t="n">
-        <v>2.631035950426689</v>
+        <v>2.631035950426268</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5435020159198981</v>
+        <v>0.5435020159194554</v>
       </c>
       <c r="I2" t="n">
-        <v>2.377285901110506</v>
+        <v>2.377285901110061</v>
       </c>
       <c r="J2" t="n">
-        <v>1.833141522639052</v>
+        <v>1.833141522638909</v>
       </c>
       <c r="K2" t="n">
-        <v>1.660758509663821</v>
+        <v>1.660758509663415</v>
       </c>
       <c r="L2" t="n">
-        <v>0.851529626449575</v>
+        <v>0.8515296264493446</v>
       </c>
       <c r="M2" t="n">
-        <v>2.304514663899825</v>
+        <v>2.304514663899834</v>
       </c>
       <c r="N2" t="n">
-        <v>1.108831063712614</v>
+        <v>1.108831063712173</v>
       </c>
       <c r="O2" t="n">
-        <v>1.162525675398995</v>
+        <v>1.162525675398545</v>
       </c>
       <c r="P2" t="n">
-        <v>1.517808593755255</v>
+        <v>1.517808593755071</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.729564450294278</v>
+        <v>1.729564450293842</v>
       </c>
       <c r="R2" t="n">
-        <v>1.726169877854159</v>
+        <v>1.726169877853713</v>
       </c>
       <c r="S2" t="n">
-        <v>1.713414586525167</v>
+        <v>1.713414586524864</v>
       </c>
       <c r="T2" t="n">
-        <v>1.342384772195357</v>
+        <v>1.342384772194922</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9519149827465687</v>
+        <v>0.9519149827461246</v>
       </c>
       <c r="V2" t="n">
-        <v>1.386673859876695</v>
+        <v>1.386673859876683</v>
       </c>
       <c r="W2" t="n">
-        <v>1.317321763023707</v>
+        <v>1.317321763023262</v>
       </c>
       <c r="X2" t="n">
-        <v>1.510699955561705</v>
+        <v>1.510699955561422</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.910725093363135</v>
+        <v>2.910725093362953</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.479355676675199</v>
+        <v>1.47935567667497</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.186533448533583</v>
+        <v>1.186533448533133</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.458699894500568</v>
+        <v>2.45869989450057</v>
       </c>
     </row>
     <row r="3">
@@ -3410,85 +3410,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6001640262568791</v>
+        <v>0.60016402625674</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8286825295122363</v>
+        <v>0.8286825295122352</v>
       </c>
       <c r="D3" t="n">
-        <v>0.8191357654279933</v>
+        <v>0.819135765427584</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6919850911930554</v>
+        <v>0.691985091193054</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6288166289178281</v>
+        <v>0.6288166289178267</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8645409819670787</v>
+        <v>0.8645409819666664</v>
       </c>
       <c r="H3" t="n">
-        <v>0.8191357654279933</v>
+        <v>0.819135765427584</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8191357654279933</v>
+        <v>0.819135765427584</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8144672154481344</v>
+        <v>0.8144672154481373</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8191357654279933</v>
+        <v>0.819135765427584</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8191357654279933</v>
+        <v>0.819135765427584</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8240413354090336</v>
+        <v>0.8240413354090426</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6493960342246259</v>
+        <v>0.6493960342245373</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6960419858201127</v>
+        <v>0.6960419858196911</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6846079360021521</v>
+        <v>0.6846079360016961</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5571310819228948</v>
+        <v>0.5571310819227268</v>
       </c>
       <c r="R3" t="n">
-        <v>0.8191357654279933</v>
+        <v>0.819135765427584</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8191357654279933</v>
+        <v>0.819135765427584</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8191357654279933</v>
+        <v>0.819135765427584</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7127427773422067</v>
+        <v>0.7127427773417968</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7483594279251745</v>
+        <v>0.748359427925155</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8191787989501659</v>
+        <v>0.8191787989498165</v>
       </c>
       <c r="X3" t="n">
-        <v>0.5772002764899942</v>
+        <v>0.5772002764899232</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.037682699209875</v>
+        <v>1.037682699209579</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.5960965138489221</v>
+        <v>0.5960965138485341</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.8191357654279933</v>
+        <v>0.819135765427584</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.047208736598078</v>
+        <v>1.047208736598074</v>
       </c>
     </row>
     <row r="4">
@@ -3498,85 +3498,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.662449810082345</v>
+        <v>1.662449810082073</v>
       </c>
       <c r="C4" t="n">
-        <v>1.546335355768997</v>
+        <v>1.546335355768973</v>
       </c>
       <c r="D4" t="n">
-        <v>1.739980293731233</v>
+        <v>1.739980293730963</v>
       </c>
       <c r="E4" t="n">
-        <v>1.393249830949264</v>
+        <v>1.393249830949231</v>
       </c>
       <c r="F4" t="n">
-        <v>1.770805344096452</v>
+        <v>1.77080534409641</v>
       </c>
       <c r="G4" t="n">
-        <v>2.279621474627384</v>
+        <v>2.279621474627133</v>
       </c>
       <c r="H4" t="n">
-        <v>1.518739868560738</v>
+        <v>1.518739868560471</v>
       </c>
       <c r="I4" t="n">
-        <v>2.18713256133516</v>
+        <v>2.187132561334893</v>
       </c>
       <c r="J4" t="n">
-        <v>1.955521256259949</v>
+        <v>1.9555212562598</v>
       </c>
       <c r="K4" t="n">
-        <v>1.925966741042303</v>
+        <v>1.92596674104202</v>
       </c>
       <c r="L4" t="n">
-        <v>1.631012315555987</v>
+        <v>1.631012315555796</v>
       </c>
       <c r="M4" t="n">
-        <v>2.163725847223812</v>
+        <v>2.163725847223789</v>
       </c>
       <c r="N4" t="n">
-        <v>1.724795668052346</v>
+        <v>1.724795668052077</v>
       </c>
       <c r="O4" t="n">
-        <v>1.744366723498068</v>
+        <v>1.744366723497797</v>
       </c>
       <c r="P4" t="n">
-        <v>1.873863175296193</v>
+        <v>1.873863175296089</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.951045698441935</v>
+        <v>1.951045698441664</v>
       </c>
       <c r="R4" t="n">
-        <v>1.949808416648587</v>
+        <v>1.949808416648318</v>
       </c>
       <c r="S4" t="n">
-        <v>1.945159262739553</v>
+        <v>1.945159262739146</v>
       </c>
       <c r="T4" t="n">
-        <v>1.809923252268201</v>
+        <v>1.80992325226793</v>
       </c>
       <c r="U4" t="n">
-        <v>1.667601599141871</v>
+        <v>1.667601599141604</v>
       </c>
       <c r="V4" t="n">
-        <v>1.616560267921855</v>
+        <v>1.616560267921544</v>
       </c>
       <c r="W4" t="n">
-        <v>1.800788079729829</v>
+        <v>1.800788079729573</v>
       </c>
       <c r="X4" t="n">
-        <v>1.871272160148596</v>
+        <v>1.87127216014835</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.381564882952027</v>
+        <v>2.381564882951821</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.85984753855772</v>
+        <v>1.859847538557343</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.753117274892111</v>
+        <v>1.753117274891849</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.216386729388055</v>
+        <v>2.216386729388018</v>
       </c>
     </row>
     <row r="5">
@@ -3586,85 +3586,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.539392505969846</v>
+        <v>1.539392505969494</v>
       </c>
       <c r="C5" t="n">
-        <v>1.628751897685968</v>
+        <v>1.628751897685936</v>
       </c>
       <c r="D5" t="n">
-        <v>1.619205133601505</v>
+        <v>1.619205133601286</v>
       </c>
       <c r="E5" t="n">
-        <v>1.566152581227797</v>
+        <v>1.566152581227746</v>
       </c>
       <c r="F5" t="n">
-        <v>1.546365745488515</v>
+        <v>1.546365745488498</v>
       </c>
       <c r="G5" t="n">
-        <v>1.635754801855212</v>
+        <v>1.63575480185481</v>
       </c>
       <c r="H5" t="n">
-        <v>1.619205133601505</v>
+        <v>1.619205133601286</v>
       </c>
       <c r="I5" t="n">
-        <v>1.619205133601505</v>
+        <v>1.619205133601286</v>
       </c>
       <c r="J5" t="n">
-        <v>1.584226433166476</v>
+        <v>1.584226433166406</v>
       </c>
       <c r="K5" t="n">
-        <v>1.619205133601505</v>
+        <v>1.619205133601286</v>
       </c>
       <c r="L5" t="n">
-        <v>1.619205133601505</v>
+        <v>1.619205133601286</v>
       </c>
       <c r="M5" t="n">
-        <v>1.62411070358445</v>
+        <v>1.624110703584429</v>
       </c>
       <c r="N5" t="n">
-        <v>1.557336994762706</v>
+        <v>1.55733699476233</v>
       </c>
       <c r="O5" t="n">
-        <v>1.574338896374631</v>
+        <v>1.574338896374346</v>
       </c>
       <c r="P5" t="n">
-        <v>1.570171319481345</v>
+        <v>1.570171319481078</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.523707503078552</v>
+        <v>1.52370750307809</v>
       </c>
       <c r="R5" t="n">
-        <v>1.619205133601505</v>
+        <v>1.619205133601286</v>
       </c>
       <c r="S5" t="n">
-        <v>1.619205133601505</v>
+        <v>1.619205133601286</v>
       </c>
       <c r="T5" t="n">
-        <v>1.619205133601505</v>
+        <v>1.619205133601286</v>
       </c>
       <c r="U5" t="n">
-        <v>1.580426138773925</v>
+        <v>1.580426138773559</v>
       </c>
       <c r="V5" t="n">
-        <v>1.383902152942</v>
+        <v>1.383902152942023</v>
       </c>
       <c r="W5" t="n">
-        <v>1.619220818815229</v>
+        <v>1.619220818814814</v>
       </c>
       <c r="X5" t="n">
-        <v>1.531022488833768</v>
+        <v>1.531022488833452</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.698862924657304</v>
+        <v>1.698862924657159</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.537909945460154</v>
+        <v>1.537909945459843</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.619205133601505</v>
+        <v>1.619205133601286</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.701914776898577</v>
+        <v>1.701914776898549</v>
       </c>
     </row>
     <row r="6">
@@ -3674,82 +3674,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5167402180392409</v>
+        <v>0.5167402180388897</v>
       </c>
       <c r="C6" t="n">
-        <v>0.4006257637257927</v>
+        <v>0.4006257637257925</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5942707016881275</v>
+        <v>0.5942707016877824</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2475402389060494</v>
+        <v>0.2475402389060496</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6250957520532302</v>
+        <v>0.6250957520532289</v>
       </c>
       <c r="G6" t="n">
-        <v>1.121378760948728</v>
+        <v>1.121378760948259</v>
       </c>
       <c r="H6" t="n">
-        <v>0.373030276517641</v>
+        <v>0.3730302765172895</v>
       </c>
       <c r="I6" t="n">
-        <v>1.041422969292057</v>
+        <v>1.041422969291712</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8280581303952605</v>
+        <v>0.8280581303951656</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7802571489991523</v>
+        <v>0.7802571489988385</v>
       </c>
       <c r="L6" t="n">
-        <v>0.485302723512855</v>
+        <v>0.4853027235126148</v>
       </c>
       <c r="M6" t="n">
-        <v>1.018016255180599</v>
+        <v>1.018016255180595</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5790860760092421</v>
+        <v>0.5790860760088963</v>
       </c>
       <c r="O6" t="n">
-        <v>0.5861240098193677</v>
+        <v>0.586124009818922</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7156204616175575</v>
+        <v>0.7156204616172148</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.8053361063988221</v>
+        <v>0.8053361063984822</v>
       </c>
       <c r="R6" t="n">
-        <v>0.804098824605491</v>
+        <v>0.8040988246051367</v>
       </c>
       <c r="S6" t="n">
-        <v>0.7994496706963478</v>
+        <v>0.7994496706959645</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6642136602251112</v>
+        <v>0.6642136602247486</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5093588854631877</v>
+        <v>0.5093588854627302</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6612310180463296</v>
+        <v>0.6612310180463202</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6425453660511488</v>
+        <v>0.6425453660506978</v>
       </c>
       <c r="X6" t="n">
-        <v>0.7130294464697073</v>
+        <v>0.7130294464694741</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.235855290908863</v>
+        <v>1.23585529090864</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.714137946514501</v>
+        <v>0.7141379465141616</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.607407682849015</v>
+        <v>0.6074076828486671</v>
       </c>
       <c r="AB6" t="n">
         <v>1.070677137344836</v>
@@ -3762,85 +3762,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3936829139264368</v>
+        <v>0.3936829139263119</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4830423056427551</v>
+        <v>0.4830423056427545</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4734955415584706</v>
+        <v>0.4734955415581041</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4204429891845654</v>
+        <v>0.4204429891845649</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4006561534453182</v>
+        <v>0.4006561534453163</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4775120881761343</v>
+        <v>0.4775120881759353</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4734955415584706</v>
+        <v>0.4734955415581041</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4734955415584706</v>
+        <v>0.4734955415581041</v>
       </c>
       <c r="J7" t="n">
-        <v>0.456763307301823</v>
+        <v>0.45676330730177</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4734955415584706</v>
+        <v>0.4734955415581041</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4734955415584706</v>
+        <v>0.4734955415581041</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4784011115412376</v>
+        <v>0.4784011115412362</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4116274027192967</v>
+        <v>0.4116274027191487</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4160961826957801</v>
+        <v>0.4160961826954716</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4119286058025376</v>
+        <v>0.4119286058022041</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3779979110351486</v>
+        <v>0.3779979110349088</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4734955415584706</v>
+        <v>0.4734955415581041</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4734955415584706</v>
+        <v>0.4734955415581041</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4734955415584706</v>
+        <v>0.4734955415581041</v>
       </c>
       <c r="U7" t="n">
-        <v>0.422183425095333</v>
+        <v>0.4221834250946835</v>
       </c>
       <c r="V7" t="n">
-        <v>0.428572903066479</v>
+        <v>0.4285729030664782</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4609781051361554</v>
+        <v>0.4609781051359394</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3727797751549181</v>
+        <v>0.3727797751545783</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5531533326142901</v>
+        <v>0.5531533326139776</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.3922003534170897</v>
+        <v>0.3922003534166628</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.4734955415584706</v>
+        <v>0.4734955415581041</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.5562051848553689</v>
+        <v>0.5562051848553671</v>
       </c>
     </row>
   </sheetData>
@@ -4006,85 +4006,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.043063047781435</v>
+        <v>1.043063047781448</v>
       </c>
       <c r="C2" t="n">
-        <v>1.390040033575685</v>
+        <v>1.390040033575683</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7004946195881981</v>
+        <v>0.7004946195882097</v>
       </c>
       <c r="E2" t="n">
-        <v>3.996694337225481</v>
+        <v>3.996694337225497</v>
       </c>
       <c r="F2" t="n">
-        <v>2.494652530795356</v>
+        <v>2.494652530795362</v>
       </c>
       <c r="G2" t="n">
-        <v>1.430825217836522</v>
+        <v>1.43082521783654</v>
       </c>
       <c r="H2" t="n">
-        <v>1.122156803756855</v>
+        <v>1.122156803756869</v>
       </c>
       <c r="I2" t="n">
-        <v>2.327695387945636</v>
+        <v>2.327695387945647</v>
       </c>
       <c r="J2" t="n">
-        <v>1.545172797617236</v>
+        <v>1.545172797617237</v>
       </c>
       <c r="K2" t="n">
-        <v>2.478903982813879</v>
+        <v>2.478903982813898</v>
       </c>
       <c r="L2" t="n">
-        <v>4.430412371193631</v>
+        <v>4.430412371193646</v>
       </c>
       <c r="M2" t="n">
-        <v>1.653660605028654</v>
+        <v>1.653660605028651</v>
       </c>
       <c r="N2" t="n">
-        <v>1.438834934209211</v>
+        <v>1.438834934209225</v>
       </c>
       <c r="O2" t="n">
-        <v>0.69177718745281</v>
+        <v>0.6917771874528158</v>
       </c>
       <c r="P2" t="n">
-        <v>1.007831827196125</v>
+        <v>1.007831827196138</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.180709041576118</v>
+        <v>2.180709041576129</v>
       </c>
       <c r="R2" t="n">
-        <v>2.506322790823797</v>
+        <v>2.506322790823812</v>
       </c>
       <c r="S2" t="n">
-        <v>3.02589852223133</v>
+        <v>3.025898522231349</v>
       </c>
       <c r="T2" t="n">
-        <v>1.125020322434017</v>
+        <v>1.125020322434027</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9051523178653371</v>
+        <v>0.905152317865353</v>
       </c>
       <c r="V2" t="n">
-        <v>1.142838919272079</v>
+        <v>1.142838919272078</v>
       </c>
       <c r="W2" t="n">
-        <v>1.15352000721549</v>
+        <v>1.153520007215511</v>
       </c>
       <c r="X2" t="n">
-        <v>2.187261715064293</v>
+        <v>2.187261715064305</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.9123329831127028</v>
+        <v>0.9123329831127216</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.333807975157569</v>
+        <v>1.333807975157589</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.7660375490676931</v>
+        <v>0.7660375490677042</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.061128862251262</v>
+        <v>1.06112886225127</v>
       </c>
     </row>
     <row r="3">
@@ -4094,85 +4094,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5697869096401503</v>
+        <v>0.5697869096401615</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7910852834833932</v>
+        <v>0.7910852834834035</v>
       </c>
       <c r="D3" t="n">
-        <v>0.7793982319846183</v>
+        <v>0.7793982319846432</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6654727436586976</v>
+        <v>0.6654727436586932</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6019029726475056</v>
+        <v>0.6019029726475046</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8228625051363248</v>
+        <v>0.8228625051363309</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7793982319846183</v>
+        <v>0.7793982319846432</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7793982319846183</v>
+        <v>0.7793982319846432</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7748974246198217</v>
+        <v>0.7748974246198223</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7793982319846183</v>
+        <v>0.7793982319846432</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7793982319846183</v>
+        <v>0.7793982319846432</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7832460141571587</v>
+        <v>0.7832460141571614</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6169143898384167</v>
+        <v>0.6169143898384203</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6615663602224852</v>
+        <v>0.6615663602224943</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6506210833668323</v>
+        <v>0.6506210833668474</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5285935007966588</v>
+        <v>0.5285935007966608</v>
       </c>
       <c r="R3" t="n">
-        <v>0.7793982319846183</v>
+        <v>0.7793982319846432</v>
       </c>
       <c r="S3" t="n">
-        <v>0.7793982319846183</v>
+        <v>0.7793982319846432</v>
       </c>
       <c r="T3" t="n">
-        <v>0.7793982319846183</v>
+        <v>0.7793982319846432</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6768635466590945</v>
+        <v>0.6768635466590975</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7108683526718196</v>
+        <v>0.710868352671814</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7794394261176033</v>
+        <v>0.7794394261176105</v>
       </c>
       <c r="X3" t="n">
-        <v>0.5478047946872563</v>
+        <v>0.5478047946872607</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.9874230426137017</v>
+        <v>0.9874230426137006</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.5658932717611654</v>
+        <v>0.5658932717611822</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.7793982319846183</v>
+        <v>0.7793982319846432</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9933477656926155</v>
+        <v>0.9933477656926164</v>
       </c>
     </row>
     <row r="4">
@@ -4182,85 +4182,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.613715898473944</v>
+        <v>1.613715898473973</v>
       </c>
       <c r="C4" t="n">
-        <v>1.747612193850244</v>
+        <v>1.747612193850247</v>
       </c>
       <c r="D4" t="n">
-        <v>1.488853729039098</v>
+        <v>1.48885372903911</v>
       </c>
       <c r="E4" t="n">
-        <v>2.68880947324826</v>
+        <v>2.688809473248274</v>
       </c>
       <c r="F4" t="n">
-        <v>2.142460722515131</v>
+        <v>2.14246072251514</v>
       </c>
       <c r="G4" t="n">
-        <v>1.755050656125737</v>
+        <v>1.755050656125758</v>
       </c>
       <c r="H4" t="n">
-        <v>1.642544643761215</v>
+        <v>1.642544643761244</v>
       </c>
       <c r="I4" t="n">
-        <v>2.081949301549249</v>
+        <v>2.081949301549283</v>
       </c>
       <c r="J4" t="n">
-        <v>1.771115779669514</v>
+        <v>1.771115779669526</v>
       </c>
       <c r="K4" t="n">
-        <v>2.137063058797763</v>
+        <v>2.137063058797786</v>
       </c>
       <c r="L4" t="n">
-        <v>2.848364950593723</v>
+        <v>2.848364950593739</v>
       </c>
       <c r="M4" t="n">
-        <v>1.838716848846701</v>
+        <v>1.83871684884671</v>
       </c>
       <c r="N4" t="n">
-        <v>1.757970103688747</v>
+        <v>1.757970103688769</v>
       </c>
       <c r="O4" t="n">
-        <v>1.485676327390996</v>
+        <v>1.485676327391014</v>
       </c>
       <c r="P4" t="n">
-        <v>1.600874532276498</v>
+        <v>1.600874532276502</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.028374504298384</v>
+        <v>2.028374504298405</v>
       </c>
       <c r="R4" t="n">
-        <v>2.14705689234948</v>
+        <v>2.147056892349504</v>
       </c>
       <c r="S4" t="n">
-        <v>2.336436145281249</v>
+        <v>2.336436145281273</v>
       </c>
       <c r="T4" t="n">
-        <v>1.643588362693901</v>
+        <v>1.643588362693927</v>
       </c>
       <c r="U4" t="n">
-        <v>1.563449056849085</v>
+        <v>1.563449056849105</v>
       </c>
       <c r="V4" t="n">
-        <v>1.491296926128693</v>
+        <v>1.491296926128696</v>
       </c>
       <c r="W4" t="n">
-        <v>1.653976163136568</v>
+        <v>1.653976163136578</v>
       </c>
       <c r="X4" t="n">
-        <v>2.030762876839449</v>
+        <v>2.030762876839475</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.566066325012121</v>
+        <v>1.56606632501214</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.719689010403239</v>
+        <v>1.719689010403264</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.512743357190429</v>
+        <v>1.512743357190458</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.617118656072921</v>
+        <v>1.617118656072922</v>
       </c>
     </row>
     <row r="5">
@@ -4270,85 +4270,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.441212303610459</v>
+        <v>1.441212303610477</v>
       </c>
       <c r="C5" t="n">
-        <v>1.529300220723374</v>
+        <v>1.529300220723385</v>
       </c>
       <c r="D5" t="n">
-        <v>1.517613169224599</v>
+        <v>1.517613169224614</v>
       </c>
       <c r="E5" t="n">
-        <v>1.474618319572059</v>
+        <v>1.474618319572067</v>
       </c>
       <c r="F5" t="n">
         <v>1.452575734357685</v>
       </c>
       <c r="G5" t="n">
-        <v>1.533455386405122</v>
+        <v>1.533455386405146</v>
       </c>
       <c r="H5" t="n">
-        <v>1.517613169224599</v>
+        <v>1.517613169224614</v>
       </c>
       <c r="I5" t="n">
-        <v>1.517613169224599</v>
+        <v>1.517613169224614</v>
       </c>
       <c r="J5" t="n">
-        <v>1.49035945124205</v>
+        <v>1.490359451242055</v>
       </c>
       <c r="K5" t="n">
-        <v>1.517613169224599</v>
+        <v>1.517613169224614</v>
       </c>
       <c r="L5" t="n">
-        <v>1.517613169224599</v>
+        <v>1.517613169224614</v>
       </c>
       <c r="M5" t="n">
-        <v>1.521460951398199</v>
+        <v>1.521460951398212</v>
       </c>
       <c r="N5" t="n">
-        <v>1.45838971674391</v>
+        <v>1.458389716743925</v>
       </c>
       <c r="O5" t="n">
-        <v>1.474664835618991</v>
+        <v>1.474664835619016</v>
       </c>
       <c r="P5" t="n">
-        <v>1.470675410731037</v>
+        <v>1.470675410731059</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.42619778980442</v>
+        <v>1.426197789804443</v>
       </c>
       <c r="R5" t="n">
-        <v>1.517613169224599</v>
+        <v>1.517613169224614</v>
       </c>
       <c r="S5" t="n">
-        <v>1.517613169224599</v>
+        <v>1.517613169224614</v>
       </c>
       <c r="T5" t="n">
-        <v>1.517613169224599</v>
+        <v>1.517613169224614</v>
       </c>
       <c r="U5" t="n">
-        <v>1.480240480446501</v>
+        <v>1.480240480446521</v>
       </c>
       <c r="V5" t="n">
-        <v>1.333848727057393</v>
+        <v>1.333848727057396</v>
       </c>
       <c r="W5" t="n">
-        <v>1.517628184002354</v>
+        <v>1.517628184002359</v>
       </c>
       <c r="X5" t="n">
-        <v>1.43320008083715</v>
+        <v>1.433200080837158</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.593435769948234</v>
+        <v>1.593435769948254</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.439793118324966</v>
+        <v>1.439793118324992</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.517613169224599</v>
+        <v>1.517613169224614</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.592413242303108</v>
+        <v>1.592413242303118</v>
       </c>
     </row>
     <row r="6">
@@ -4358,85 +4358,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.5454505397701613</v>
+        <v>0.5454505397701703</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6793468351464508</v>
+        <v>0.6793468351464594</v>
       </c>
       <c r="D6" t="n">
-        <v>0.420588370335317</v>
+        <v>0.4205883703353202</v>
       </c>
       <c r="E6" t="n">
         <v>1.620544114544475</v>
       </c>
       <c r="F6" t="n">
-        <v>1.074195363811345</v>
+        <v>1.074195363811346</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6739732615055161</v>
+        <v>0.6739732615055177</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5742792850574309</v>
+        <v>0.5742792850574479</v>
       </c>
       <c r="I6" t="n">
-        <v>1.013683942845466</v>
+        <v>1.013683942845489</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7132509546774692</v>
+        <v>0.7132509546774846</v>
       </c>
       <c r="K6" t="n">
-        <v>1.068797700093984</v>
+        <v>1.068797700093997</v>
       </c>
       <c r="L6" t="n">
-        <v>1.780099591889938</v>
+        <v>1.780099591889944</v>
       </c>
       <c r="M6" t="n">
-        <v>0.770451490142921</v>
+        <v>0.7704514901429179</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6897047449849624</v>
+        <v>0.6897047449849747</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4045989327707792</v>
+        <v>0.4045989327707829</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5197971376562697</v>
+        <v>0.5197971376562677</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.9601091455946017</v>
+        <v>0.9601091455946157</v>
       </c>
       <c r="R6" t="n">
-        <v>1.078791533645697</v>
+        <v>1.078791533645708</v>
       </c>
       <c r="S6" t="n">
-        <v>1.268170786577472</v>
+        <v>1.268170786577483</v>
       </c>
       <c r="T6" t="n">
-        <v>0.575323003990122</v>
+        <v>0.5753230039901376</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4823716622288589</v>
+        <v>0.48237166222887</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5626777011004742</v>
+        <v>0.5626777011004757</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5728987685163464</v>
+        <v>0.5728987685163481</v>
       </c>
       <c r="X6" t="n">
-        <v>0.9496854822192211</v>
+        <v>0.9496854822192381</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4978009663083373</v>
+        <v>0.4978009663083506</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.6514236516994624</v>
+        <v>0.6514236516994675</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.4444779984866515</v>
+        <v>0.4444779984866575</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.5488532973691287</v>
+        <v>0.5488532973691277</v>
       </c>
     </row>
     <row r="7">
@@ -4446,85 +4446,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3729469449066692</v>
+        <v>0.3729469449066822</v>
       </c>
       <c r="C7" t="n">
-        <v>0.461034862019592</v>
+        <v>0.4610348620195927</v>
       </c>
       <c r="D7" t="n">
-        <v>0.449347810520816</v>
+        <v>0.4493478105208208</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4063529608682748</v>
+        <v>0.4063529608682708</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3843103756538924</v>
+        <v>0.3843103756538977</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4523779917848981</v>
+        <v>0.4523779917849073</v>
       </c>
       <c r="H7" t="n">
-        <v>0.449347810520816</v>
+        <v>0.4493478105208208</v>
       </c>
       <c r="I7" t="n">
-        <v>0.449347810520816</v>
+        <v>0.4493478105208208</v>
       </c>
       <c r="J7" t="n">
-        <v>0.432494626250015</v>
+        <v>0.4324946262500173</v>
       </c>
       <c r="K7" t="n">
-        <v>0.449347810520816</v>
+        <v>0.4493478105208208</v>
       </c>
       <c r="L7" t="n">
-        <v>0.449347810520816</v>
+        <v>0.4493478105208208</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4531955926944208</v>
+        <v>0.4531955926944186</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3901243580401276</v>
+        <v>0.3901243580401286</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3935874409987641</v>
+        <v>0.3935874409987777</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3895980161108067</v>
+        <v>0.3895980161108204</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3579324311006393</v>
+        <v>0.3579324311006503</v>
       </c>
       <c r="R7" t="n">
-        <v>0.449347810520816</v>
+        <v>0.4493478105208208</v>
       </c>
       <c r="S7" t="n">
-        <v>0.449347810520816</v>
+        <v>0.4493478105208208</v>
       </c>
       <c r="T7" t="n">
-        <v>0.449347810520816</v>
+        <v>0.4493478105208208</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3991630858262724</v>
+        <v>0.3991630858262842</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4052295020291673</v>
+        <v>0.4052295020291681</v>
       </c>
       <c r="W7" t="n">
-        <v>0.4365507893821204</v>
+        <v>0.4365507893821225</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3521226862169199</v>
+        <v>0.352122686216924</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5251704112444535</v>
+        <v>0.5251704112444703</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.3715277596211792</v>
+        <v>0.3715277596211948</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.449347810520816</v>
+        <v>0.4493478105208208</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.5241478835993234</v>
+        <v>0.5241478835993186</v>
       </c>
     </row>
   </sheetData>
@@ -4690,85 +4690,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.579340246657654</v>
+        <v>4.579340246657647</v>
       </c>
       <c r="C2" t="n">
-        <v>2.594587372575765</v>
+        <v>2.594587372575836</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7076101109542112</v>
+        <v>0.7076101109542067</v>
       </c>
       <c r="E2" t="n">
-        <v>8.081231726671358</v>
+        <v>8.081231726671371</v>
       </c>
       <c r="F2" t="n">
-        <v>5.395941926710317</v>
+        <v>5.395941926710314</v>
       </c>
       <c r="G2" t="n">
-        <v>1.264027553236977</v>
+        <v>1.264027553236955</v>
       </c>
       <c r="H2" t="n">
-        <v>1.455603604180794</v>
+        <v>1.455603604180786</v>
       </c>
       <c r="I2" t="n">
-        <v>3.94058712512033</v>
+        <v>3.940587125120329</v>
       </c>
       <c r="J2" t="n">
-        <v>2.322399645173322</v>
+        <v>2.322399645173313</v>
       </c>
       <c r="K2" t="n">
-        <v>2.376671434665049</v>
+        <v>2.37667143466504</v>
       </c>
       <c r="L2" t="n">
-        <v>3.925515473859513</v>
+        <v>3.925515473859506</v>
       </c>
       <c r="M2" t="n">
-        <v>1.240486249152135</v>
+        <v>1.240486249152133</v>
       </c>
       <c r="N2" t="n">
-        <v>2.824334430098811</v>
+        <v>2.824334430098807</v>
       </c>
       <c r="O2" t="n">
-        <v>2.796550751499004</v>
+        <v>2.796550751498992</v>
       </c>
       <c r="P2" t="n">
-        <v>1.140212793433836</v>
+        <v>1.14021279343383</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.628881785281456</v>
+        <v>2.628881785281448</v>
       </c>
       <c r="R2" t="n">
-        <v>5.767003789035781</v>
+        <v>5.767003789035764</v>
       </c>
       <c r="S2" t="n">
-        <v>3.159132687601296</v>
+        <v>3.159132687601288</v>
       </c>
       <c r="T2" t="n">
-        <v>1.826774673969818</v>
+        <v>1.826774673969822</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9659466465966547</v>
+        <v>0.9659466465966485</v>
       </c>
       <c r="V2" t="n">
-        <v>1.91258484206037</v>
+        <v>1.912584842060345</v>
       </c>
       <c r="W2" t="n">
-        <v>2.361742035416195</v>
+        <v>2.361742035416201</v>
       </c>
       <c r="X2" t="n">
-        <v>2.397909784975207</v>
+        <v>2.397909784975219</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.314075069606405</v>
+        <v>1.314075069606397</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.498583747701543</v>
+        <v>3.498583747701531</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.001546677124082</v>
+        <v>1.001546677124077</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.217306093932724</v>
+        <v>1.217306093932725</v>
       </c>
     </row>
     <row r="3">
@@ -4778,85 +4778,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.6700633714565634</v>
+        <v>0.6700633714565701</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9174694847193555</v>
+        <v>0.9174694847191053</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9094737279718255</v>
+        <v>0.9094737279718053</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7783850198851224</v>
+        <v>0.7783850198851223</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7086722334668953</v>
+        <v>0.708672233466895</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9591170249515825</v>
+        <v>0.9591170249515865</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9094737279718255</v>
+        <v>0.9094737279718053</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9094737279718255</v>
+        <v>0.9094737279718053</v>
       </c>
       <c r="J3" t="n">
-        <v>0.9011740928952108</v>
+        <v>0.9011740928952001</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9094737279718255</v>
+        <v>0.9094737279718053</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9094737279718255</v>
+        <v>0.9094737279718053</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9039714509013536</v>
+        <v>0.9039714509013523</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7238906489849447</v>
+        <v>0.7238906489849488</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7748904900416854</v>
+        <v>0.7748904900416711</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7623891967170445</v>
+        <v>0.7623891967170477</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6230137723635495</v>
+        <v>0.6230137723635583</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9094737279718255</v>
+        <v>0.9094737279718053</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9094737279718255</v>
+        <v>0.9094737279718053</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9094737279718255</v>
+        <v>0.9094737279718053</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7909475570666638</v>
+        <v>0.790947557066663</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8228716674702455</v>
+        <v>0.8228716674702213</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9095207781248229</v>
+        <v>0.909520778124808</v>
       </c>
       <c r="X3" t="n">
-        <v>0.6449562067354543</v>
+        <v>0.6449562067354402</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.144651687496563</v>
+        <v>1.144651687496545</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.6656162012520074</v>
+        <v>0.6656162012520063</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.9094737279718255</v>
+        <v>0.9094737279718053</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.146606783203601</v>
+        <v>1.146606783203596</v>
       </c>
     </row>
     <row r="4">
@@ -4866,82 +4866,82 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.112932280549806</v>
+        <v>3.112932280549796</v>
       </c>
       <c r="C4" t="n">
-        <v>2.394594561395849</v>
+        <v>2.394594561395482</v>
       </c>
       <c r="D4" t="n">
-        <v>1.701732110236545</v>
+        <v>1.701732110236531</v>
       </c>
       <c r="E4" t="n">
-        <v>4.387036561664009</v>
+        <v>4.387036561664015</v>
       </c>
       <c r="F4" t="n">
-        <v>3.411407494466701</v>
+        <v>3.411407494466705</v>
       </c>
       <c r="G4" t="n">
-        <v>1.904539734165106</v>
+        <v>1.904539734165109</v>
       </c>
       <c r="H4" t="n">
-        <v>1.974366955134581</v>
+        <v>1.974366955134567</v>
       </c>
       <c r="I4" t="n">
-        <v>2.880114268367286</v>
+        <v>2.880114268367284</v>
       </c>
       <c r="J4" t="n">
-        <v>2.258347149048336</v>
+        <v>2.258347149048309</v>
       </c>
       <c r="K4" t="n">
-        <v>2.310085363621562</v>
+        <v>2.310085363621551</v>
       </c>
       <c r="L4" t="n">
-        <v>2.874620828462994</v>
+        <v>2.87462082846298</v>
       </c>
       <c r="M4" t="n">
-        <v>1.892462443572779</v>
+        <v>1.89246244357278</v>
       </c>
       <c r="N4" t="n">
-        <v>2.473253268732883</v>
+        <v>2.473253268732865</v>
       </c>
       <c r="O4" t="n">
-        <v>2.463126444135671</v>
+        <v>2.463126444135656</v>
       </c>
       <c r="P4" t="n">
-        <v>1.859410708123194</v>
+        <v>1.859410708123183</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.402013074817781</v>
+        <v>2.402013074817793</v>
       </c>
       <c r="R4" t="n">
-        <v>3.545821695497202</v>
+        <v>3.545821695497186</v>
       </c>
       <c r="S4" t="n">
         <v>2.595283302192894</v>
       </c>
       <c r="T4" t="n">
-        <v>2.109654451561924</v>
+        <v>2.10965445156192</v>
       </c>
       <c r="U4" t="n">
-        <v>1.795892743937452</v>
+        <v>1.795892743937441</v>
       </c>
       <c r="V4" t="n">
-        <v>1.950634594951577</v>
+        <v>1.950634594951722</v>
       </c>
       <c r="W4" t="n">
-        <v>2.304643772905217</v>
+        <v>2.304643772905207</v>
       </c>
       <c r="X4" t="n">
-        <v>2.317826492916318</v>
+        <v>2.317826492916309</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.922781466194177</v>
+        <v>1.922781466194162</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.71900922756385</v>
+        <v>2.719009227563836</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.808868537028029</v>
+        <v>1.808868537028026</v>
       </c>
       <c r="AB4" t="n">
         <v>1.879279747134646</v>
@@ -4954,85 +4954,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.688046764585726</v>
+        <v>1.688046764585682</v>
       </c>
       <c r="C5" t="n">
-        <v>1.783304784984723</v>
+        <v>1.783304784984219</v>
       </c>
       <c r="D5" t="n">
-        <v>1.775309028237192</v>
+        <v>1.775309028237173</v>
       </c>
       <c r="E5" t="n">
         <v>1.725234691396012</v>
       </c>
       <c r="F5" t="n">
-        <v>1.702952731979098</v>
+        <v>1.7029527319791</v>
       </c>
       <c r="G5" t="n">
-        <v>1.793403427045281</v>
+        <v>1.793403427045278</v>
       </c>
       <c r="H5" t="n">
-        <v>1.775309028237192</v>
+        <v>1.775309028237173</v>
       </c>
       <c r="I5" t="n">
-        <v>1.775309028237192</v>
+        <v>1.775309028237173</v>
       </c>
       <c r="J5" t="n">
-        <v>1.740327124115988</v>
+        <v>1.740327124115996</v>
       </c>
       <c r="K5" t="n">
-        <v>1.775309028237192</v>
+        <v>1.775309028237173</v>
       </c>
       <c r="L5" t="n">
-        <v>1.775309028237192</v>
+        <v>1.775309028237173</v>
       </c>
       <c r="M5" t="n">
-        <v>1.769806751166637</v>
+        <v>1.769806751166635</v>
       </c>
       <c r="N5" t="n">
-        <v>1.707666175173007</v>
+        <v>1.707666175173008</v>
       </c>
       <c r="O5" t="n">
-        <v>1.726255018367816</v>
+        <v>1.726255018367826</v>
       </c>
       <c r="P5" t="n">
-        <v>1.721698443748586</v>
+        <v>1.721698443748589</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.670897738200605</v>
+        <v>1.670897738200598</v>
       </c>
       <c r="R5" t="n">
-        <v>1.775309028237192</v>
+        <v>1.775309028237173</v>
       </c>
       <c r="S5" t="n">
-        <v>1.775309028237192</v>
+        <v>1.775309028237173</v>
       </c>
       <c r="T5" t="n">
-        <v>1.775309028237192</v>
+        <v>1.775309028237173</v>
       </c>
       <c r="U5" t="n">
-        <v>1.732107630746825</v>
+        <v>1.732107630746827</v>
       </c>
       <c r="V5" t="n">
-        <v>1.553446938871608</v>
+        <v>1.553446938871773</v>
       </c>
       <c r="W5" t="n">
-        <v>1.775326177465466</v>
+        <v>1.77532617746546</v>
       </c>
       <c r="X5" t="n">
-        <v>1.678895497868091</v>
+        <v>1.678895497868071</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.861028632884915</v>
+        <v>1.861028632884906</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.686425823267471</v>
+        <v>1.686425823267467</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.775309028237192</v>
+        <v>1.775309028237173</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.8535106785671</v>
+        <v>1.853510678567098</v>
       </c>
     </row>
     <row r="6">
@@ -5042,82 +5042,82 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.871093248686348</v>
+        <v>1.871093248686347</v>
       </c>
       <c r="C6" t="n">
-        <v>1.152755529532403</v>
+        <v>1.152755529532263</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4598930783730837</v>
+        <v>0.4598930783730825</v>
       </c>
       <c r="E6" t="n">
-        <v>3.14519752980056</v>
+        <v>3.145197529800563</v>
       </c>
       <c r="F6" t="n">
-        <v>2.169568462603255</v>
+        <v>2.169568462603256</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6470995233169252</v>
+        <v>0.6470995233169127</v>
       </c>
       <c r="H6" t="n">
-        <v>0.732527923271122</v>
+        <v>0.7325279232711183</v>
       </c>
       <c r="I6" t="n">
-        <v>1.638275236503844</v>
+        <v>1.638275236503837</v>
       </c>
       <c r="J6" t="n">
-        <v>1.028122222528508</v>
+        <v>1.028122222528493</v>
       </c>
       <c r="K6" t="n">
-        <v>1.068246331758105</v>
+        <v>1.068246331758102</v>
       </c>
       <c r="L6" t="n">
-        <v>1.63278179659953</v>
+        <v>1.632781796599531</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6506234117093299</v>
+        <v>0.6506234117093307</v>
       </c>
       <c r="N6" t="n">
-        <v>1.231414236869414</v>
+        <v>1.231414236869417</v>
       </c>
       <c r="O6" t="n">
-        <v>1.205686233287466</v>
+        <v>1.205686233287462</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6019704972749911</v>
+        <v>0.6019704972749875</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.160174042954321</v>
+        <v>1.160174042954342</v>
       </c>
       <c r="R6" t="n">
-        <v>2.303982663633742</v>
+        <v>2.303982663633739</v>
       </c>
       <c r="S6" t="n">
-        <v>1.353444270329447</v>
+        <v>1.353444270329443</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8678154196984651</v>
+        <v>0.8678154196984715</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5384525330892486</v>
+        <v>0.5384525330892459</v>
       </c>
       <c r="V6" t="n">
-        <v>0.8719442026711709</v>
+        <v>0.8719442026711856</v>
       </c>
       <c r="W6" t="n">
-        <v>1.047203562057009</v>
+        <v>1.047203562057008</v>
       </c>
       <c r="X6" t="n">
-        <v>1.060386282068119</v>
+        <v>1.060386282068113</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.6809424343307184</v>
+        <v>0.6809424343307144</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.477170195700393</v>
+        <v>1.477170195700388</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.567029505164573</v>
+        <v>0.5670295051645777</v>
       </c>
       <c r="AB6" t="n">
         <v>0.6374407152711951</v>
@@ -5130,85 +5130,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4462077327222684</v>
+        <v>0.4462077327222333</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5414657531212773</v>
+        <v>0.5414657531209</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5334699963737327</v>
+        <v>0.5334699963737257</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4833956595325637</v>
+        <v>0.4833956595325644</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4611137001156502</v>
+        <v>0.4611137001156519</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5359632161970893</v>
+        <v>0.5359632161970802</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5334699963737327</v>
+        <v>0.5334699963737257</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5334699963737327</v>
+        <v>0.5334699963737257</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5101021975961539</v>
+        <v>0.5101021975961331</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5334699963737327</v>
+        <v>0.5334699963737257</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5334699963737327</v>
+        <v>0.5334699963737257</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5279677193031866</v>
+        <v>0.5279677193031875</v>
       </c>
       <c r="N7" t="n">
-        <v>0.46582714330956</v>
+        <v>0.4658271433095598</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4688148075196225</v>
+        <v>0.4688148075196281</v>
       </c>
       <c r="P7" t="n">
-        <v>0.46425823290039</v>
+        <v>0.4642582329003917</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4290587063371437</v>
+        <v>0.429058706337149</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5334699963737327</v>
+        <v>0.5334699963737257</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5334699963737327</v>
+        <v>0.5334699963737257</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5334699963737327</v>
+        <v>0.5334699963737257</v>
       </c>
       <c r="U7" t="n">
-        <v>0.474667419898627</v>
+        <v>0.4746674198986302</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4747565465912214</v>
+        <v>0.4747565465912145</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5178859666172687</v>
+        <v>0.5178859666172643</v>
       </c>
       <c r="X7" t="n">
-        <v>0.4214552870198814</v>
+        <v>0.4214552870198744</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.6191896010214726</v>
+        <v>0.6191896010214601</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.4445867914040286</v>
+        <v>0.4445867914040165</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.5334699963737327</v>
+        <v>0.5334699963737257</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.6116716467036485</v>
+        <v>0.6116716467036498</v>
       </c>
     </row>
   </sheetData>
@@ -5374,85 +5374,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>6.984450103856945</v>
+        <v>6.984450103856905</v>
       </c>
       <c r="C2" t="n">
-        <v>3.527767661183439</v>
+        <v>3.52776766118344</v>
       </c>
       <c r="D2" t="n">
-        <v>2.801506749405522</v>
+        <v>2.801506749405525</v>
       </c>
       <c r="E2" t="n">
-        <v>7.617317258728602</v>
+        <v>7.617317258728596</v>
       </c>
       <c r="F2" t="n">
-        <v>4.308961619697352</v>
+        <v>4.308961619697341</v>
       </c>
       <c r="G2" t="n">
-        <v>1.589543685572694</v>
+        <v>1.589543685572681</v>
       </c>
       <c r="H2" t="n">
-        <v>1.086930753622629</v>
+        <v>1.086930753622703</v>
       </c>
       <c r="I2" t="n">
-        <v>2.207527336017554</v>
+        <v>2.207527336017565</v>
       </c>
       <c r="J2" t="n">
-        <v>2.33718531483391</v>
+        <v>2.337185314833999</v>
       </c>
       <c r="K2" t="n">
-        <v>1.636436255145712</v>
+        <v>1.636436255145728</v>
       </c>
       <c r="L2" t="n">
-        <v>3.376140678513634</v>
+        <v>3.376140678513637</v>
       </c>
       <c r="M2" t="n">
-        <v>1.027086935827449</v>
+        <v>1.027086935827444</v>
       </c>
       <c r="N2" t="n">
-        <v>2.116150868985321</v>
+        <v>2.11615086898534</v>
       </c>
       <c r="O2" t="n">
-        <v>2.83930151476634</v>
+        <v>2.839301514766387</v>
       </c>
       <c r="P2" t="n">
-        <v>1.528795358999735</v>
+        <v>1.528795358999755</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.988143909729544</v>
+        <v>2.98814390972956</v>
       </c>
       <c r="R2" t="n">
-        <v>6.766151362158928</v>
+        <v>6.766151362158896</v>
       </c>
       <c r="S2" t="n">
-        <v>2.879286830520354</v>
+        <v>2.879286830520372</v>
       </c>
       <c r="T2" t="n">
-        <v>1.29094850507672</v>
+        <v>1.290948505076761</v>
       </c>
       <c r="U2" t="n">
-        <v>1.016627928450948</v>
+        <v>1.016627928450963</v>
       </c>
       <c r="V2" t="n">
-        <v>2.176194373567985</v>
+        <v>2.17619437356798</v>
       </c>
       <c r="W2" t="n">
-        <v>2.798366831508641</v>
+        <v>2.798366831508622</v>
       </c>
       <c r="X2" t="n">
-        <v>2.388952725099936</v>
+        <v>2.388952725100063</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.701083329913977</v>
+        <v>1.701083329913999</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.303584588533963</v>
+        <v>3.303584588533966</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.150076748316658</v>
+        <v>1.150076748316671</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.614881723635953</v>
+        <v>1.614881723635939</v>
       </c>
     </row>
     <row r="3">
@@ -5462,85 +5462,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7071938971579079</v>
+        <v>0.7071938971579913</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9692405418472471</v>
+        <v>0.9692405418472331</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9589228798431841</v>
+        <v>0.9589228798432263</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8193942020364069</v>
+        <v>0.8193942020364055</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7435833816610635</v>
+        <v>0.7435833816610595</v>
       </c>
       <c r="G3" t="n">
-        <v>1.011120524194299</v>
+        <v>1.011120524194375</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9589228798431841</v>
+        <v>0.9589228798432263</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9589228798431841</v>
+        <v>0.9589228798432263</v>
       </c>
       <c r="J3" t="n">
-        <v>0.95035295030565</v>
+        <v>0.9503529503056858</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9589228798431841</v>
+        <v>0.9589228798432263</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9589228798431841</v>
+        <v>0.9589228798432263</v>
       </c>
       <c r="M3" t="n">
         <v>0.9524190767252898</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7637908046730573</v>
+        <v>0.7637908046730678</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8174147927108769</v>
+        <v>0.8174147927108151</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8042702575618175</v>
+        <v>0.8042702575618019</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6577234069083204</v>
+        <v>0.6577234069083088</v>
       </c>
       <c r="R3" t="n">
-        <v>0.9589228798431841</v>
+        <v>0.9589228798432263</v>
       </c>
       <c r="S3" t="n">
-        <v>0.9589228798431841</v>
+        <v>0.9589228798432263</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9589228798431841</v>
+        <v>0.9589228798432263</v>
       </c>
       <c r="U3" t="n">
-        <v>0.8336529887827407</v>
+        <v>0.8336529887828455</v>
       </c>
       <c r="V3" t="n">
-        <v>0.8675316309522891</v>
+        <v>0.8675316309522784</v>
       </c>
       <c r="W3" t="n">
-        <v>0.9589723507998762</v>
+        <v>0.958972350799784</v>
       </c>
       <c r="X3" t="n">
-        <v>0.680794867747775</v>
+        <v>0.6807948677478132</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.205098161694784</v>
+        <v>1.205098161694736</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.7025179021630202</v>
+        <v>0.7025179021630801</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.9589228798431841</v>
+        <v>0.9589228798432263</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.209765539443409</v>
+        <v>1.209765539443392</v>
       </c>
     </row>
     <row r="4">
@@ -5550,85 +5550,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.062954297121674</v>
+        <v>4.062954297121657</v>
       </c>
       <c r="C4" t="n">
-        <v>2.809591132541404</v>
+        <v>2.809591132541393</v>
       </c>
       <c r="D4" t="n">
-        <v>2.538320563024861</v>
+        <v>2.538320563024884</v>
       </c>
       <c r="E4" t="n">
-        <v>4.290137717009639</v>
+        <v>4.290137717009628</v>
       </c>
       <c r="F4" t="n">
-        <v>3.085973602614238</v>
+        <v>3.085973602614243</v>
       </c>
       <c r="G4" t="n">
-        <v>2.096574257846622</v>
+        <v>2.096574257846636</v>
       </c>
       <c r="H4" t="n">
-        <v>1.913377746129866</v>
+        <v>1.913377746129892</v>
       </c>
       <c r="I4" t="n">
-        <v>2.321822041703378</v>
+        <v>2.321822041703394</v>
       </c>
       <c r="J4" t="n">
-        <v>2.338334979990041</v>
+        <v>2.33833497999008</v>
       </c>
       <c r="K4" t="n">
-        <v>2.113666048815596</v>
+        <v>2.113666048815649</v>
       </c>
       <c r="L4" t="n">
-        <v>2.747767882492484</v>
+        <v>2.747767882492524</v>
       </c>
       <c r="M4" t="n">
-        <v>1.887432134011278</v>
+        <v>1.887432134011287</v>
       </c>
       <c r="N4" t="n">
-        <v>2.288516392466756</v>
+        <v>2.288516392466796</v>
       </c>
       <c r="O4" t="n">
-        <v>2.552096311190361</v>
+        <v>2.55209631119038</v>
       </c>
       <c r="P4" t="n">
-        <v>2.074432206153574</v>
+        <v>2.074432206153667</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.606347616358784</v>
+        <v>2.606347616358811</v>
       </c>
       <c r="R4" t="n">
-        <v>3.983386969165944</v>
+        <v>3.983386969165973</v>
       </c>
       <c r="S4" t="n">
-        <v>2.566670489251429</v>
+        <v>2.566670489251421</v>
       </c>
       <c r="T4" t="n">
-        <v>1.987739820837495</v>
+        <v>1.987739820837504</v>
       </c>
       <c r="U4" t="n">
-        <v>1.887753191892245</v>
+        <v>1.887753191892239</v>
       </c>
       <c r="V4" t="n">
-        <v>2.128938446103026</v>
+        <v>2.128938446103019</v>
       </c>
       <c r="W4" t="n">
-        <v>2.537176099822238</v>
+        <v>2.537176099822243</v>
       </c>
       <c r="X4" t="n">
-        <v>2.387949465619545</v>
+        <v>2.387949465619484</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.137229148444391</v>
+        <v>2.13722914844441</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.721322039691479</v>
+        <v>2.721322039691557</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.936393719698039</v>
+        <v>1.936393719698133</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.098114065791564</v>
+        <v>2.098114065791556</v>
       </c>
     </row>
     <row r="5">
@@ -5638,85 +5638,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.774968121043728</v>
+        <v>1.774968121043807</v>
       </c>
       <c r="C5" t="n">
-        <v>1.877038041285612</v>
+        <v>1.877038041285626</v>
       </c>
       <c r="D5" t="n">
-        <v>1.866720379281536</v>
+        <v>1.866720379281618</v>
       </c>
       <c r="E5" t="n">
-        <v>1.812374588088048</v>
+        <v>1.81237458808806</v>
       </c>
       <c r="F5" t="n">
-        <v>1.786435101635038</v>
+        <v>1.78643510163505</v>
       </c>
       <c r="G5" t="n">
-        <v>1.885745807711853</v>
+        <v>1.885745807711931</v>
       </c>
       <c r="H5" t="n">
-        <v>1.866720379281536</v>
+        <v>1.866720379281618</v>
       </c>
       <c r="I5" t="n">
-        <v>1.866720379281536</v>
+        <v>1.866720379281618</v>
       </c>
       <c r="J5" t="n">
-        <v>1.83285086812728</v>
+        <v>1.832850868127331</v>
       </c>
       <c r="K5" t="n">
-        <v>1.866720379281536</v>
+        <v>1.866720379281618</v>
       </c>
       <c r="L5" t="n">
-        <v>1.866720379281536</v>
+        <v>1.866720379281618</v>
       </c>
       <c r="M5" t="n">
-        <v>1.860216576162819</v>
+        <v>1.860216576162822</v>
       </c>
       <c r="N5" t="n">
-        <v>1.795597029238593</v>
+        <v>1.795597029238601</v>
       </c>
       <c r="O5" t="n">
-        <v>1.815142343193785</v>
+        <v>1.815142343193709</v>
       </c>
       <c r="P5" t="n">
-        <v>1.81035131448289</v>
+        <v>1.810351314482817</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.756936708259583</v>
+        <v>1.756936708259619</v>
       </c>
       <c r="R5" t="n">
-        <v>1.866720379281536</v>
+        <v>1.866720379281618</v>
       </c>
       <c r="S5" t="n">
-        <v>1.866720379281536</v>
+        <v>1.866720379281618</v>
       </c>
       <c r="T5" t="n">
-        <v>1.866720379281536</v>
+        <v>1.866720379281618</v>
       </c>
       <c r="U5" t="n">
-        <v>1.821060974983514</v>
+        <v>1.821060974983432</v>
       </c>
       <c r="V5" t="n">
-        <v>1.651946243513371</v>
+        <v>1.651946243513372</v>
       </c>
       <c r="W5" t="n">
-        <v>1.866738410864318</v>
+        <v>1.866738410864365</v>
       </c>
       <c r="X5" t="n">
-        <v>1.765345984816851</v>
+        <v>1.765345984816841</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.956448378780397</v>
+        <v>1.956448378780385</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.77326377577648</v>
+        <v>1.773263775776464</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.866720379281536</v>
+        <v>1.866720379281618</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.950453973767771</v>
+        <v>1.95045397376778</v>
       </c>
     </row>
     <row r="6">
@@ -5726,85 +5726,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.760500730463416</v>
+        <v>2.760500730463335</v>
       </c>
       <c r="C6" t="n">
-        <v>1.507137565883081</v>
+        <v>1.507137565883071</v>
       </c>
       <c r="D6" t="n">
-        <v>1.235866996366688</v>
+        <v>1.235866996366564</v>
       </c>
       <c r="E6" t="n">
-        <v>2.987684150351317</v>
+        <v>2.987684150351308</v>
       </c>
       <c r="F6" t="n">
-        <v>1.783520035955918</v>
+        <v>1.783520035955922</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7770221994836969</v>
+        <v>0.7770221994837113</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6109241794716714</v>
+        <v>0.6109241794715708</v>
       </c>
       <c r="I6" t="n">
-        <v>1.019368475045136</v>
+        <v>1.019368475045073</v>
       </c>
       <c r="J6" t="n">
-        <v>1.044651376245745</v>
+        <v>1.044651376245755</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8112124821574251</v>
+        <v>0.8112124821573278</v>
       </c>
       <c r="L6" t="n">
-        <v>1.445314315834267</v>
+        <v>1.445314315834202</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5849785673529655</v>
+        <v>0.5849785673529659</v>
       </c>
       <c r="N6" t="n">
-        <v>0.986062825808562</v>
+        <v>0.9860628258084758</v>
       </c>
       <c r="O6" t="n">
-        <v>1.232544252827455</v>
+        <v>1.232544252827453</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7548801477906439</v>
+        <v>0.7548801477907398</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.303894049700623</v>
+        <v>1.303894049700492</v>
       </c>
       <c r="R6" t="n">
-        <v>2.680933402507758</v>
+        <v>2.680933402507654</v>
       </c>
       <c r="S6" t="n">
-        <v>1.264216922593244</v>
+        <v>1.264216922593099</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6852862541793269</v>
+        <v>0.685286254179184</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5682011335293435</v>
+        <v>0.5682011335293135</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9789432162403132</v>
+        <v>0.9789432162403007</v>
       </c>
       <c r="W6" t="n">
-        <v>1.217624041459305</v>
+        <v>1.217624041459316</v>
       </c>
       <c r="X6" t="n">
-        <v>1.068397407256558</v>
+        <v>1.068397407256559</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.8347755817861638</v>
+        <v>0.8347755817860886</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.418868473033329</v>
+        <v>1.418868473033235</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.6339401530399132</v>
+        <v>0.6339401530398117</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.7956604991332514</v>
+        <v>0.7956604991332366</v>
       </c>
     </row>
     <row r="7">
@@ -5814,85 +5814,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.4725145543855156</v>
+        <v>0.4725145543854855</v>
       </c>
       <c r="C7" t="n">
-        <v>0.5745844746273141</v>
+        <v>0.5745844746273037</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5642668126231766</v>
+        <v>0.5642668126232959</v>
       </c>
       <c r="E7" t="n">
-        <v>0.5099210214297425</v>
+        <v>0.5099210214297395</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4839815349767402</v>
+        <v>0.48398153497673</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5661937493489098</v>
+        <v>0.5661937493490039</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5642668126231766</v>
+        <v>0.5642668126232959</v>
       </c>
       <c r="I7" t="n">
-        <v>0.5642668126231766</v>
+        <v>0.5642668126232959</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5391672643830374</v>
+        <v>0.5391672643830073</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5642668126231766</v>
+        <v>0.5642668126232959</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5642668126231766</v>
+        <v>0.5642668126232959</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5577630095045037</v>
+        <v>0.5577630095044985</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4931434625802865</v>
+        <v>0.4931434625802799</v>
       </c>
       <c r="O7" t="n">
-        <v>0.495590284830814</v>
+        <v>0.4955902848307833</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4907992561200045</v>
+        <v>0.4907992561198916</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4544831416013759</v>
+        <v>0.4544831416012977</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5642668126231766</v>
+        <v>0.5642668126232959</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5642668126231766</v>
+        <v>0.5642668126232959</v>
       </c>
       <c r="T7" t="n">
-        <v>0.5642668126231766</v>
+        <v>0.5642668126232959</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5015089166205885</v>
+        <v>0.5015089166205037</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5019510136506653</v>
+        <v>0.5019510136506534</v>
       </c>
       <c r="W7" t="n">
-        <v>0.5471863525014353</v>
+        <v>0.5471863525014387</v>
       </c>
       <c r="X7" t="n">
-        <v>0.4457939264539462</v>
+        <v>0.4457939264539138</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.6539948121220502</v>
+        <v>0.6539948121220647</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.4708102091181961</v>
+        <v>0.4708102091181438</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.5642668126231766</v>
+        <v>0.5642668126232959</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.6480004071094836</v>
+        <v>0.6480004071094596</v>
       </c>
     </row>
   </sheetData>
@@ -6058,85 +6058,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.247271288415959</v>
+        <v>1.247271288416028</v>
       </c>
       <c r="C2" t="n">
-        <v>1.193401364753608</v>
+        <v>1.193401364754157</v>
       </c>
       <c r="D2" t="n">
-        <v>0.58213339399789</v>
+        <v>0.5821333939978972</v>
       </c>
       <c r="E2" t="n">
-        <v>2.292092917801475</v>
+        <v>2.292092917801517</v>
       </c>
       <c r="F2" t="n">
-        <v>1.994599073760686</v>
+        <v>1.994599073760681</v>
       </c>
       <c r="G2" t="n">
-        <v>2.623841364095718</v>
+        <v>2.623841364095791</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6840576455791773</v>
+        <v>0.6840576455792342</v>
       </c>
       <c r="I2" t="n">
-        <v>2.592573234754261</v>
+        <v>2.592573234754327</v>
       </c>
       <c r="J2" t="n">
-        <v>1.86567468822443</v>
+        <v>1.865674688224436</v>
       </c>
       <c r="K2" t="n">
-        <v>2.734284858785477</v>
+        <v>2.734284858785577</v>
       </c>
       <c r="L2" t="n">
-        <v>1.791209297230699</v>
+        <v>1.791209297230779</v>
       </c>
       <c r="M2" t="n">
-        <v>3.151188422932398</v>
+        <v>3.151188422932393</v>
       </c>
       <c r="N2" t="n">
-        <v>1.310166566190536</v>
+        <v>1.310166566190614</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9009909396695016</v>
+        <v>0.9009909396695499</v>
       </c>
       <c r="P2" t="n">
-        <v>1.263771000707304</v>
+        <v>1.263771000707363</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.986055806642228</v>
+        <v>1.986055806642318</v>
       </c>
       <c r="R2" t="n">
-        <v>2.01608528394746</v>
+        <v>2.016085283947444</v>
       </c>
       <c r="S2" t="n">
-        <v>2.384615318519137</v>
+        <v>2.384615318519196</v>
       </c>
       <c r="T2" t="n">
-        <v>1.213097806753775</v>
+        <v>1.213097806753838</v>
       </c>
       <c r="U2" t="n">
-        <v>1.123990098600546</v>
+        <v>1.123990098600682</v>
       </c>
       <c r="V2" t="n">
-        <v>1.049588473546264</v>
+        <v>1.049588473546316</v>
       </c>
       <c r="W2" t="n">
-        <v>0.820249186175312</v>
+        <v>0.8202491861753727</v>
       </c>
       <c r="X2" t="n">
-        <v>2.045042038993724</v>
+        <v>2.045042038993774</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.192485284960713</v>
+        <v>1.192485284960786</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.8302815361117728</v>
+        <v>0.8302815361118645</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.9395310630710746</v>
+        <v>0.9395310630711605</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.220839911628927</v>
+        <v>2.220839911628924</v>
       </c>
     </row>
     <row r="3">
@@ -6146,85 +6146,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4963579077239235</v>
+        <v>0.4963579077239059</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6937681444921009</v>
+        <v>0.6937681444917211</v>
       </c>
       <c r="D3" t="n">
-        <v>0.6830423318652702</v>
+        <v>0.6830423318653697</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5799414252221763</v>
+        <v>0.5799414252222086</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5245326540873183</v>
+        <v>0.5245326540873153</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7217525633339008</v>
+        <v>0.7217525633338777</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6830423318652702</v>
+        <v>0.6830423318653697</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6830423318652702</v>
+        <v>0.6830423318653697</v>
       </c>
       <c r="J3" t="n">
-        <v>0.6794985806981958</v>
+        <v>0.6794985806982198</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6830423318652702</v>
+        <v>0.6830423318653697</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6830423318652702</v>
+        <v>0.6830423318653697</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6927656678343455</v>
+        <v>0.6927656678343452</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5383306714552381</v>
+        <v>0.5383306714553152</v>
       </c>
       <c r="O3" t="n">
-        <v>0.5780986920781064</v>
+        <v>0.5780986920782115</v>
       </c>
       <c r="P3" t="n">
-        <v>0.5683505893123262</v>
+        <v>0.5683505893123432</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.459670157603677</v>
+        <v>0.4596701576037583</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6830423318652702</v>
+        <v>0.6830423318653697</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6830423318652702</v>
+        <v>0.6830423318653697</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6830423318652702</v>
+        <v>0.6830423318653697</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5906322611699866</v>
+        <v>0.5906322611699352</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6212646409997734</v>
+        <v>0.6212646409997934</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6830790203832171</v>
+        <v>0.6830790203832434</v>
       </c>
       <c r="X3" t="n">
-        <v>0.4767801558295883</v>
+        <v>0.4767801558295747</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.866448349468539</v>
+        <v>0.8664483494686118</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.4928901487306277</v>
+        <v>0.492890148730562</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.6830423318652702</v>
+        <v>0.6830423318653697</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8783320625636244</v>
+        <v>0.8783320625636264</v>
       </c>
     </row>
     <row r="4">
@@ -6234,85 +6234,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.610567342344775</v>
+        <v>1.610567342344894</v>
       </c>
       <c r="C4" t="n">
-        <v>1.597748767615429</v>
+        <v>1.597748767615624</v>
       </c>
       <c r="D4" t="n">
-        <v>1.368132390272947</v>
+        <v>1.368132390272984</v>
       </c>
       <c r="E4" t="n">
-        <v>1.989043097303677</v>
+        <v>1.989043097303742</v>
       </c>
       <c r="F4" t="n">
-        <v>1.882382178906913</v>
+        <v>1.882382178906947</v>
       </c>
       <c r="G4" t="n">
-        <v>2.112310970428129</v>
+        <v>2.112310970428219</v>
       </c>
       <c r="H4" t="n">
-        <v>1.405282583119296</v>
+        <v>1.405282583119372</v>
       </c>
       <c r="I4" t="n">
-        <v>2.100914104452085</v>
+        <v>2.100914104452198</v>
       </c>
       <c r="J4" t="n">
-        <v>1.805268821694753</v>
+        <v>1.80526882169472</v>
       </c>
       <c r="K4" t="n">
-        <v>2.152566327349561</v>
+        <v>2.152566327349652</v>
       </c>
       <c r="L4" t="n">
-        <v>1.808826359315149</v>
+        <v>1.808826359315276</v>
       </c>
       <c r="M4" t="n">
-        <v>2.31070207513833</v>
+        <v>2.310702075138382</v>
       </c>
       <c r="N4" t="n">
-        <v>1.633491932539978</v>
+        <v>1.633491932540084</v>
       </c>
       <c r="O4" t="n">
-        <v>1.48435222145585</v>
+        <v>1.484352221455946</v>
       </c>
       <c r="P4" t="n">
-        <v>1.616581293725546</v>
+        <v>1.616581293725681</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.879845623992471</v>
+        <v>1.879845623992569</v>
       </c>
       <c r="R4" t="n">
-        <v>1.890791015846275</v>
+        <v>1.890791015846373</v>
       </c>
       <c r="S4" t="n">
-        <v>2.025115885949511</v>
+        <v>2.0251158859496</v>
       </c>
       <c r="T4" t="n">
-        <v>1.598111509564223</v>
+        <v>1.598111509564309</v>
       </c>
       <c r="U4" t="n">
-        <v>1.565632796297913</v>
+        <v>1.565632796297967</v>
       </c>
       <c r="V4" t="n">
-        <v>1.342793095628532</v>
+        <v>1.342793095628572</v>
       </c>
       <c r="W4" t="n">
-        <v>1.454922800424756</v>
+        <v>1.454922800424877</v>
       </c>
       <c r="X4" t="n">
-        <v>1.901345413033309</v>
+        <v>1.901345413033364</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.59059848741508</v>
+        <v>1.590598487415201</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.458579474170793</v>
+        <v>1.458579474170922</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.498399643874743</v>
+        <v>1.49839964387487</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.965601039922629</v>
+        <v>1.965601039922632</v>
       </c>
     </row>
     <row r="5">
@@ -6322,85 +6322,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.336868232752683</v>
+        <v>1.336868232752736</v>
       </c>
       <c r="C5" t="n">
-        <v>1.415638325819746</v>
+        <v>1.415638325819449</v>
       </c>
       <c r="D5" t="n">
-        <v>1.404912513193009</v>
+        <v>1.40491251319308</v>
       </c>
       <c r="E5" t="n">
-        <v>1.364983983356423</v>
+        <v>1.364983983356498</v>
       </c>
       <c r="F5" t="n">
-        <v>1.346560231327431</v>
+        <v>1.346560231327435</v>
       </c>
       <c r="G5" t="n">
-        <v>1.419021938004836</v>
+        <v>1.419021938004878</v>
       </c>
       <c r="H5" t="n">
-        <v>1.404912513193009</v>
+        <v>1.40491251319308</v>
       </c>
       <c r="I5" t="n">
-        <v>1.404912513193009</v>
+        <v>1.40491251319308</v>
       </c>
       <c r="J5" t="n">
-        <v>1.372921559284528</v>
+        <v>1.372921559284575</v>
       </c>
       <c r="K5" t="n">
-        <v>1.404912513193009</v>
+        <v>1.40491251319308</v>
       </c>
       <c r="L5" t="n">
-        <v>1.404912513193009</v>
+        <v>1.40491251319308</v>
       </c>
       <c r="M5" t="n">
-        <v>1.414635849162587</v>
+        <v>1.414635849162607</v>
       </c>
       <c r="N5" t="n">
-        <v>1.352166812263733</v>
+        <v>1.352166812263725</v>
       </c>
       <c r="O5" t="n">
-        <v>1.366661788801082</v>
+        <v>1.366661788801065</v>
       </c>
       <c r="P5" t="n">
-        <v>1.363108719810842</v>
+        <v>1.363108719810921</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.323495978643198</v>
+        <v>1.323495978643245</v>
       </c>
       <c r="R5" t="n">
-        <v>1.404912513193009</v>
+        <v>1.40491251319308</v>
       </c>
       <c r="S5" t="n">
-        <v>1.404912513193009</v>
+        <v>1.40491251319308</v>
       </c>
       <c r="T5" t="n">
-        <v>1.404912513193009</v>
+        <v>1.40491251319308</v>
       </c>
       <c r="U5" t="n">
-        <v>1.371230127558406</v>
+        <v>1.371230127558472</v>
       </c>
       <c r="V5" t="n">
-        <v>1.186674088297718</v>
+        <v>1.186674088297741</v>
       </c>
       <c r="W5" t="n">
-        <v>1.404925885727036</v>
+        <v>1.404925885727015</v>
       </c>
       <c r="X5" t="n">
-        <v>1.329732372080793</v>
+        <v>1.329732372080827</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.47176185294721</v>
+        <v>1.471761852947238</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.335604275320009</v>
+        <v>1.335604275320159</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.404912513193009</v>
+        <v>1.40491251319308</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.476272693461382</v>
+        <v>1.476272693461417</v>
       </c>
     </row>
     <row r="6">
@@ -6410,85 +6410,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.592976641994112</v>
+        <v>0.5929766419942022</v>
       </c>
       <c r="C6" t="n">
-        <v>0.5801580672649334</v>
+        <v>0.580158067264923</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3505416899222693</v>
+        <v>0.350541689922283</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9714523969530208</v>
+        <v>0.9714523969530544</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8647914785562576</v>
+        <v>0.8647914785562602</v>
       </c>
       <c r="G6" t="n">
-        <v>1.085079992238118</v>
+        <v>1.085079992238213</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3876918827686391</v>
+        <v>0.387691882768689</v>
       </c>
       <c r="I6" t="n">
-        <v>1.083323404101398</v>
+        <v>1.083323404101487</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8068334903946088</v>
+        <v>0.8068334903945983</v>
       </c>
       <c r="K6" t="n">
-        <v>1.134975626998892</v>
+        <v>1.134975626998963</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7912356589645226</v>
+        <v>0.791235658964599</v>
       </c>
       <c r="M6" t="n">
         <v>1.293111374787674</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6159012321893441</v>
+        <v>0.6159012321893983</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4571212432658456</v>
+        <v>0.4571212432659438</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5893503155355854</v>
+        <v>0.5893503155356549</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.8622549236417703</v>
+        <v>0.8622549236418774</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8732003154956153</v>
+        <v>0.8732003154956991</v>
       </c>
       <c r="S6" t="n">
-        <v>1.007525185598865</v>
+        <v>1.007525185598919</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5805208092135201</v>
+        <v>0.5805208092136149</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5384018181079158</v>
+        <v>0.5384018181078826</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5058550836881692</v>
+        <v>0.505855083688161</v>
       </c>
       <c r="W6" t="n">
-        <v>0.4276918222347856</v>
+        <v>0.4276918222348656</v>
       </c>
       <c r="X6" t="n">
-        <v>0.874114434843266</v>
+        <v>0.8741144348433514</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5730077870644414</v>
+        <v>0.5730077870644976</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.4409887738201361</v>
+        <v>0.4409887738202213</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.4808089435241037</v>
+        <v>0.4808089435241714</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9480103395719454</v>
+        <v>0.9480103395719388</v>
       </c>
     </row>
     <row r="7">
@@ -6498,85 +6498,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3192775324019747</v>
+        <v>0.3192775324020284</v>
       </c>
       <c r="C7" t="n">
-        <v>0.398047625469075</v>
+        <v>0.3980476254687485</v>
       </c>
       <c r="D7" t="n">
-        <v>0.387321812842356</v>
+        <v>0.3873218128424002</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3473932830057568</v>
+        <v>0.3473932830057865</v>
       </c>
       <c r="F7" t="n">
-        <v>0.328969530976762</v>
+        <v>0.3289695309767606</v>
       </c>
       <c r="G7" t="n">
-        <v>0.3917909598148428</v>
+        <v>0.3917909598148711</v>
       </c>
       <c r="H7" t="n">
-        <v>0.387321812842356</v>
+        <v>0.3873218128424002</v>
       </c>
       <c r="I7" t="n">
-        <v>0.387321812842356</v>
+        <v>0.3873218128424002</v>
       </c>
       <c r="J7" t="n">
-        <v>0.374486227984358</v>
+        <v>0.3744862279843735</v>
       </c>
       <c r="K7" t="n">
-        <v>0.387321812842356</v>
+        <v>0.3873218128424002</v>
       </c>
       <c r="L7" t="n">
-        <v>0.387321812842356</v>
+        <v>0.3873218128424002</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3970451488119214</v>
+        <v>0.3970451488119225</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3345761119130924</v>
+        <v>0.3345761119130363</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3394308106110425</v>
+        <v>0.339430810611064</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3358777416208721</v>
+        <v>0.3358777416209068</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3059052782925137</v>
+        <v>0.3059052782925503</v>
       </c>
       <c r="R7" t="n">
-        <v>0.387321812842356</v>
+        <v>0.3873218128424002</v>
       </c>
       <c r="S7" t="n">
-        <v>0.387321812842356</v>
+        <v>0.3873218128424002</v>
       </c>
       <c r="T7" t="n">
-        <v>0.387321812842356</v>
+        <v>0.3873218128424002</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3439991493684177</v>
+        <v>0.3439991493684467</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3497360763573641</v>
+        <v>0.3497360763573497</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3776949075370589</v>
+        <v>0.3776949075370226</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3025013938907687</v>
+        <v>0.3025013938908017</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4541711525965277</v>
+        <v>0.4541711525965553</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.3180135749693277</v>
+        <v>0.3180135749694536</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.387321812842356</v>
+        <v>0.3873218128424002</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.4586819931107213</v>
+        <v>0.4586819931107177</v>
       </c>
     </row>
   </sheetData>
@@ -6742,85 +6742,85 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.434932751459804</v>
+        <v>2.434932751459815</v>
       </c>
       <c r="C2" t="n">
         <v>2.97602141231558</v>
       </c>
       <c r="D2" t="n">
-        <v>1.516225685908624</v>
+        <v>1.516225685908633</v>
       </c>
       <c r="E2" t="n">
-        <v>4.156107113402934</v>
+        <v>4.15610711340294</v>
       </c>
       <c r="F2" t="n">
-        <v>4.320357137358664</v>
+        <v>4.320357137358658</v>
       </c>
       <c r="G2" t="n">
-        <v>2.468261792934524</v>
+        <v>2.468261792934534</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6981184482862116</v>
+        <v>0.6981184482862185</v>
       </c>
       <c r="I2" t="n">
-        <v>3.137783551184273</v>
+        <v>3.137783551184284</v>
       </c>
       <c r="J2" t="n">
-        <v>2.163422729629959</v>
+        <v>2.163422729629955</v>
       </c>
       <c r="K2" t="n">
-        <v>2.870558729354352</v>
+        <v>2.870558729354359</v>
       </c>
       <c r="L2" t="n">
-        <v>4.49127121414273</v>
+        <v>4.491271214142738</v>
       </c>
       <c r="M2" t="n">
-        <v>1.577383319731413</v>
+        <v>1.577383319731414</v>
       </c>
       <c r="N2" t="n">
-        <v>1.468961059938946</v>
+        <v>1.468961059938953</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8297118598789384</v>
+        <v>0.8297118598789474</v>
       </c>
       <c r="P2" t="n">
-        <v>1.333204310356135</v>
+        <v>1.333204310356143</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.162315195418332</v>
+        <v>3.162315195418341</v>
       </c>
       <c r="R2" t="n">
-        <v>4.497813628585578</v>
+        <v>4.497813628585588</v>
       </c>
       <c r="S2" t="n">
-        <v>3.442983168779189</v>
+        <v>3.442983168779204</v>
       </c>
       <c r="T2" t="n">
-        <v>2.089680708540121</v>
+        <v>2.089680708540123</v>
       </c>
       <c r="U2" t="n">
-        <v>0.978301544665208</v>
+        <v>0.9783015446652205</v>
       </c>
       <c r="V2" t="n">
-        <v>1.233237433056028</v>
+        <v>1.233237433056027</v>
       </c>
       <c r="W2" t="n">
-        <v>1.944555841903573</v>
+        <v>1.944555841903582</v>
       </c>
       <c r="X2" t="n">
-        <v>2.297385161071614</v>
+        <v>2.297385161071625</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.203517737957302</v>
+        <v>2.203517737957304</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.483413028216959</v>
+        <v>1.483413028216968</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.213225269578905</v>
+        <v>1.213225269578913</v>
       </c>
       <c r="AB2" t="n">
-        <v>2.268086503704077</v>
+        <v>2.268086503704079</v>
       </c>
     </row>
     <row r="3">
@@ -6830,85 +6830,85 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.5984485912416329</v>
+        <v>0.5984485912416446</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8298984922369578</v>
+        <v>0.8298984922369542</v>
       </c>
       <c r="D3" t="n">
-        <v>0.816681688398556</v>
+        <v>0.8166816883985656</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6952814251464083</v>
+        <v>0.6952814251464091</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6352130575687399</v>
+        <v>0.6352130575687414</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8619337427077591</v>
+        <v>0.8619337427077695</v>
       </c>
       <c r="H3" t="n">
-        <v>0.816681688398556</v>
+        <v>0.8166816883985656</v>
       </c>
       <c r="I3" t="n">
-        <v>0.816681688398556</v>
+        <v>0.8166816883985656</v>
       </c>
       <c r="J3" t="n">
-        <v>0.810748899474074</v>
+        <v>0.8107488994740779</v>
       </c>
       <c r="K3" t="n">
-        <v>0.816681688398556</v>
+        <v>0.8166816883985656</v>
       </c>
       <c r="L3" t="n">
-        <v>0.816681688398556</v>
+        <v>0.8166816883985656</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8174178165103402</v>
+        <v>0.8174178165103436</v>
       </c>
       <c r="N3" t="n">
-        <v>0.6475145283387764</v>
+        <v>0.6475145283387843</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6940031324323372</v>
+        <v>0.6940031324323448</v>
       </c>
       <c r="P3" t="n">
-        <v>0.6826076522854003</v>
+        <v>0.682607652285415</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.555560806909541</v>
+        <v>0.5555608069095528</v>
       </c>
       <c r="R3" t="n">
-        <v>0.816681688398556</v>
+        <v>0.8166816883985656</v>
       </c>
       <c r="S3" t="n">
-        <v>0.816681688398556</v>
+        <v>0.8166816883985656</v>
       </c>
       <c r="T3" t="n">
-        <v>0.816681688398556</v>
+        <v>0.8166816883985656</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7085209803227281</v>
+        <v>0.7085209803227354</v>
       </c>
       <c r="V3" t="n">
-        <v>0.7408738861039357</v>
+        <v>0.7408738861039381</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8167245767956638</v>
+        <v>0.8167245767956747</v>
       </c>
       <c r="X3" t="n">
-        <v>0.5755623034931248</v>
+        <v>0.57556230349313</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.030853405556509</v>
+        <v>1.030853405556523</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.5943947994838009</v>
+        <v>0.5943947994838107</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.816681688398556</v>
+        <v>0.8166816883985656</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.040847582813912</v>
+        <v>1.040847582813913</v>
       </c>
     </row>
     <row r="4">
@@ -6918,85 +6918,85 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2.227078412640255</v>
+        <v>2.227078412640273</v>
       </c>
       <c r="C4" t="n">
-        <v>2.432698309777195</v>
+        <v>2.432698309777201</v>
       </c>
       <c r="D4" t="n">
-        <v>1.89222047524988</v>
+        <v>1.892220475249895</v>
       </c>
       <c r="E4" t="n">
-        <v>2.851123135534422</v>
+        <v>2.851123135534424</v>
       </c>
       <c r="F4" t="n">
-        <v>2.916051477921999</v>
+        <v>2.916051477922007</v>
       </c>
       <c r="G4" t="n">
-        <v>2.239226456888428</v>
+        <v>2.239226456888442</v>
       </c>
       <c r="H4" t="n">
-        <v>1.594029993836716</v>
+        <v>1.594029993836726</v>
       </c>
       <c r="I4" t="n">
-        <v>2.483259275849045</v>
+        <v>2.483259275849062</v>
       </c>
       <c r="J4" t="n">
         <v>2.08928058898932</v>
       </c>
       <c r="K4" t="n">
-        <v>2.385858966204323</v>
+        <v>2.385858966204339</v>
       </c>
       <c r="L4" t="n">
-        <v>2.976589635542839</v>
+        <v>2.976589635542854</v>
       </c>
       <c r="M4" t="n">
-        <v>1.914979532689331</v>
+        <v>1.914979532689337</v>
       </c>
       <c r="N4" t="n">
-        <v>1.874993074093191</v>
+        <v>1.874993074093209</v>
       </c>
       <c r="O4" t="n">
-        <v>1.64199424711441</v>
+        <v>1.641994247114426</v>
       </c>
       <c r="P4" t="n">
-        <v>1.825511333006494</v>
+        <v>1.825511333006511</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.492200772107249</v>
+        <v>2.492200772107266</v>
       </c>
       <c r="R4" t="n">
-        <v>2.978974268782349</v>
+        <v>2.978974268782364</v>
       </c>
       <c r="S4" t="n">
-        <v>2.594500952627544</v>
+        <v>2.594500952627557</v>
       </c>
       <c r="T4" t="n">
-        <v>2.101238097150202</v>
+        <v>2.101238097150215</v>
       </c>
       <c r="U4" t="n">
-        <v>1.696153442390833</v>
+        <v>1.696153442390851</v>
       </c>
       <c r="V4" t="n">
-        <v>1.546009847968903</v>
+        <v>1.546009847968938</v>
       </c>
       <c r="W4" t="n">
-        <v>2.048341787403408</v>
+        <v>2.048341787403423</v>
       </c>
       <c r="X4" t="n">
-        <v>2.176943931109115</v>
+        <v>2.17694393110913</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.142730357630878</v>
+        <v>2.142730357630894</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.880260646826948</v>
+        <v>1.880260646826963</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.781780381508222</v>
+        <v>1.781780381508236</v>
       </c>
       <c r="AB4" t="n">
-        <v>2.163851988755555</v>
+        <v>2.163851988755561</v>
       </c>
     </row>
     <row r="5">
@@ -7006,85 +7006,85 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.557701501326524</v>
+        <v>1.557701501326535</v>
       </c>
       <c r="C5" t="n">
-        <v>1.650461706456211</v>
+        <v>1.650461706456215</v>
       </c>
       <c r="D5" t="n">
-        <v>1.637244902617815</v>
+        <v>1.637244902617825</v>
       </c>
       <c r="E5" t="n">
-        <v>1.589692811231923</v>
+        <v>1.589692811231932</v>
       </c>
       <c r="F5" t="n">
-        <v>1.572859733985127</v>
+        <v>1.572859733985136</v>
       </c>
       <c r="G5" t="n">
-        <v>1.653738745037066</v>
+        <v>1.65373874503708</v>
       </c>
       <c r="H5" t="n">
-        <v>1.637244902617815</v>
+        <v>1.637244902617825</v>
       </c>
       <c r="I5" t="n">
-        <v>1.637244902617815</v>
+        <v>1.637244902617825</v>
       </c>
       <c r="J5" t="n">
-        <v>1.596246861795556</v>
+        <v>1.596246861795562</v>
       </c>
       <c r="K5" t="n">
-        <v>1.637244902617815</v>
+        <v>1.637244902617825</v>
       </c>
       <c r="L5" t="n">
-        <v>1.637244902617815</v>
+        <v>1.637244902617825</v>
       </c>
       <c r="M5" t="n">
-        <v>1.63798103073074</v>
+        <v>1.637981030730748</v>
       </c>
       <c r="N5" t="n">
-        <v>1.575585459237112</v>
+        <v>1.57558545923712</v>
       </c>
       <c r="O5" t="n">
-        <v>1.592530009532459</v>
+        <v>1.592530009532471</v>
       </c>
       <c r="P5" t="n">
-        <v>1.588376490831386</v>
+        <v>1.588376490831399</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.542069407551264</v>
+        <v>1.542069407551278</v>
       </c>
       <c r="R5" t="n">
-        <v>1.637244902617815</v>
+        <v>1.637244902617825</v>
       </c>
       <c r="S5" t="n">
-        <v>1.637244902617815</v>
+        <v>1.637244902617825</v>
       </c>
       <c r="T5" t="n">
-        <v>1.637244902617815</v>
+        <v>1.637244902617825</v>
       </c>
       <c r="U5" t="n">
-        <v>1.597821594611331</v>
+        <v>1.597821594611341</v>
       </c>
       <c r="V5" t="n">
-        <v>1.366549116729663</v>
+        <v>1.366549116729568</v>
       </c>
       <c r="W5" t="n">
-        <v>1.637260534934935</v>
+        <v>1.637260534934948</v>
       </c>
       <c r="X5" t="n">
-        <v>1.549359718186543</v>
+        <v>1.54935971818656</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.715307978590613</v>
+        <v>1.715307978590624</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.556223941832817</v>
+        <v>1.556223941832831</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.637244902617815</v>
+        <v>1.637244902617825</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.716537813058074</v>
+        <v>1.716537813058084</v>
       </c>
     </row>
     <row r="6">
@@ -7094,85 +7094,85 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.062225302045034</v>
+        <v>1.062225302045043</v>
       </c>
       <c r="C6" t="n">
-        <v>1.267845199181973</v>
+        <v>1.267845199181974</v>
       </c>
       <c r="D6" t="n">
-        <v>0.727367364654658</v>
+        <v>0.7273673646546641</v>
       </c>
       <c r="E6" t="n">
-        <v>1.686270024939196</v>
+        <v>1.686270024939197</v>
       </c>
       <c r="F6" t="n">
-        <v>1.751198367326779</v>
+        <v>1.751198367326777</v>
       </c>
       <c r="G6" t="n">
-        <v>1.061698098185427</v>
+        <v>1.061698098185436</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4291768832414949</v>
+        <v>0.4291768832414975</v>
       </c>
       <c r="I6" t="n">
-        <v>1.318406165253823</v>
+        <v>1.31840616525383</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9472643068448386</v>
+        <v>0.9472643068448425</v>
       </c>
       <c r="K6" t="n">
-        <v>1.221005855609101</v>
+        <v>1.221005855609109</v>
       </c>
       <c r="L6" t="n">
-        <v>1.811736524947617</v>
+        <v>1.811736524947623</v>
       </c>
       <c r="M6" t="n">
-        <v>0.7501264220941084</v>
+        <v>0.7501264220941091</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7101399634979696</v>
+        <v>0.7101399634979804</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4644658884114077</v>
+        <v>0.4644658884114172</v>
       </c>
       <c r="P6" t="n">
-        <v>0.6479829743034925</v>
+        <v>0.6479829743035023</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.327347661512027</v>
+        <v>1.327347661512034</v>
       </c>
       <c r="R6" t="n">
-        <v>1.814121158187127</v>
+        <v>1.814121158187133</v>
       </c>
       <c r="S6" t="n">
-        <v>1.429647842032321</v>
+        <v>1.429647842032329</v>
       </c>
       <c r="T6" t="n">
-        <v>0.9363849865549825</v>
+        <v>0.9363849865549929</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5186250836878312</v>
+        <v>0.5186250836878429</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6030575980585898</v>
+        <v>0.6030575980585899</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8708134287004066</v>
+        <v>0.8708134287004164</v>
       </c>
       <c r="X6" t="n">
-        <v>0.9994155724061144</v>
+        <v>0.9994155724061231</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.9778772470356575</v>
+        <v>0.9778772470356675</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.7154075362317263</v>
+        <v>0.7154075362317315</v>
       </c>
       <c r="AA6" t="n">
-        <v>0.6169272709129994</v>
+        <v>0.6169272709130061</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9989988781603328</v>
+        <v>0.9989988781603324</v>
       </c>
     </row>
     <row r="7">
@@ -7182,85 +7182,85 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3928483907313023</v>
+        <v>0.3928483907313044</v>
       </c>
       <c r="C7" t="n">
-        <v>0.4856085958609905</v>
+        <v>0.4856085958609921</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4723917920225937</v>
+        <v>0.4723917920225949</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4248397006367029</v>
+        <v>0.4248397006367033</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4080066233899052</v>
+        <v>0.4080066233899059</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4762103863340626</v>
+        <v>0.4762103863340715</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4723917920225937</v>
+        <v>0.4723917920225949</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4723917920225937</v>
+        <v>0.4723917920225949</v>
       </c>
       <c r="J7" t="n">
-        <v>0.454230579651079</v>
+        <v>0.4542305796510832</v>
       </c>
       <c r="K7" t="n">
-        <v>0.4723917920225937</v>
+        <v>0.4723917920225949</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4723917920225937</v>
+        <v>0.4723917920225949</v>
       </c>
       <c r="M7" t="n">
-        <v>0.4731279201355191</v>
+        <v>0.4731279201355194</v>
       </c>
       <c r="N7" t="n">
-        <v>0.410732348641889</v>
+        <v>0.4107323486418887</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4150016508294572</v>
+        <v>0.4150016508294643</v>
       </c>
       <c r="P7" t="n">
-        <v>0.4108481321283844</v>
+        <v>0.4108481321283917</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3772162969560432</v>
+        <v>0.3772162969560462</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4723917920225937</v>
+        <v>0.4723917920225949</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4723917920225937</v>
+        <v>0.4723917920225949</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4723917920225937</v>
+        <v>0.4723917920225949</v>
       </c>
       <c r="U7" t="n">
-        <v>0.4202932359083288</v>
+        <v>0.4202932359083347</v>
       </c>
       <c r="V7" t="n">
-        <v>0.4235968668192238</v>
+        <v>0.4235968668192236</v>
       </c>
       <c r="W7" t="n">
-        <v>0.459732176231935</v>
+        <v>0.4597321762319418</v>
       </c>
       <c r="X7" t="n">
-        <v>0.3718313594835419</v>
+        <v>0.3718313594835532</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5504548679953928</v>
+        <v>0.5504548679953932</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.3913708312375956</v>
+        <v>0.3913708312376002</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.4723917920225937</v>
+        <v>0.4723917920225949</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.5516847024628551</v>
+        <v>0.5516847024628548</v>
       </c>
     </row>
   </sheetData>
